--- a/public/templates/inventory-count-template.xlsx
+++ b/public/templates/inventory-count-template.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1163" uniqueCount="120">
   <si>
     <t xml:space="preserve">ATELIER BY RICHARD — PHYSICAL INVENTORY COUNT</t>
   </si>
@@ -236,6 +236,9 @@
     <t xml:space="preserve">Béret Basque  (BBQ)</t>
   </si>
   <si>
+    <t xml:space="preserve">☐</t>
+  </si>
+  <si>
     <t xml:space="preserve">Bérichon / Herbe  (BER)</t>
   </si>
   <si>
@@ -398,7 +401,7 @@
     <numFmt numFmtId="168" formatCode="#,##0.000"/>
     <numFmt numFmtId="169" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="19">
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -505,6 +508,14 @@
       <charset val="1"/>
     </font>
     <font>
+      <b val="true"/>
+      <sz val="16"/>
+      <color rgb="FF1F3B2C"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
       <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
@@ -598,16 +609,16 @@
     </border>
     <border diagonalUp="false" diagonalDown="false">
       <left style="thin">
-        <color rgb="FF9CA3AF"/>
+        <color rgb="FFB0B0B0"/>
       </left>
       <right style="thin">
-        <color rgb="FF9CA3AF"/>
+        <color rgb="FFB0B0B0"/>
       </right>
       <top style="thin">
-        <color rgb="FF9CA3AF"/>
+        <color rgb="FFB0B0B0"/>
       </top>
       <bottom style="thin">
-        <color rgb="FF9CA3AF"/>
+        <color rgb="FFB0B0B0"/>
       </bottom>
       <diagonal/>
     </border>
@@ -746,7 +757,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -774,7 +785,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -790,7 +801,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -802,23 +813,23 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="17" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="18" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="17" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="18" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="17" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="18" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="17" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="169" fontId="18" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -947,7 +958,7 @@
       <rgbColor rgb="FFFF9900"/>
       <rgbColor rgb="FFFF6600"/>
       <rgbColor rgb="FF595959"/>
-      <rgbColor rgb="FF9CA3AF"/>
+      <rgbColor rgb="FFB0B0B0"/>
       <rgbColor rgb="FF003366"/>
       <rgbColor rgb="FF339966"/>
       <rgbColor rgb="FF003300"/>
@@ -4882,8 +4893,8 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="11" style="1" width="12"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="1" width="15"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="1" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="0" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="1" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="1" width="9"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4972,8 +4983,12 @@
       <c r="C6" s="26"/>
       <c r="D6" s="26"/>
       <c r="E6" s="26"/>
-      <c r="F6" s="27"/>
-      <c r="G6" s="27"/>
+      <c r="F6" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G6" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H6" s="26"/>
       <c r="I6" s="28"/>
       <c r="J6" s="26"/>
@@ -5002,8 +5017,12 @@
       <c r="C7" s="34"/>
       <c r="D7" s="34"/>
       <c r="E7" s="34"/>
-      <c r="F7" s="27"/>
-      <c r="G7" s="27"/>
+      <c r="F7" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G7" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H7" s="26"/>
       <c r="I7" s="26"/>
       <c r="J7" s="26"/>
@@ -5020,8 +5039,12 @@
       <c r="C8" s="34"/>
       <c r="D8" s="34"/>
       <c r="E8" s="34"/>
-      <c r="F8" s="27"/>
-      <c r="G8" s="27"/>
+      <c r="F8" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G8" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H8" s="26"/>
       <c r="I8" s="26"/>
       <c r="J8" s="26"/>
@@ -5038,8 +5061,12 @@
       <c r="C9" s="34"/>
       <c r="D9" s="34"/>
       <c r="E9" s="34"/>
-      <c r="F9" s="27"/>
-      <c r="G9" s="27"/>
+      <c r="F9" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G9" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H9" s="26"/>
       <c r="I9" s="26"/>
       <c r="J9" s="26"/>
@@ -5056,8 +5083,12 @@
       <c r="C10" s="34"/>
       <c r="D10" s="34"/>
       <c r="E10" s="34"/>
-      <c r="F10" s="27"/>
-      <c r="G10" s="27"/>
+      <c r="F10" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G10" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H10" s="26"/>
       <c r="I10" s="26"/>
       <c r="J10" s="26"/>
@@ -5074,8 +5105,12 @@
       <c r="C11" s="34"/>
       <c r="D11" s="34"/>
       <c r="E11" s="34"/>
-      <c r="F11" s="27"/>
-      <c r="G11" s="27"/>
+      <c r="F11" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G11" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H11" s="26"/>
       <c r="I11" s="26"/>
       <c r="J11" s="26"/>
@@ -5088,7 +5123,7 @@
     </row>
     <row r="12" s="25" customFormat="true" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="24" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B12" s="24"/>
       <c r="C12" s="24"/>
@@ -5112,8 +5147,12 @@
       <c r="C13" s="34"/>
       <c r="D13" s="34"/>
       <c r="E13" s="34"/>
-      <c r="F13" s="27"/>
-      <c r="G13" s="27"/>
+      <c r="F13" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G13" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H13" s="26"/>
       <c r="I13" s="26"/>
       <c r="J13" s="26"/>
@@ -5142,8 +5181,12 @@
       <c r="C14" s="34"/>
       <c r="D14" s="34"/>
       <c r="E14" s="34"/>
-      <c r="F14" s="27"/>
-      <c r="G14" s="27"/>
+      <c r="F14" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G14" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H14" s="26"/>
       <c r="I14" s="26"/>
       <c r="J14" s="26"/>
@@ -5160,8 +5203,12 @@
       <c r="C15" s="34"/>
       <c r="D15" s="34"/>
       <c r="E15" s="34"/>
-      <c r="F15" s="27"/>
-      <c r="G15" s="27"/>
+      <c r="F15" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G15" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H15" s="26"/>
       <c r="I15" s="26"/>
       <c r="J15" s="26"/>
@@ -5178,8 +5225,12 @@
       <c r="C16" s="34"/>
       <c r="D16" s="34"/>
       <c r="E16" s="34"/>
-      <c r="F16" s="27"/>
-      <c r="G16" s="27"/>
+      <c r="F16" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G16" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H16" s="26"/>
       <c r="I16" s="26"/>
       <c r="J16" s="26"/>
@@ -5196,8 +5247,12 @@
       <c r="C17" s="34"/>
       <c r="D17" s="34"/>
       <c r="E17" s="34"/>
-      <c r="F17" s="27"/>
-      <c r="G17" s="27"/>
+      <c r="F17" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G17" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H17" s="26"/>
       <c r="I17" s="26"/>
       <c r="J17" s="26"/>
@@ -5214,8 +5269,12 @@
       <c r="C18" s="34"/>
       <c r="D18" s="34"/>
       <c r="E18" s="34"/>
-      <c r="F18" s="27"/>
-      <c r="G18" s="27"/>
+      <c r="F18" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G18" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H18" s="26"/>
       <c r="I18" s="26"/>
       <c r="J18" s="26"/>
@@ -5232,8 +5291,12 @@
       <c r="C19" s="34"/>
       <c r="D19" s="34"/>
       <c r="E19" s="34"/>
-      <c r="F19" s="27"/>
-      <c r="G19" s="27"/>
+      <c r="F19" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G19" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H19" s="26"/>
       <c r="I19" s="26"/>
       <c r="J19" s="26"/>
@@ -5250,8 +5313,12 @@
       <c r="C20" s="34"/>
       <c r="D20" s="34"/>
       <c r="E20" s="34"/>
-      <c r="F20" s="27"/>
-      <c r="G20" s="27"/>
+      <c r="F20" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G20" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H20" s="26"/>
       <c r="I20" s="26"/>
       <c r="J20" s="26"/>
@@ -5268,8 +5335,12 @@
       <c r="C21" s="34"/>
       <c r="D21" s="34"/>
       <c r="E21" s="34"/>
-      <c r="F21" s="27"/>
-      <c r="G21" s="27"/>
+      <c r="F21" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G21" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H21" s="26"/>
       <c r="I21" s="26"/>
       <c r="J21" s="26"/>
@@ -5286,8 +5357,12 @@
       <c r="C22" s="34"/>
       <c r="D22" s="34"/>
       <c r="E22" s="34"/>
-      <c r="F22" s="27"/>
-      <c r="G22" s="27"/>
+      <c r="F22" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G22" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H22" s="26"/>
       <c r="I22" s="26"/>
       <c r="J22" s="26"/>
@@ -5304,8 +5379,12 @@
       <c r="C23" s="34"/>
       <c r="D23" s="34"/>
       <c r="E23" s="34"/>
-      <c r="F23" s="27"/>
-      <c r="G23" s="27"/>
+      <c r="F23" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G23" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H23" s="26"/>
       <c r="I23" s="26"/>
       <c r="J23" s="26"/>
@@ -5322,8 +5401,12 @@
       <c r="C24" s="34"/>
       <c r="D24" s="34"/>
       <c r="E24" s="34"/>
-      <c r="F24" s="27"/>
-      <c r="G24" s="27"/>
+      <c r="F24" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G24" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H24" s="26"/>
       <c r="I24" s="26"/>
       <c r="J24" s="26"/>
@@ -5336,7 +5419,7 @@
     </row>
     <row r="25" s="25" customFormat="true" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="24" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B25" s="24"/>
       <c r="C25" s="24"/>
@@ -5360,8 +5443,12 @@
       <c r="C26" s="34"/>
       <c r="D26" s="34"/>
       <c r="E26" s="34"/>
-      <c r="F26" s="27"/>
-      <c r="G26" s="27"/>
+      <c r="F26" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G26" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H26" s="26"/>
       <c r="I26" s="26"/>
       <c r="J26" s="26"/>
@@ -5390,8 +5477,12 @@
       <c r="C27" s="34"/>
       <c r="D27" s="34"/>
       <c r="E27" s="34"/>
-      <c r="F27" s="27"/>
-      <c r="G27" s="27"/>
+      <c r="F27" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G27" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H27" s="26"/>
       <c r="I27" s="26"/>
       <c r="J27" s="26"/>
@@ -5408,8 +5499,12 @@
       <c r="C28" s="34"/>
       <c r="D28" s="34"/>
       <c r="E28" s="34"/>
-      <c r="F28" s="27"/>
-      <c r="G28" s="27"/>
+      <c r="F28" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G28" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H28" s="26"/>
       <c r="I28" s="26"/>
       <c r="J28" s="26"/>
@@ -5426,8 +5521,12 @@
       <c r="C29" s="34"/>
       <c r="D29" s="34"/>
       <c r="E29" s="34"/>
-      <c r="F29" s="27"/>
-      <c r="G29" s="27"/>
+      <c r="F29" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G29" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H29" s="26"/>
       <c r="I29" s="26"/>
       <c r="J29" s="26"/>
@@ -5444,8 +5543,12 @@
       <c r="C30" s="34"/>
       <c r="D30" s="34"/>
       <c r="E30" s="34"/>
-      <c r="F30" s="27"/>
-      <c r="G30" s="27"/>
+      <c r="F30" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G30" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H30" s="26"/>
       <c r="I30" s="26"/>
       <c r="J30" s="26"/>
@@ -5462,8 +5565,12 @@
       <c r="C31" s="34"/>
       <c r="D31" s="34"/>
       <c r="E31" s="34"/>
-      <c r="F31" s="27"/>
-      <c r="G31" s="27"/>
+      <c r="F31" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G31" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H31" s="26"/>
       <c r="I31" s="26"/>
       <c r="J31" s="26"/>
@@ -5480,8 +5587,12 @@
       <c r="C32" s="34"/>
       <c r="D32" s="34"/>
       <c r="E32" s="34"/>
-      <c r="F32" s="27"/>
-      <c r="G32" s="27"/>
+      <c r="F32" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G32" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H32" s="26"/>
       <c r="I32" s="26"/>
       <c r="J32" s="26"/>
@@ -5498,8 +5609,12 @@
       <c r="C33" s="34"/>
       <c r="D33" s="34"/>
       <c r="E33" s="34"/>
-      <c r="F33" s="27"/>
-      <c r="G33" s="27"/>
+      <c r="F33" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G33" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H33" s="26"/>
       <c r="I33" s="26"/>
       <c r="J33" s="26"/>
@@ -5516,8 +5631,12 @@
       <c r="C34" s="34"/>
       <c r="D34" s="34"/>
       <c r="E34" s="34"/>
-      <c r="F34" s="27"/>
-      <c r="G34" s="27"/>
+      <c r="F34" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G34" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H34" s="26"/>
       <c r="I34" s="26"/>
       <c r="J34" s="26"/>
@@ -5534,8 +5653,12 @@
       <c r="C35" s="34"/>
       <c r="D35" s="34"/>
       <c r="E35" s="34"/>
-      <c r="F35" s="27"/>
-      <c r="G35" s="27"/>
+      <c r="F35" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G35" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H35" s="26"/>
       <c r="I35" s="26"/>
       <c r="J35" s="26"/>
@@ -5552,8 +5675,12 @@
       <c r="C36" s="34"/>
       <c r="D36" s="34"/>
       <c r="E36" s="34"/>
-      <c r="F36" s="27"/>
-      <c r="G36" s="27"/>
+      <c r="F36" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G36" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H36" s="26"/>
       <c r="I36" s="26"/>
       <c r="J36" s="26"/>
@@ -5570,8 +5697,12 @@
       <c r="C37" s="34"/>
       <c r="D37" s="34"/>
       <c r="E37" s="34"/>
-      <c r="F37" s="27"/>
-      <c r="G37" s="27"/>
+      <c r="F37" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G37" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H37" s="26"/>
       <c r="I37" s="26"/>
       <c r="J37" s="26"/>
@@ -5588,8 +5719,12 @@
       <c r="C38" s="34"/>
       <c r="D38" s="34"/>
       <c r="E38" s="34"/>
-      <c r="F38" s="27"/>
-      <c r="G38" s="27"/>
+      <c r="F38" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G38" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H38" s="26"/>
       <c r="I38" s="26"/>
       <c r="J38" s="26"/>
@@ -5606,8 +5741,12 @@
       <c r="C39" s="34"/>
       <c r="D39" s="34"/>
       <c r="E39" s="34"/>
-      <c r="F39" s="27"/>
-      <c r="G39" s="27"/>
+      <c r="F39" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G39" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H39" s="26"/>
       <c r="I39" s="26"/>
       <c r="J39" s="26"/>
@@ -5624,8 +5763,12 @@
       <c r="C40" s="34"/>
       <c r="D40" s="34"/>
       <c r="E40" s="34"/>
-      <c r="F40" s="27"/>
-      <c r="G40" s="27"/>
+      <c r="F40" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G40" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H40" s="26"/>
       <c r="I40" s="26"/>
       <c r="J40" s="26"/>
@@ -5642,8 +5785,12 @@
       <c r="C41" s="34"/>
       <c r="D41" s="34"/>
       <c r="E41" s="34"/>
-      <c r="F41" s="27"/>
-      <c r="G41" s="27"/>
+      <c r="F41" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G41" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H41" s="26"/>
       <c r="I41" s="26"/>
       <c r="J41" s="26"/>
@@ -5660,8 +5807,12 @@
       <c r="C42" s="34"/>
       <c r="D42" s="34"/>
       <c r="E42" s="34"/>
-      <c r="F42" s="27"/>
-      <c r="G42" s="27"/>
+      <c r="F42" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G42" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H42" s="26"/>
       <c r="I42" s="26"/>
       <c r="J42" s="26"/>
@@ -5678,8 +5829,12 @@
       <c r="C43" s="34"/>
       <c r="D43" s="34"/>
       <c r="E43" s="34"/>
-      <c r="F43" s="27"/>
-      <c r="G43" s="27"/>
+      <c r="F43" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G43" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H43" s="26"/>
       <c r="I43" s="26"/>
       <c r="J43" s="26"/>
@@ -5692,7 +5847,7 @@
     </row>
     <row r="44" s="25" customFormat="true" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="24" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B44" s="24"/>
       <c r="C44" s="24"/>
@@ -5716,8 +5871,12 @@
       <c r="C45" s="34"/>
       <c r="D45" s="34"/>
       <c r="E45" s="34"/>
-      <c r="F45" s="27"/>
-      <c r="G45" s="27"/>
+      <c r="F45" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G45" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H45" s="26"/>
       <c r="I45" s="26"/>
       <c r="J45" s="26"/>
@@ -5746,8 +5905,12 @@
       <c r="C46" s="34"/>
       <c r="D46" s="34"/>
       <c r="E46" s="34"/>
-      <c r="F46" s="27"/>
-      <c r="G46" s="27"/>
+      <c r="F46" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G46" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H46" s="26"/>
       <c r="I46" s="26"/>
       <c r="J46" s="26"/>
@@ -5764,8 +5927,12 @@
       <c r="C47" s="34"/>
       <c r="D47" s="34"/>
       <c r="E47" s="34"/>
-      <c r="F47" s="27"/>
-      <c r="G47" s="27"/>
+      <c r="F47" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G47" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H47" s="26"/>
       <c r="I47" s="26"/>
       <c r="J47" s="26"/>
@@ -5782,8 +5949,12 @@
       <c r="C48" s="34"/>
       <c r="D48" s="34"/>
       <c r="E48" s="34"/>
-      <c r="F48" s="27"/>
-      <c r="G48" s="27"/>
+      <c r="F48" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G48" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H48" s="26"/>
       <c r="I48" s="26"/>
       <c r="J48" s="26"/>
@@ -5800,8 +5971,12 @@
       <c r="C49" s="34"/>
       <c r="D49" s="34"/>
       <c r="E49" s="34"/>
-      <c r="F49" s="27"/>
-      <c r="G49" s="27"/>
+      <c r="F49" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G49" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H49" s="26"/>
       <c r="I49" s="26"/>
       <c r="J49" s="26"/>
@@ -5818,8 +5993,12 @@
       <c r="C50" s="34"/>
       <c r="D50" s="34"/>
       <c r="E50" s="34"/>
-      <c r="F50" s="27"/>
-      <c r="G50" s="27"/>
+      <c r="F50" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G50" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H50" s="26"/>
       <c r="I50" s="26"/>
       <c r="J50" s="26"/>
@@ -5836,8 +6015,12 @@
       <c r="C51" s="34"/>
       <c r="D51" s="34"/>
       <c r="E51" s="34"/>
-      <c r="F51" s="27"/>
-      <c r="G51" s="27"/>
+      <c r="F51" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G51" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H51" s="26"/>
       <c r="I51" s="26"/>
       <c r="J51" s="26"/>
@@ -5854,8 +6037,12 @@
       <c r="C52" s="34"/>
       <c r="D52" s="34"/>
       <c r="E52" s="34"/>
-      <c r="F52" s="27"/>
-      <c r="G52" s="27"/>
+      <c r="F52" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G52" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H52" s="26"/>
       <c r="I52" s="26"/>
       <c r="J52" s="26"/>
@@ -5872,8 +6059,12 @@
       <c r="C53" s="34"/>
       <c r="D53" s="34"/>
       <c r="E53" s="34"/>
-      <c r="F53" s="27"/>
-      <c r="G53" s="27"/>
+      <c r="F53" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G53" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H53" s="26"/>
       <c r="I53" s="26"/>
       <c r="J53" s="26"/>
@@ -5890,8 +6081,12 @@
       <c r="C54" s="34"/>
       <c r="D54" s="34"/>
       <c r="E54" s="34"/>
-      <c r="F54" s="27"/>
-      <c r="G54" s="27"/>
+      <c r="F54" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G54" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H54" s="26"/>
       <c r="I54" s="26"/>
       <c r="J54" s="26"/>
@@ -5908,8 +6103,12 @@
       <c r="C55" s="34"/>
       <c r="D55" s="34"/>
       <c r="E55" s="34"/>
-      <c r="F55" s="27"/>
-      <c r="G55" s="27"/>
+      <c r="F55" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G55" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H55" s="26"/>
       <c r="I55" s="26"/>
       <c r="J55" s="26"/>
@@ -5926,8 +6125,12 @@
       <c r="C56" s="34"/>
       <c r="D56" s="34"/>
       <c r="E56" s="34"/>
-      <c r="F56" s="27"/>
-      <c r="G56" s="27"/>
+      <c r="F56" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G56" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H56" s="26"/>
       <c r="I56" s="26"/>
       <c r="J56" s="26"/>
@@ -5944,8 +6147,12 @@
       <c r="C57" s="34"/>
       <c r="D57" s="34"/>
       <c r="E57" s="34"/>
-      <c r="F57" s="27"/>
-      <c r="G57" s="27"/>
+      <c r="F57" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G57" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H57" s="26"/>
       <c r="I57" s="26"/>
       <c r="J57" s="26"/>
@@ -5962,8 +6169,12 @@
       <c r="C58" s="34"/>
       <c r="D58" s="34"/>
       <c r="E58" s="34"/>
-      <c r="F58" s="27"/>
-      <c r="G58" s="27"/>
+      <c r="F58" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G58" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H58" s="26"/>
       <c r="I58" s="26"/>
       <c r="J58" s="26"/>
@@ -5980,8 +6191,12 @@
       <c r="C59" s="34"/>
       <c r="D59" s="34"/>
       <c r="E59" s="34"/>
-      <c r="F59" s="27"/>
-      <c r="G59" s="27"/>
+      <c r="F59" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G59" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H59" s="26"/>
       <c r="I59" s="26"/>
       <c r="J59" s="26"/>
@@ -5998,8 +6213,12 @@
       <c r="C60" s="34"/>
       <c r="D60" s="34"/>
       <c r="E60" s="34"/>
-      <c r="F60" s="27"/>
-      <c r="G60" s="27"/>
+      <c r="F60" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G60" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H60" s="26"/>
       <c r="I60" s="26"/>
       <c r="J60" s="26"/>
@@ -6016,8 +6235,12 @@
       <c r="C61" s="34"/>
       <c r="D61" s="34"/>
       <c r="E61" s="34"/>
-      <c r="F61" s="27"/>
-      <c r="G61" s="27"/>
+      <c r="F61" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G61" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H61" s="26"/>
       <c r="I61" s="26"/>
       <c r="J61" s="26"/>
@@ -6034,8 +6257,12 @@
       <c r="C62" s="34"/>
       <c r="D62" s="34"/>
       <c r="E62" s="34"/>
-      <c r="F62" s="27"/>
-      <c r="G62" s="27"/>
+      <c r="F62" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G62" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H62" s="26"/>
       <c r="I62" s="26"/>
       <c r="J62" s="26"/>
@@ -6048,7 +6275,7 @@
     </row>
     <row r="63" s="25" customFormat="true" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A63" s="24" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B63" s="24"/>
       <c r="C63" s="24"/>
@@ -6072,8 +6299,12 @@
       <c r="C64" s="34"/>
       <c r="D64" s="34"/>
       <c r="E64" s="34"/>
-      <c r="F64" s="27"/>
-      <c r="G64" s="27"/>
+      <c r="F64" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G64" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H64" s="26"/>
       <c r="I64" s="26"/>
       <c r="J64" s="26"/>
@@ -6102,8 +6333,12 @@
       <c r="C65" s="34"/>
       <c r="D65" s="34"/>
       <c r="E65" s="34"/>
-      <c r="F65" s="27"/>
-      <c r="G65" s="27"/>
+      <c r="F65" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G65" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H65" s="26"/>
       <c r="I65" s="26"/>
       <c r="J65" s="26"/>
@@ -6132,8 +6367,12 @@
       <c r="C66" s="34"/>
       <c r="D66" s="34"/>
       <c r="E66" s="34"/>
-      <c r="F66" s="27"/>
-      <c r="G66" s="27"/>
+      <c r="F66" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G66" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H66" s="26"/>
       <c r="I66" s="26"/>
       <c r="J66" s="26"/>
@@ -6162,8 +6401,12 @@
       <c r="C67" s="34"/>
       <c r="D67" s="34"/>
       <c r="E67" s="34"/>
-      <c r="F67" s="27"/>
-      <c r="G67" s="27"/>
+      <c r="F67" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G67" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H67" s="26"/>
       <c r="I67" s="26"/>
       <c r="J67" s="26"/>
@@ -6192,8 +6435,12 @@
       <c r="C68" s="34"/>
       <c r="D68" s="34"/>
       <c r="E68" s="34"/>
-      <c r="F68" s="27"/>
-      <c r="G68" s="27"/>
+      <c r="F68" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G68" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H68" s="26"/>
       <c r="I68" s="26"/>
       <c r="J68" s="26"/>
@@ -6222,8 +6469,12 @@
       <c r="C69" s="34"/>
       <c r="D69" s="34"/>
       <c r="E69" s="34"/>
-      <c r="F69" s="27"/>
-      <c r="G69" s="27"/>
+      <c r="F69" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G69" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H69" s="26"/>
       <c r="I69" s="26"/>
       <c r="J69" s="26"/>
@@ -6252,8 +6503,12 @@
       <c r="C70" s="34"/>
       <c r="D70" s="34"/>
       <c r="E70" s="34"/>
-      <c r="F70" s="27"/>
-      <c r="G70" s="27"/>
+      <c r="F70" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G70" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H70" s="26"/>
       <c r="I70" s="26"/>
       <c r="J70" s="26"/>
@@ -6282,8 +6537,12 @@
       <c r="C71" s="34"/>
       <c r="D71" s="34"/>
       <c r="E71" s="34"/>
-      <c r="F71" s="27"/>
-      <c r="G71" s="27"/>
+      <c r="F71" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G71" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H71" s="26"/>
       <c r="I71" s="26"/>
       <c r="J71" s="26"/>
@@ -6312,8 +6571,12 @@
       <c r="C72" s="34"/>
       <c r="D72" s="34"/>
       <c r="E72" s="34"/>
-      <c r="F72" s="27"/>
-      <c r="G72" s="27"/>
+      <c r="F72" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G72" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H72" s="26"/>
       <c r="I72" s="26"/>
       <c r="J72" s="26"/>
@@ -6342,8 +6605,12 @@
       <c r="C73" s="34"/>
       <c r="D73" s="34"/>
       <c r="E73" s="34"/>
-      <c r="F73" s="27"/>
-      <c r="G73" s="27"/>
+      <c r="F73" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G73" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H73" s="26"/>
       <c r="I73" s="26"/>
       <c r="J73" s="26"/>
@@ -6372,8 +6639,12 @@
       <c r="C74" s="34"/>
       <c r="D74" s="34"/>
       <c r="E74" s="34"/>
-      <c r="F74" s="27"/>
-      <c r="G74" s="27"/>
+      <c r="F74" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G74" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H74" s="26"/>
       <c r="I74" s="26"/>
       <c r="J74" s="26"/>
@@ -6402,8 +6673,12 @@
       <c r="C75" s="34"/>
       <c r="D75" s="34"/>
       <c r="E75" s="34"/>
-      <c r="F75" s="27"/>
-      <c r="G75" s="27"/>
+      <c r="F75" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G75" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H75" s="26"/>
       <c r="I75" s="26"/>
       <c r="J75" s="26"/>
@@ -6432,8 +6707,12 @@
       <c r="C76" s="34"/>
       <c r="D76" s="34"/>
       <c r="E76" s="34"/>
-      <c r="F76" s="27"/>
-      <c r="G76" s="27"/>
+      <c r="F76" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G76" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H76" s="26"/>
       <c r="I76" s="26"/>
       <c r="J76" s="26"/>
@@ -6462,8 +6741,12 @@
       <c r="C77" s="34"/>
       <c r="D77" s="34"/>
       <c r="E77" s="34"/>
-      <c r="F77" s="27"/>
-      <c r="G77" s="27"/>
+      <c r="F77" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G77" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H77" s="26"/>
       <c r="I77" s="26"/>
       <c r="J77" s="26"/>
@@ -6492,8 +6775,12 @@
       <c r="C78" s="34"/>
       <c r="D78" s="34"/>
       <c r="E78" s="34"/>
-      <c r="F78" s="27"/>
-      <c r="G78" s="27"/>
+      <c r="F78" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G78" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H78" s="26"/>
       <c r="I78" s="26"/>
       <c r="J78" s="26"/>
@@ -6522,8 +6809,12 @@
       <c r="C79" s="34"/>
       <c r="D79" s="34"/>
       <c r="E79" s="34"/>
-      <c r="F79" s="27"/>
-      <c r="G79" s="27"/>
+      <c r="F79" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G79" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H79" s="26"/>
       <c r="I79" s="26"/>
       <c r="J79" s="26"/>
@@ -6552,8 +6843,12 @@
       <c r="C80" s="34"/>
       <c r="D80" s="34"/>
       <c r="E80" s="34"/>
-      <c r="F80" s="27"/>
-      <c r="G80" s="27"/>
+      <c r="F80" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G80" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H80" s="26"/>
       <c r="I80" s="26"/>
       <c r="J80" s="26"/>
@@ -6582,8 +6877,12 @@
       <c r="C81" s="34"/>
       <c r="D81" s="34"/>
       <c r="E81" s="34"/>
-      <c r="F81" s="27"/>
-      <c r="G81" s="27"/>
+      <c r="F81" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G81" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H81" s="26"/>
       <c r="I81" s="26"/>
       <c r="J81" s="26"/>
@@ -6612,8 +6911,12 @@
       <c r="C82" s="34"/>
       <c r="D82" s="34"/>
       <c r="E82" s="34"/>
-      <c r="F82" s="27"/>
-      <c r="G82" s="27"/>
+      <c r="F82" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G82" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H82" s="26"/>
       <c r="I82" s="26"/>
       <c r="J82" s="26"/>
@@ -6642,8 +6945,12 @@
       <c r="C83" s="34"/>
       <c r="D83" s="34"/>
       <c r="E83" s="34"/>
-      <c r="F83" s="27"/>
-      <c r="G83" s="27"/>
+      <c r="F83" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G83" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H83" s="26"/>
       <c r="I83" s="26"/>
       <c r="J83" s="26"/>
@@ -6672,8 +6979,12 @@
       <c r="C84" s="34"/>
       <c r="D84" s="34"/>
       <c r="E84" s="34"/>
-      <c r="F84" s="27"/>
-      <c r="G84" s="27"/>
+      <c r="F84" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G84" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H84" s="26"/>
       <c r="I84" s="26"/>
       <c r="J84" s="26"/>
@@ -6702,8 +7013,12 @@
       <c r="C85" s="34"/>
       <c r="D85" s="34"/>
       <c r="E85" s="34"/>
-      <c r="F85" s="27"/>
-      <c r="G85" s="27"/>
+      <c r="F85" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G85" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H85" s="26"/>
       <c r="I85" s="26"/>
       <c r="J85" s="26"/>
@@ -6732,8 +7047,12 @@
       <c r="C86" s="34"/>
       <c r="D86" s="34"/>
       <c r="E86" s="34"/>
-      <c r="F86" s="27"/>
-      <c r="G86" s="27"/>
+      <c r="F86" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G86" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H86" s="26"/>
       <c r="I86" s="26"/>
       <c r="J86" s="26"/>
@@ -6762,8 +7081,12 @@
       <c r="C87" s="34"/>
       <c r="D87" s="34"/>
       <c r="E87" s="34"/>
-      <c r="F87" s="27"/>
-      <c r="G87" s="27"/>
+      <c r="F87" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G87" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H87" s="26"/>
       <c r="I87" s="26"/>
       <c r="J87" s="26"/>
@@ -6792,8 +7115,12 @@
       <c r="C88" s="34"/>
       <c r="D88" s="34"/>
       <c r="E88" s="34"/>
-      <c r="F88" s="27"/>
-      <c r="G88" s="27"/>
+      <c r="F88" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G88" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H88" s="26"/>
       <c r="I88" s="26"/>
       <c r="J88" s="26"/>
@@ -6822,8 +7149,12 @@
       <c r="C89" s="34"/>
       <c r="D89" s="34"/>
       <c r="E89" s="34"/>
-      <c r="F89" s="27"/>
-      <c r="G89" s="27"/>
+      <c r="F89" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G89" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H89" s="26"/>
       <c r="I89" s="26"/>
       <c r="J89" s="26"/>
@@ -6852,8 +7183,12 @@
       <c r="C90" s="34"/>
       <c r="D90" s="34"/>
       <c r="E90" s="34"/>
-      <c r="F90" s="27"/>
-      <c r="G90" s="27"/>
+      <c r="F90" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G90" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H90" s="26"/>
       <c r="I90" s="26"/>
       <c r="J90" s="26"/>
@@ -6882,8 +7217,12 @@
       <c r="C91" s="34"/>
       <c r="D91" s="34"/>
       <c r="E91" s="34"/>
-      <c r="F91" s="27"/>
-      <c r="G91" s="27"/>
+      <c r="F91" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G91" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H91" s="26"/>
       <c r="I91" s="26"/>
       <c r="J91" s="26"/>
@@ -6912,8 +7251,12 @@
       <c r="C92" s="34"/>
       <c r="D92" s="34"/>
       <c r="E92" s="34"/>
-      <c r="F92" s="27"/>
-      <c r="G92" s="27"/>
+      <c r="F92" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G92" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H92" s="26"/>
       <c r="I92" s="26"/>
       <c r="J92" s="26"/>
@@ -6942,8 +7285,12 @@
       <c r="C93" s="34"/>
       <c r="D93" s="34"/>
       <c r="E93" s="34"/>
-      <c r="F93" s="27"/>
-      <c r="G93" s="27"/>
+      <c r="F93" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G93" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H93" s="26"/>
       <c r="I93" s="26"/>
       <c r="J93" s="26"/>
@@ -6972,8 +7319,12 @@
       <c r="C94" s="34"/>
       <c r="D94" s="34"/>
       <c r="E94" s="34"/>
-      <c r="F94" s="27"/>
-      <c r="G94" s="27"/>
+      <c r="F94" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G94" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H94" s="26"/>
       <c r="I94" s="26"/>
       <c r="J94" s="26"/>
@@ -7002,8 +7353,12 @@
       <c r="C95" s="34"/>
       <c r="D95" s="34"/>
       <c r="E95" s="34"/>
-      <c r="F95" s="27"/>
-      <c r="G95" s="27"/>
+      <c r="F95" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G95" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H95" s="26"/>
       <c r="I95" s="26"/>
       <c r="J95" s="26"/>
@@ -7032,8 +7387,12 @@
       <c r="C96" s="34"/>
       <c r="D96" s="34"/>
       <c r="E96" s="34"/>
-      <c r="F96" s="27"/>
-      <c r="G96" s="27"/>
+      <c r="F96" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G96" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H96" s="26"/>
       <c r="I96" s="26"/>
       <c r="J96" s="26"/>
@@ -7062,8 +7421,12 @@
       <c r="C97" s="34"/>
       <c r="D97" s="34"/>
       <c r="E97" s="34"/>
-      <c r="F97" s="27"/>
-      <c r="G97" s="27"/>
+      <c r="F97" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G97" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H97" s="26"/>
       <c r="I97" s="26"/>
       <c r="J97" s="26"/>
@@ -7092,8 +7455,12 @@
       <c r="C98" s="34"/>
       <c r="D98" s="34"/>
       <c r="E98" s="34"/>
-      <c r="F98" s="27"/>
-      <c r="G98" s="27"/>
+      <c r="F98" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G98" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H98" s="26"/>
       <c r="I98" s="26"/>
       <c r="J98" s="26"/>
@@ -7122,8 +7489,12 @@
       <c r="C99" s="34"/>
       <c r="D99" s="34"/>
       <c r="E99" s="34"/>
-      <c r="F99" s="27"/>
-      <c r="G99" s="27"/>
+      <c r="F99" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G99" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H99" s="26"/>
       <c r="I99" s="26"/>
       <c r="J99" s="26"/>
@@ -7152,8 +7523,12 @@
       <c r="C100" s="34"/>
       <c r="D100" s="34"/>
       <c r="E100" s="34"/>
-      <c r="F100" s="27"/>
-      <c r="G100" s="27"/>
+      <c r="F100" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G100" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H100" s="26"/>
       <c r="I100" s="26"/>
       <c r="J100" s="26"/>
@@ -7182,8 +7557,12 @@
       <c r="C101" s="34"/>
       <c r="D101" s="34"/>
       <c r="E101" s="34"/>
-      <c r="F101" s="27"/>
-      <c r="G101" s="27"/>
+      <c r="F101" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G101" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H101" s="26"/>
       <c r="I101" s="26"/>
       <c r="J101" s="26"/>
@@ -7200,8 +7579,12 @@
       <c r="C102" s="34"/>
       <c r="D102" s="34"/>
       <c r="E102" s="34"/>
-      <c r="F102" s="27"/>
-      <c r="G102" s="27"/>
+      <c r="F102" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G102" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H102" s="26"/>
       <c r="I102" s="26"/>
       <c r="J102" s="26"/>
@@ -7218,8 +7601,12 @@
       <c r="C103" s="34"/>
       <c r="D103" s="34"/>
       <c r="E103" s="34"/>
-      <c r="F103" s="27"/>
-      <c r="G103" s="27"/>
+      <c r="F103" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G103" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H103" s="26"/>
       <c r="I103" s="26"/>
       <c r="J103" s="26"/>
@@ -7236,8 +7623,12 @@
       <c r="C104" s="34"/>
       <c r="D104" s="34"/>
       <c r="E104" s="34"/>
-      <c r="F104" s="27"/>
-      <c r="G104" s="27"/>
+      <c r="F104" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G104" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H104" s="26"/>
       <c r="I104" s="26"/>
       <c r="J104" s="26"/>
@@ -7254,8 +7645,12 @@
       <c r="C105" s="34"/>
       <c r="D105" s="34"/>
       <c r="E105" s="34"/>
-      <c r="F105" s="27"/>
-      <c r="G105" s="27"/>
+      <c r="F105" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G105" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H105" s="26"/>
       <c r="I105" s="26"/>
       <c r="J105" s="26"/>
@@ -7272,8 +7667,12 @@
       <c r="C106" s="34"/>
       <c r="D106" s="34"/>
       <c r="E106" s="34"/>
-      <c r="F106" s="27"/>
-      <c r="G106" s="27"/>
+      <c r="F106" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G106" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H106" s="26"/>
       <c r="I106" s="26"/>
       <c r="J106" s="26"/>
@@ -7290,8 +7689,12 @@
       <c r="C107" s="34"/>
       <c r="D107" s="34"/>
       <c r="E107" s="34"/>
-      <c r="F107" s="27"/>
-      <c r="G107" s="27"/>
+      <c r="F107" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G107" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H107" s="26"/>
       <c r="I107" s="26"/>
       <c r="J107" s="26"/>
@@ -7308,8 +7711,12 @@
       <c r="C108" s="34"/>
       <c r="D108" s="34"/>
       <c r="E108" s="34"/>
-      <c r="F108" s="27"/>
-      <c r="G108" s="27"/>
+      <c r="F108" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G108" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H108" s="26"/>
       <c r="I108" s="26"/>
       <c r="J108" s="26"/>
@@ -7326,8 +7733,12 @@
       <c r="C109" s="34"/>
       <c r="D109" s="34"/>
       <c r="E109" s="34"/>
-      <c r="F109" s="27"/>
-      <c r="G109" s="27"/>
+      <c r="F109" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G109" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H109" s="26"/>
       <c r="I109" s="26"/>
       <c r="J109" s="26"/>
@@ -7344,8 +7755,12 @@
       <c r="C110" s="34"/>
       <c r="D110" s="34"/>
       <c r="E110" s="34"/>
-      <c r="F110" s="27"/>
-      <c r="G110" s="27"/>
+      <c r="F110" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G110" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H110" s="26"/>
       <c r="I110" s="26"/>
       <c r="J110" s="26"/>
@@ -7362,8 +7777,12 @@
       <c r="C111" s="34"/>
       <c r="D111" s="34"/>
       <c r="E111" s="34"/>
-      <c r="F111" s="27"/>
-      <c r="G111" s="27"/>
+      <c r="F111" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G111" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H111" s="26"/>
       <c r="I111" s="26"/>
       <c r="J111" s="26"/>
@@ -7380,8 +7799,12 @@
       <c r="C112" s="34"/>
       <c r="D112" s="34"/>
       <c r="E112" s="34"/>
-      <c r="F112" s="27"/>
-      <c r="G112" s="27"/>
+      <c r="F112" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G112" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H112" s="26"/>
       <c r="I112" s="26"/>
       <c r="J112" s="26"/>
@@ -7398,8 +7821,12 @@
       <c r="C113" s="34"/>
       <c r="D113" s="34"/>
       <c r="E113" s="34"/>
-      <c r="F113" s="27"/>
-      <c r="G113" s="27"/>
+      <c r="F113" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G113" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H113" s="26"/>
       <c r="I113" s="26"/>
       <c r="J113" s="26"/>
@@ -7416,8 +7843,12 @@
       <c r="C114" s="34"/>
       <c r="D114" s="34"/>
       <c r="E114" s="34"/>
-      <c r="F114" s="27"/>
-      <c r="G114" s="27"/>
+      <c r="F114" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G114" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H114" s="26"/>
       <c r="I114" s="26"/>
       <c r="J114" s="26"/>
@@ -7434,8 +7865,12 @@
       <c r="C115" s="34"/>
       <c r="D115" s="34"/>
       <c r="E115" s="34"/>
-      <c r="F115" s="27"/>
-      <c r="G115" s="27"/>
+      <c r="F115" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G115" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H115" s="26"/>
       <c r="I115" s="26"/>
       <c r="J115" s="26"/>
@@ -7452,8 +7887,12 @@
       <c r="C116" s="34"/>
       <c r="D116" s="34"/>
       <c r="E116" s="34"/>
-      <c r="F116" s="27"/>
-      <c r="G116" s="27"/>
+      <c r="F116" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G116" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H116" s="26"/>
       <c r="I116" s="26"/>
       <c r="J116" s="26"/>
@@ -7470,8 +7909,12 @@
       <c r="C117" s="34"/>
       <c r="D117" s="34"/>
       <c r="E117" s="34"/>
-      <c r="F117" s="27"/>
-      <c r="G117" s="27"/>
+      <c r="F117" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G117" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H117" s="26"/>
       <c r="I117" s="26"/>
       <c r="J117" s="26"/>
@@ -7488,8 +7931,12 @@
       <c r="C118" s="34"/>
       <c r="D118" s="34"/>
       <c r="E118" s="34"/>
-      <c r="F118" s="27"/>
-      <c r="G118" s="27"/>
+      <c r="F118" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G118" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H118" s="26"/>
       <c r="I118" s="26"/>
       <c r="J118" s="26"/>
@@ -7506,8 +7953,12 @@
       <c r="C119" s="34"/>
       <c r="D119" s="34"/>
       <c r="E119" s="34"/>
-      <c r="F119" s="27"/>
-      <c r="G119" s="27"/>
+      <c r="F119" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G119" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H119" s="26"/>
       <c r="I119" s="26"/>
       <c r="J119" s="26"/>
@@ -7524,8 +7975,12 @@
       <c r="C120" s="34"/>
       <c r="D120" s="34"/>
       <c r="E120" s="34"/>
-      <c r="F120" s="27"/>
-      <c r="G120" s="27"/>
+      <c r="F120" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G120" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H120" s="26"/>
       <c r="I120" s="26"/>
       <c r="J120" s="26"/>
@@ -7542,8 +7997,12 @@
       <c r="C121" s="34"/>
       <c r="D121" s="34"/>
       <c r="E121" s="34"/>
-      <c r="F121" s="27"/>
-      <c r="G121" s="27"/>
+      <c r="F121" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G121" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H121" s="26"/>
       <c r="I121" s="26"/>
       <c r="J121" s="26"/>
@@ -7560,8 +8019,12 @@
       <c r="C122" s="34"/>
       <c r="D122" s="34"/>
       <c r="E122" s="34"/>
-      <c r="F122" s="27"/>
-      <c r="G122" s="27"/>
+      <c r="F122" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G122" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H122" s="26"/>
       <c r="I122" s="26"/>
       <c r="J122" s="26"/>
@@ -7578,8 +8041,12 @@
       <c r="C123" s="34"/>
       <c r="D123" s="34"/>
       <c r="E123" s="34"/>
-      <c r="F123" s="27"/>
-      <c r="G123" s="27"/>
+      <c r="F123" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G123" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H123" s="26"/>
       <c r="I123" s="26"/>
       <c r="J123" s="26"/>
@@ -7596,8 +8063,12 @@
       <c r="C124" s="34"/>
       <c r="D124" s="34"/>
       <c r="E124" s="34"/>
-      <c r="F124" s="27"/>
-      <c r="G124" s="27"/>
+      <c r="F124" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G124" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H124" s="26"/>
       <c r="I124" s="26"/>
       <c r="J124" s="26"/>
@@ -7614,8 +8085,12 @@
       <c r="C125" s="34"/>
       <c r="D125" s="34"/>
       <c r="E125" s="34"/>
-      <c r="F125" s="27"/>
-      <c r="G125" s="27"/>
+      <c r="F125" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G125" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H125" s="26"/>
       <c r="I125" s="26"/>
       <c r="J125" s="26"/>
@@ -7632,8 +8107,12 @@
       <c r="C126" s="34"/>
       <c r="D126" s="34"/>
       <c r="E126" s="34"/>
-      <c r="F126" s="27"/>
-      <c r="G126" s="27"/>
+      <c r="F126" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G126" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H126" s="26"/>
       <c r="I126" s="26"/>
       <c r="J126" s="26"/>
@@ -7650,8 +8129,12 @@
       <c r="C127" s="34"/>
       <c r="D127" s="34"/>
       <c r="E127" s="34"/>
-      <c r="F127" s="27"/>
-      <c r="G127" s="27"/>
+      <c r="F127" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G127" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H127" s="26"/>
       <c r="I127" s="26"/>
       <c r="J127" s="26"/>
@@ -7668,8 +8151,12 @@
       <c r="C128" s="34"/>
       <c r="D128" s="34"/>
       <c r="E128" s="34"/>
-      <c r="F128" s="27"/>
-      <c r="G128" s="27"/>
+      <c r="F128" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G128" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H128" s="26"/>
       <c r="I128" s="26"/>
       <c r="J128" s="26"/>
@@ -7686,8 +8173,12 @@
       <c r="C129" s="34"/>
       <c r="D129" s="34"/>
       <c r="E129" s="34"/>
-      <c r="F129" s="27"/>
-      <c r="G129" s="27"/>
+      <c r="F129" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G129" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H129" s="26"/>
       <c r="I129" s="26"/>
       <c r="J129" s="26"/>
@@ -7704,8 +8195,12 @@
       <c r="C130" s="34"/>
       <c r="D130" s="34"/>
       <c r="E130" s="34"/>
-      <c r="F130" s="27"/>
-      <c r="G130" s="27"/>
+      <c r="F130" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G130" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H130" s="26"/>
       <c r="I130" s="26"/>
       <c r="J130" s="26"/>
@@ -7722,8 +8217,12 @@
       <c r="C131" s="34"/>
       <c r="D131" s="34"/>
       <c r="E131" s="34"/>
-      <c r="F131" s="27"/>
-      <c r="G131" s="27"/>
+      <c r="F131" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G131" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H131" s="26"/>
       <c r="I131" s="26"/>
       <c r="J131" s="26"/>
@@ -7740,8 +8239,12 @@
       <c r="C132" s="34"/>
       <c r="D132" s="34"/>
       <c r="E132" s="34"/>
-      <c r="F132" s="27"/>
-      <c r="G132" s="27"/>
+      <c r="F132" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G132" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H132" s="26"/>
       <c r="I132" s="26"/>
       <c r="J132" s="26"/>
@@ -7758,8 +8261,12 @@
       <c r="C133" s="34"/>
       <c r="D133" s="34"/>
       <c r="E133" s="34"/>
-      <c r="F133" s="27"/>
-      <c r="G133" s="27"/>
+      <c r="F133" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G133" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H133" s="26"/>
       <c r="I133" s="26"/>
       <c r="J133" s="26"/>
@@ -7776,8 +8283,12 @@
       <c r="C134" s="34"/>
       <c r="D134" s="34"/>
       <c r="E134" s="34"/>
-      <c r="F134" s="27"/>
-      <c r="G134" s="27"/>
+      <c r="F134" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G134" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H134" s="26"/>
       <c r="I134" s="26"/>
       <c r="J134" s="26"/>
@@ -7794,8 +8305,12 @@
       <c r="C135" s="34"/>
       <c r="D135" s="34"/>
       <c r="E135" s="34"/>
-      <c r="F135" s="27"/>
-      <c r="G135" s="27"/>
+      <c r="F135" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G135" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H135" s="26"/>
       <c r="I135" s="26"/>
       <c r="J135" s="26"/>
@@ -7812,8 +8327,12 @@
       <c r="C136" s="34"/>
       <c r="D136" s="34"/>
       <c r="E136" s="34"/>
-      <c r="F136" s="27"/>
-      <c r="G136" s="27"/>
+      <c r="F136" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G136" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H136" s="26"/>
       <c r="I136" s="26"/>
       <c r="J136" s="26"/>
@@ -7830,8 +8349,12 @@
       <c r="C137" s="34"/>
       <c r="D137" s="34"/>
       <c r="E137" s="34"/>
-      <c r="F137" s="27"/>
-      <c r="G137" s="27"/>
+      <c r="F137" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G137" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H137" s="26"/>
       <c r="I137" s="26"/>
       <c r="J137" s="26"/>
@@ -7848,8 +8371,12 @@
       <c r="C138" s="34"/>
       <c r="D138" s="34"/>
       <c r="E138" s="34"/>
-      <c r="F138" s="27"/>
-      <c r="G138" s="27"/>
+      <c r="F138" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G138" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H138" s="26"/>
       <c r="I138" s="26"/>
       <c r="J138" s="26"/>
@@ -7866,8 +8393,12 @@
       <c r="C139" s="34"/>
       <c r="D139" s="34"/>
       <c r="E139" s="34"/>
-      <c r="F139" s="27"/>
-      <c r="G139" s="27"/>
+      <c r="F139" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G139" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H139" s="26"/>
       <c r="I139" s="26"/>
       <c r="J139" s="26"/>
@@ -7884,8 +8415,12 @@
       <c r="C140" s="34"/>
       <c r="D140" s="34"/>
       <c r="E140" s="34"/>
-      <c r="F140" s="27"/>
-      <c r="G140" s="27"/>
+      <c r="F140" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G140" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H140" s="26"/>
       <c r="I140" s="26"/>
       <c r="J140" s="26"/>
@@ -7902,8 +8437,12 @@
       <c r="C141" s="34"/>
       <c r="D141" s="34"/>
       <c r="E141" s="34"/>
-      <c r="F141" s="27"/>
-      <c r="G141" s="27"/>
+      <c r="F141" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G141" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H141" s="26"/>
       <c r="I141" s="26"/>
       <c r="J141" s="26"/>
@@ -7920,8 +8459,12 @@
       <c r="C142" s="34"/>
       <c r="D142" s="34"/>
       <c r="E142" s="34"/>
-      <c r="F142" s="27"/>
-      <c r="G142" s="27"/>
+      <c r="F142" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G142" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H142" s="26"/>
       <c r="I142" s="26"/>
       <c r="J142" s="26"/>
@@ -7938,8 +8481,12 @@
       <c r="C143" s="34"/>
       <c r="D143" s="34"/>
       <c r="E143" s="34"/>
-      <c r="F143" s="27"/>
-      <c r="G143" s="27"/>
+      <c r="F143" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G143" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H143" s="26"/>
       <c r="I143" s="26"/>
       <c r="J143" s="26"/>
@@ -7956,8 +8503,12 @@
       <c r="C144" s="34"/>
       <c r="D144" s="34"/>
       <c r="E144" s="34"/>
-      <c r="F144" s="27"/>
-      <c r="G144" s="27"/>
+      <c r="F144" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G144" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H144" s="26"/>
       <c r="I144" s="26"/>
       <c r="J144" s="26"/>
@@ -7974,8 +8525,12 @@
       <c r="C145" s="34"/>
       <c r="D145" s="34"/>
       <c r="E145" s="34"/>
-      <c r="F145" s="27"/>
-      <c r="G145" s="27"/>
+      <c r="F145" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G145" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H145" s="26"/>
       <c r="I145" s="26"/>
       <c r="J145" s="26"/>
@@ -7992,8 +8547,12 @@
       <c r="C146" s="34"/>
       <c r="D146" s="34"/>
       <c r="E146" s="34"/>
-      <c r="F146" s="27"/>
-      <c r="G146" s="27"/>
+      <c r="F146" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G146" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H146" s="26"/>
       <c r="I146" s="26"/>
       <c r="J146" s="26"/>
@@ -8010,8 +8569,12 @@
       <c r="C147" s="34"/>
       <c r="D147" s="34"/>
       <c r="E147" s="34"/>
-      <c r="F147" s="27"/>
-      <c r="G147" s="27"/>
+      <c r="F147" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G147" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H147" s="26"/>
       <c r="I147" s="26"/>
       <c r="J147" s="26"/>
@@ -8028,8 +8591,12 @@
       <c r="C148" s="34"/>
       <c r="D148" s="34"/>
       <c r="E148" s="34"/>
-      <c r="F148" s="27"/>
-      <c r="G148" s="27"/>
+      <c r="F148" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G148" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H148" s="26"/>
       <c r="I148" s="26"/>
       <c r="J148" s="26"/>
@@ -8046,8 +8613,12 @@
       <c r="C149" s="34"/>
       <c r="D149" s="34"/>
       <c r="E149" s="34"/>
-      <c r="F149" s="27"/>
-      <c r="G149" s="27"/>
+      <c r="F149" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G149" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H149" s="26"/>
       <c r="I149" s="26"/>
       <c r="J149" s="26"/>
@@ -8064,8 +8635,12 @@
       <c r="C150" s="34"/>
       <c r="D150" s="34"/>
       <c r="E150" s="34"/>
-      <c r="F150" s="27"/>
-      <c r="G150" s="27"/>
+      <c r="F150" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G150" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H150" s="26"/>
       <c r="I150" s="26"/>
       <c r="J150" s="26"/>
@@ -8082,8 +8657,12 @@
       <c r="C151" s="34"/>
       <c r="D151" s="34"/>
       <c r="E151" s="34"/>
-      <c r="F151" s="27"/>
-      <c r="G151" s="27"/>
+      <c r="F151" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G151" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H151" s="26"/>
       <c r="I151" s="26"/>
       <c r="J151" s="26"/>
@@ -8100,8 +8679,12 @@
       <c r="C152" s="34"/>
       <c r="D152" s="34"/>
       <c r="E152" s="34"/>
-      <c r="F152" s="27"/>
-      <c r="G152" s="27"/>
+      <c r="F152" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G152" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H152" s="26"/>
       <c r="I152" s="26"/>
       <c r="J152" s="26"/>
@@ -8130,8 +8713,12 @@
       <c r="C153" s="34"/>
       <c r="D153" s="34"/>
       <c r="E153" s="34"/>
-      <c r="F153" s="27"/>
-      <c r="G153" s="27"/>
+      <c r="F153" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G153" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H153" s="26"/>
       <c r="I153" s="26"/>
       <c r="J153" s="26"/>
@@ -8160,8 +8747,12 @@
       <c r="C154" s="34"/>
       <c r="D154" s="34"/>
       <c r="E154" s="34"/>
-      <c r="F154" s="27"/>
-      <c r="G154" s="27"/>
+      <c r="F154" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G154" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H154" s="26"/>
       <c r="I154" s="26"/>
       <c r="J154" s="26"/>
@@ -8190,8 +8781,12 @@
       <c r="C155" s="34"/>
       <c r="D155" s="34"/>
       <c r="E155" s="34"/>
-      <c r="F155" s="27"/>
-      <c r="G155" s="27"/>
+      <c r="F155" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G155" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H155" s="26"/>
       <c r="I155" s="26"/>
       <c r="J155" s="26"/>
@@ -8220,8 +8815,12 @@
       <c r="C156" s="34"/>
       <c r="D156" s="34"/>
       <c r="E156" s="34"/>
-      <c r="F156" s="27"/>
-      <c r="G156" s="27"/>
+      <c r="F156" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G156" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H156" s="26"/>
       <c r="I156" s="26"/>
       <c r="J156" s="26"/>
@@ -8250,8 +8849,12 @@
       <c r="C157" s="34"/>
       <c r="D157" s="34"/>
       <c r="E157" s="34"/>
-      <c r="F157" s="27"/>
-      <c r="G157" s="27"/>
+      <c r="F157" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G157" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H157" s="26"/>
       <c r="I157" s="26"/>
       <c r="J157" s="26"/>
@@ -8268,8 +8871,12 @@
       <c r="C158" s="34"/>
       <c r="D158" s="34"/>
       <c r="E158" s="34"/>
-      <c r="F158" s="27"/>
-      <c r="G158" s="27"/>
+      <c r="F158" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G158" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H158" s="26"/>
       <c r="I158" s="26"/>
       <c r="J158" s="26"/>
@@ -8298,8 +8905,12 @@
       <c r="C159" s="34"/>
       <c r="D159" s="34"/>
       <c r="E159" s="34"/>
-      <c r="F159" s="27"/>
-      <c r="G159" s="27"/>
+      <c r="F159" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G159" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H159" s="26"/>
       <c r="I159" s="26"/>
       <c r="J159" s="26"/>
@@ -8328,8 +8939,12 @@
       <c r="C160" s="34"/>
       <c r="D160" s="34"/>
       <c r="E160" s="34"/>
-      <c r="F160" s="27"/>
-      <c r="G160" s="27"/>
+      <c r="F160" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G160" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H160" s="26"/>
       <c r="I160" s="26"/>
       <c r="J160" s="26"/>
@@ -8358,8 +8973,12 @@
       <c r="C161" s="34"/>
       <c r="D161" s="34"/>
       <c r="E161" s="34"/>
-      <c r="F161" s="27"/>
-      <c r="G161" s="27"/>
+      <c r="F161" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G161" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H161" s="26"/>
       <c r="I161" s="26"/>
       <c r="J161" s="26"/>
@@ -8388,8 +9007,12 @@
       <c r="C162" s="34"/>
       <c r="D162" s="34"/>
       <c r="E162" s="34"/>
-      <c r="F162" s="27"/>
-      <c r="G162" s="27"/>
+      <c r="F162" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G162" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H162" s="26"/>
       <c r="I162" s="26"/>
       <c r="J162" s="26"/>
@@ -8418,8 +9041,12 @@
       <c r="C163" s="34"/>
       <c r="D163" s="34"/>
       <c r="E163" s="34"/>
-      <c r="F163" s="27"/>
-      <c r="G163" s="27"/>
+      <c r="F163" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G163" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H163" s="26"/>
       <c r="I163" s="26"/>
       <c r="J163" s="26"/>
@@ -8448,8 +9075,12 @@
       <c r="C164" s="34"/>
       <c r="D164" s="34"/>
       <c r="E164" s="34"/>
-      <c r="F164" s="27"/>
-      <c r="G164" s="27"/>
+      <c r="F164" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G164" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H164" s="26"/>
       <c r="I164" s="26"/>
       <c r="J164" s="26"/>
@@ -8478,8 +9109,12 @@
       <c r="C165" s="34"/>
       <c r="D165" s="34"/>
       <c r="E165" s="34"/>
-      <c r="F165" s="27"/>
-      <c r="G165" s="27"/>
+      <c r="F165" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G165" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H165" s="26"/>
       <c r="I165" s="26"/>
       <c r="J165" s="26"/>
@@ -8508,8 +9143,12 @@
       <c r="C166" s="34"/>
       <c r="D166" s="34"/>
       <c r="E166" s="34"/>
-      <c r="F166" s="27"/>
-      <c r="G166" s="27"/>
+      <c r="F166" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G166" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H166" s="26"/>
       <c r="I166" s="26"/>
       <c r="J166" s="26"/>
@@ -8538,8 +9177,12 @@
       <c r="C167" s="34"/>
       <c r="D167" s="34"/>
       <c r="E167" s="34"/>
-      <c r="F167" s="27"/>
-      <c r="G167" s="27"/>
+      <c r="F167" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G167" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H167" s="26"/>
       <c r="I167" s="26"/>
       <c r="J167" s="26"/>
@@ -8568,8 +9211,12 @@
       <c r="C168" s="34"/>
       <c r="D168" s="34"/>
       <c r="E168" s="34"/>
-      <c r="F168" s="27"/>
-      <c r="G168" s="27"/>
+      <c r="F168" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G168" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H168" s="26"/>
       <c r="I168" s="26"/>
       <c r="J168" s="26"/>
@@ -8598,8 +9245,12 @@
       <c r="C169" s="34"/>
       <c r="D169" s="34"/>
       <c r="E169" s="34"/>
-      <c r="F169" s="27"/>
-      <c r="G169" s="27"/>
+      <c r="F169" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G169" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H169" s="26"/>
       <c r="I169" s="26"/>
       <c r="J169" s="26"/>
@@ -8628,8 +9279,12 @@
       <c r="C170" s="34"/>
       <c r="D170" s="34"/>
       <c r="E170" s="34"/>
-      <c r="F170" s="27"/>
-      <c r="G170" s="27"/>
+      <c r="F170" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G170" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H170" s="26"/>
       <c r="I170" s="26"/>
       <c r="J170" s="26"/>
@@ -8658,8 +9313,12 @@
       <c r="C171" s="34"/>
       <c r="D171" s="34"/>
       <c r="E171" s="34"/>
-      <c r="F171" s="27"/>
-      <c r="G171" s="27"/>
+      <c r="F171" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G171" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H171" s="26"/>
       <c r="I171" s="26"/>
       <c r="J171" s="26"/>
@@ -8688,8 +9347,12 @@
       <c r="C172" s="34"/>
       <c r="D172" s="34"/>
       <c r="E172" s="34"/>
-      <c r="F172" s="27"/>
-      <c r="G172" s="27"/>
+      <c r="F172" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G172" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H172" s="26"/>
       <c r="I172" s="26"/>
       <c r="J172" s="26"/>
@@ -8718,8 +9381,12 @@
       <c r="C173" s="34"/>
       <c r="D173" s="34"/>
       <c r="E173" s="34"/>
-      <c r="F173" s="27"/>
-      <c r="G173" s="27"/>
+      <c r="F173" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G173" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H173" s="26"/>
       <c r="I173" s="26"/>
       <c r="J173" s="26"/>
@@ -8748,8 +9415,12 @@
       <c r="C174" s="34"/>
       <c r="D174" s="34"/>
       <c r="E174" s="34"/>
-      <c r="F174" s="27"/>
-      <c r="G174" s="27"/>
+      <c r="F174" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G174" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H174" s="26"/>
       <c r="I174" s="26"/>
       <c r="J174" s="26"/>
@@ -8778,8 +9449,12 @@
       <c r="C175" s="34"/>
       <c r="D175" s="34"/>
       <c r="E175" s="34"/>
-      <c r="F175" s="27"/>
-      <c r="G175" s="27"/>
+      <c r="F175" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G175" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H175" s="26"/>
       <c r="I175" s="26"/>
       <c r="J175" s="26"/>
@@ -8808,8 +9483,12 @@
       <c r="C176" s="34"/>
       <c r="D176" s="34"/>
       <c r="E176" s="34"/>
-      <c r="F176" s="27"/>
-      <c r="G176" s="27"/>
+      <c r="F176" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G176" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H176" s="26"/>
       <c r="I176" s="26"/>
       <c r="J176" s="26"/>
@@ -8838,8 +9517,12 @@
       <c r="C177" s="34"/>
       <c r="D177" s="34"/>
       <c r="E177" s="34"/>
-      <c r="F177" s="27"/>
-      <c r="G177" s="27"/>
+      <c r="F177" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G177" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H177" s="26"/>
       <c r="I177" s="26"/>
       <c r="J177" s="26"/>
@@ -8868,8 +9551,12 @@
       <c r="C178" s="34"/>
       <c r="D178" s="34"/>
       <c r="E178" s="34"/>
-      <c r="F178" s="27"/>
-      <c r="G178" s="27"/>
+      <c r="F178" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G178" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H178" s="26"/>
       <c r="I178" s="26"/>
       <c r="J178" s="26"/>
@@ -8898,8 +9585,12 @@
       <c r="C179" s="34"/>
       <c r="D179" s="34"/>
       <c r="E179" s="34"/>
-      <c r="F179" s="27"/>
-      <c r="G179" s="27"/>
+      <c r="F179" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G179" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H179" s="26"/>
       <c r="I179" s="26"/>
       <c r="J179" s="26"/>
@@ -8928,8 +9619,12 @@
       <c r="C180" s="34"/>
       <c r="D180" s="34"/>
       <c r="E180" s="34"/>
-      <c r="F180" s="27"/>
-      <c r="G180" s="27"/>
+      <c r="F180" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G180" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H180" s="26"/>
       <c r="I180" s="26"/>
       <c r="J180" s="26"/>
@@ -8958,8 +9653,12 @@
       <c r="C181" s="34"/>
       <c r="D181" s="34"/>
       <c r="E181" s="34"/>
-      <c r="F181" s="27"/>
-      <c r="G181" s="27"/>
+      <c r="F181" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G181" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H181" s="26"/>
       <c r="I181" s="26"/>
       <c r="J181" s="26"/>
@@ -8988,8 +9687,12 @@
       <c r="C182" s="34"/>
       <c r="D182" s="34"/>
       <c r="E182" s="34"/>
-      <c r="F182" s="27"/>
-      <c r="G182" s="27"/>
+      <c r="F182" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G182" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H182" s="26"/>
       <c r="I182" s="26"/>
       <c r="J182" s="26"/>
@@ -9018,8 +9721,12 @@
       <c r="C183" s="34"/>
       <c r="D183" s="34"/>
       <c r="E183" s="34"/>
-      <c r="F183" s="27"/>
-      <c r="G183" s="27"/>
+      <c r="F183" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G183" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H183" s="26"/>
       <c r="I183" s="26"/>
       <c r="J183" s="26"/>
@@ -9048,8 +9755,12 @@
       <c r="C184" s="34"/>
       <c r="D184" s="34"/>
       <c r="E184" s="34"/>
-      <c r="F184" s="27"/>
-      <c r="G184" s="27"/>
+      <c r="F184" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G184" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H184" s="26"/>
       <c r="I184" s="26"/>
       <c r="J184" s="26"/>
@@ -9078,8 +9789,12 @@
       <c r="C185" s="34"/>
       <c r="D185" s="34"/>
       <c r="E185" s="34"/>
-      <c r="F185" s="27"/>
-      <c r="G185" s="27"/>
+      <c r="F185" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G185" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H185" s="26"/>
       <c r="I185" s="26"/>
       <c r="J185" s="26"/>
@@ -9108,8 +9823,12 @@
       <c r="C186" s="34"/>
       <c r="D186" s="34"/>
       <c r="E186" s="34"/>
-      <c r="F186" s="27"/>
-      <c r="G186" s="27"/>
+      <c r="F186" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G186" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H186" s="26"/>
       <c r="I186" s="26"/>
       <c r="J186" s="26"/>
@@ -9138,8 +9857,12 @@
       <c r="C187" s="34"/>
       <c r="D187" s="34"/>
       <c r="E187" s="34"/>
-      <c r="F187" s="27"/>
-      <c r="G187" s="27"/>
+      <c r="F187" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G187" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H187" s="26"/>
       <c r="I187" s="26"/>
       <c r="J187" s="26"/>
@@ -9168,8 +9891,12 @@
       <c r="C188" s="34"/>
       <c r="D188" s="34"/>
       <c r="E188" s="34"/>
-      <c r="F188" s="27"/>
-      <c r="G188" s="27"/>
+      <c r="F188" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G188" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H188" s="26"/>
       <c r="I188" s="26"/>
       <c r="J188" s="26"/>
@@ -9198,8 +9925,12 @@
       <c r="C189" s="34"/>
       <c r="D189" s="34"/>
       <c r="E189" s="34"/>
-      <c r="F189" s="27"/>
-      <c r="G189" s="27"/>
+      <c r="F189" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G189" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H189" s="26"/>
       <c r="I189" s="26"/>
       <c r="J189" s="26"/>
@@ -9228,8 +9959,12 @@
       <c r="C190" s="34"/>
       <c r="D190" s="34"/>
       <c r="E190" s="34"/>
-      <c r="F190" s="27"/>
-      <c r="G190" s="27"/>
+      <c r="F190" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G190" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H190" s="26"/>
       <c r="I190" s="26"/>
       <c r="J190" s="26"/>
@@ -9258,8 +9993,12 @@
       <c r="C191" s="34"/>
       <c r="D191" s="34"/>
       <c r="E191" s="34"/>
-      <c r="F191" s="27"/>
-      <c r="G191" s="27"/>
+      <c r="F191" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G191" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H191" s="26"/>
       <c r="I191" s="26"/>
       <c r="J191" s="26"/>
@@ -9288,8 +10027,12 @@
       <c r="C192" s="34"/>
       <c r="D192" s="34"/>
       <c r="E192" s="34"/>
-      <c r="F192" s="27"/>
-      <c r="G192" s="27"/>
+      <c r="F192" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G192" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H192" s="26"/>
       <c r="I192" s="26"/>
       <c r="J192" s="26"/>
@@ -9318,8 +10061,12 @@
       <c r="C193" s="34"/>
       <c r="D193" s="34"/>
       <c r="E193" s="34"/>
-      <c r="F193" s="27"/>
-      <c r="G193" s="27"/>
+      <c r="F193" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G193" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H193" s="26"/>
       <c r="I193" s="26"/>
       <c r="J193" s="26"/>
@@ -9348,8 +10095,12 @@
       <c r="C194" s="34"/>
       <c r="D194" s="34"/>
       <c r="E194" s="34"/>
-      <c r="F194" s="27"/>
-      <c r="G194" s="27"/>
+      <c r="F194" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G194" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H194" s="26"/>
       <c r="I194" s="26"/>
       <c r="J194" s="26"/>
@@ -9378,8 +10129,12 @@
       <c r="C195" s="34"/>
       <c r="D195" s="34"/>
       <c r="E195" s="34"/>
-      <c r="F195" s="27"/>
-      <c r="G195" s="27"/>
+      <c r="F195" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G195" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H195" s="26"/>
       <c r="I195" s="26"/>
       <c r="J195" s="26"/>
@@ -9408,8 +10163,12 @@
       <c r="C196" s="34"/>
       <c r="D196" s="34"/>
       <c r="E196" s="34"/>
-      <c r="F196" s="27"/>
-      <c r="G196" s="27"/>
+      <c r="F196" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G196" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H196" s="26"/>
       <c r="I196" s="26"/>
       <c r="J196" s="26"/>
@@ -9438,8 +10197,12 @@
       <c r="C197" s="34"/>
       <c r="D197" s="34"/>
       <c r="E197" s="34"/>
-      <c r="F197" s="27"/>
-      <c r="G197" s="27"/>
+      <c r="F197" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G197" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H197" s="26"/>
       <c r="I197" s="26"/>
       <c r="J197" s="26"/>
@@ -9468,8 +10231,12 @@
       <c r="C198" s="34"/>
       <c r="D198" s="34"/>
       <c r="E198" s="34"/>
-      <c r="F198" s="27"/>
-      <c r="G198" s="27"/>
+      <c r="F198" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G198" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H198" s="26"/>
       <c r="I198" s="26"/>
       <c r="J198" s="26"/>
@@ -9498,8 +10265,12 @@
       <c r="C199" s="34"/>
       <c r="D199" s="34"/>
       <c r="E199" s="34"/>
-      <c r="F199" s="27"/>
-      <c r="G199" s="27"/>
+      <c r="F199" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G199" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H199" s="26"/>
       <c r="I199" s="26"/>
       <c r="J199" s="26"/>
@@ -9528,8 +10299,12 @@
       <c r="C200" s="34"/>
       <c r="D200" s="34"/>
       <c r="E200" s="34"/>
-      <c r="F200" s="27"/>
-      <c r="G200" s="27"/>
+      <c r="F200" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G200" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H200" s="26"/>
       <c r="I200" s="26"/>
       <c r="J200" s="26"/>
@@ -9546,8 +10321,12 @@
       <c r="C201" s="34"/>
       <c r="D201" s="34"/>
       <c r="E201" s="34"/>
-      <c r="F201" s="27"/>
-      <c r="G201" s="27"/>
+      <c r="F201" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G201" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H201" s="26"/>
       <c r="I201" s="26"/>
       <c r="J201" s="26"/>
@@ -9564,8 +10343,12 @@
       <c r="C202" s="34"/>
       <c r="D202" s="34"/>
       <c r="E202" s="34"/>
-      <c r="F202" s="27"/>
-      <c r="G202" s="27"/>
+      <c r="F202" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G202" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H202" s="26"/>
       <c r="I202" s="26"/>
       <c r="J202" s="26"/>
@@ -9582,8 +10365,12 @@
       <c r="C203" s="34"/>
       <c r="D203" s="34"/>
       <c r="E203" s="34"/>
-      <c r="F203" s="27"/>
-      <c r="G203" s="27"/>
+      <c r="F203" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G203" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H203" s="26"/>
       <c r="I203" s="26"/>
       <c r="J203" s="26"/>
@@ -9600,8 +10387,12 @@
       <c r="C204" s="34"/>
       <c r="D204" s="34"/>
       <c r="E204" s="34"/>
-      <c r="F204" s="27"/>
-      <c r="G204" s="27"/>
+      <c r="F204" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G204" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H204" s="26"/>
       <c r="I204" s="26"/>
       <c r="J204" s="26"/>
@@ -9618,8 +10409,12 @@
       <c r="C205" s="34"/>
       <c r="D205" s="34"/>
       <c r="E205" s="34"/>
-      <c r="F205" s="27"/>
-      <c r="G205" s="27"/>
+      <c r="F205" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G205" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H205" s="26"/>
       <c r="I205" s="26"/>
       <c r="J205" s="26"/>
@@ -9636,8 +10431,12 @@
       <c r="C206" s="34"/>
       <c r="D206" s="34"/>
       <c r="E206" s="34"/>
-      <c r="F206" s="27"/>
-      <c r="G206" s="27"/>
+      <c r="F206" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G206" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H206" s="26"/>
       <c r="I206" s="26"/>
       <c r="J206" s="26"/>
@@ -9654,8 +10453,12 @@
       <c r="C207" s="34"/>
       <c r="D207" s="34"/>
       <c r="E207" s="34"/>
-      <c r="F207" s="27"/>
-      <c r="G207" s="27"/>
+      <c r="F207" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G207" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H207" s="26"/>
       <c r="I207" s="26"/>
       <c r="J207" s="26"/>
@@ -9672,8 +10475,12 @@
       <c r="C208" s="34"/>
       <c r="D208" s="34"/>
       <c r="E208" s="34"/>
-      <c r="F208" s="27"/>
-      <c r="G208" s="27"/>
+      <c r="F208" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G208" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H208" s="26"/>
       <c r="I208" s="26"/>
       <c r="J208" s="26"/>
@@ -9690,8 +10497,12 @@
       <c r="C209" s="34"/>
       <c r="D209" s="34"/>
       <c r="E209" s="34"/>
-      <c r="F209" s="27"/>
-      <c r="G209" s="27"/>
+      <c r="F209" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G209" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H209" s="26"/>
       <c r="I209" s="26"/>
       <c r="J209" s="26"/>
@@ -9708,8 +10519,12 @@
       <c r="C210" s="34"/>
       <c r="D210" s="34"/>
       <c r="E210" s="34"/>
-      <c r="F210" s="27"/>
-      <c r="G210" s="27"/>
+      <c r="F210" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G210" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H210" s="26"/>
       <c r="I210" s="26"/>
       <c r="J210" s="26"/>
@@ -9726,8 +10541,12 @@
       <c r="C211" s="34"/>
       <c r="D211" s="34"/>
       <c r="E211" s="34"/>
-      <c r="F211" s="27"/>
-      <c r="G211" s="27"/>
+      <c r="F211" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G211" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H211" s="26"/>
       <c r="I211" s="26"/>
       <c r="J211" s="26"/>
@@ -9744,8 +10563,12 @@
       <c r="C212" s="34"/>
       <c r="D212" s="34"/>
       <c r="E212" s="34"/>
-      <c r="F212" s="27"/>
-      <c r="G212" s="27"/>
+      <c r="F212" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G212" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H212" s="26"/>
       <c r="I212" s="26"/>
       <c r="J212" s="26"/>
@@ -9762,8 +10585,12 @@
       <c r="C213" s="34"/>
       <c r="D213" s="34"/>
       <c r="E213" s="34"/>
-      <c r="F213" s="27"/>
-      <c r="G213" s="27"/>
+      <c r="F213" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G213" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H213" s="26"/>
       <c r="I213" s="26"/>
       <c r="J213" s="26"/>
@@ -9780,8 +10607,12 @@
       <c r="C214" s="34"/>
       <c r="D214" s="34"/>
       <c r="E214" s="34"/>
-      <c r="F214" s="27"/>
-      <c r="G214" s="27"/>
+      <c r="F214" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G214" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H214" s="26"/>
       <c r="I214" s="26"/>
       <c r="J214" s="26"/>
@@ -9798,8 +10629,12 @@
       <c r="C215" s="34"/>
       <c r="D215" s="34"/>
       <c r="E215" s="34"/>
-      <c r="F215" s="27"/>
-      <c r="G215" s="27"/>
+      <c r="F215" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G215" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H215" s="26"/>
       <c r="I215" s="26"/>
       <c r="J215" s="26"/>
@@ -9816,8 +10651,12 @@
       <c r="C216" s="34"/>
       <c r="D216" s="34"/>
       <c r="E216" s="34"/>
-      <c r="F216" s="27"/>
-      <c r="G216" s="27"/>
+      <c r="F216" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G216" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H216" s="26"/>
       <c r="I216" s="26"/>
       <c r="J216" s="26"/>
@@ -9834,8 +10673,12 @@
       <c r="C217" s="34"/>
       <c r="D217" s="34"/>
       <c r="E217" s="34"/>
-      <c r="F217" s="27"/>
-      <c r="G217" s="27"/>
+      <c r="F217" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G217" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H217" s="26"/>
       <c r="I217" s="26"/>
       <c r="J217" s="26"/>
@@ -9852,8 +10695,12 @@
       <c r="C218" s="34"/>
       <c r="D218" s="34"/>
       <c r="E218" s="34"/>
-      <c r="F218" s="27"/>
-      <c r="G218" s="27"/>
+      <c r="F218" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G218" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H218" s="26"/>
       <c r="I218" s="26"/>
       <c r="J218" s="26"/>
@@ -9870,8 +10717,12 @@
       <c r="C219" s="34"/>
       <c r="D219" s="34"/>
       <c r="E219" s="34"/>
-      <c r="F219" s="27"/>
-      <c r="G219" s="27"/>
+      <c r="F219" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G219" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H219" s="26"/>
       <c r="I219" s="26"/>
       <c r="J219" s="26"/>
@@ -9888,8 +10739,12 @@
       <c r="C220" s="34"/>
       <c r="D220" s="34"/>
       <c r="E220" s="34"/>
-      <c r="F220" s="27"/>
-      <c r="G220" s="27"/>
+      <c r="F220" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G220" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H220" s="26"/>
       <c r="I220" s="26"/>
       <c r="J220" s="26"/>
@@ -9918,8 +10773,12 @@
       <c r="C221" s="34"/>
       <c r="D221" s="34"/>
       <c r="E221" s="34"/>
-      <c r="F221" s="27"/>
-      <c r="G221" s="27"/>
+      <c r="F221" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G221" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H221" s="26"/>
       <c r="I221" s="26"/>
       <c r="J221" s="26"/>
@@ -9948,8 +10807,12 @@
       <c r="C222" s="34"/>
       <c r="D222" s="34"/>
       <c r="E222" s="34"/>
-      <c r="F222" s="27"/>
-      <c r="G222" s="27"/>
+      <c r="F222" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G222" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H222" s="26"/>
       <c r="I222" s="26"/>
       <c r="J222" s="26"/>
@@ -9978,8 +10841,12 @@
       <c r="C223" s="34"/>
       <c r="D223" s="34"/>
       <c r="E223" s="34"/>
-      <c r="F223" s="27"/>
-      <c r="G223" s="27"/>
+      <c r="F223" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G223" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H223" s="26"/>
       <c r="I223" s="26"/>
       <c r="J223" s="26"/>
@@ -10008,8 +10875,12 @@
       <c r="C224" s="34"/>
       <c r="D224" s="34"/>
       <c r="E224" s="34"/>
-      <c r="F224" s="27"/>
-      <c r="G224" s="27"/>
+      <c r="F224" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G224" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H224" s="26"/>
       <c r="I224" s="26"/>
       <c r="J224" s="26"/>
@@ -10034,7 +10905,7 @@
     </row>
     <row r="225" s="25" customFormat="true" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A225" s="24" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B225" s="24"/>
       <c r="C225" s="24"/>
@@ -10058,8 +10929,12 @@
       <c r="C226" s="34"/>
       <c r="D226" s="34"/>
       <c r="E226" s="34"/>
-      <c r="F226" s="27"/>
-      <c r="G226" s="27"/>
+      <c r="F226" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G226" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H226" s="26"/>
       <c r="I226" s="26"/>
       <c r="J226" s="26"/>
@@ -10088,8 +10963,12 @@
       <c r="C227" s="34"/>
       <c r="D227" s="34"/>
       <c r="E227" s="34"/>
-      <c r="F227" s="27"/>
-      <c r="G227" s="27"/>
+      <c r="F227" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G227" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H227" s="26"/>
       <c r="I227" s="26"/>
       <c r="J227" s="26"/>
@@ -10106,8 +10985,12 @@
       <c r="C228" s="34"/>
       <c r="D228" s="34"/>
       <c r="E228" s="34"/>
-      <c r="F228" s="27"/>
-      <c r="G228" s="27"/>
+      <c r="F228" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G228" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H228" s="26"/>
       <c r="I228" s="26"/>
       <c r="J228" s="26"/>
@@ -10124,8 +11007,12 @@
       <c r="C229" s="34"/>
       <c r="D229" s="34"/>
       <c r="E229" s="34"/>
-      <c r="F229" s="27"/>
-      <c r="G229" s="27"/>
+      <c r="F229" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G229" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H229" s="26"/>
       <c r="I229" s="26"/>
       <c r="J229" s="26"/>
@@ -10142,8 +11029,12 @@
       <c r="C230" s="34"/>
       <c r="D230" s="34"/>
       <c r="E230" s="34"/>
-      <c r="F230" s="27"/>
-      <c r="G230" s="27"/>
+      <c r="F230" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G230" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H230" s="26"/>
       <c r="I230" s="26"/>
       <c r="J230" s="26"/>
@@ -10160,8 +11051,12 @@
       <c r="C231" s="34"/>
       <c r="D231" s="34"/>
       <c r="E231" s="34"/>
-      <c r="F231" s="27"/>
-      <c r="G231" s="27"/>
+      <c r="F231" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G231" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H231" s="26"/>
       <c r="I231" s="26"/>
       <c r="J231" s="26"/>
@@ -10178,8 +11073,12 @@
       <c r="C232" s="34"/>
       <c r="D232" s="34"/>
       <c r="E232" s="34"/>
-      <c r="F232" s="27"/>
-      <c r="G232" s="27"/>
+      <c r="F232" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G232" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H232" s="26"/>
       <c r="I232" s="26"/>
       <c r="J232" s="26"/>
@@ -10196,8 +11095,12 @@
       <c r="C233" s="34"/>
       <c r="D233" s="34"/>
       <c r="E233" s="34"/>
-      <c r="F233" s="27"/>
-      <c r="G233" s="27"/>
+      <c r="F233" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G233" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H233" s="26"/>
       <c r="I233" s="26"/>
       <c r="J233" s="26"/>
@@ -10214,8 +11117,12 @@
       <c r="C234" s="34"/>
       <c r="D234" s="34"/>
       <c r="E234" s="34"/>
-      <c r="F234" s="27"/>
-      <c r="G234" s="27"/>
+      <c r="F234" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G234" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H234" s="26"/>
       <c r="I234" s="26"/>
       <c r="J234" s="26"/>
@@ -10232,8 +11139,12 @@
       <c r="C235" s="34"/>
       <c r="D235" s="34"/>
       <c r="E235" s="34"/>
-      <c r="F235" s="27"/>
-      <c r="G235" s="27"/>
+      <c r="F235" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G235" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H235" s="26"/>
       <c r="I235" s="26"/>
       <c r="J235" s="26"/>
@@ -10250,8 +11161,12 @@
       <c r="C236" s="34"/>
       <c r="D236" s="34"/>
       <c r="E236" s="34"/>
-      <c r="F236" s="27"/>
-      <c r="G236" s="27"/>
+      <c r="F236" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G236" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H236" s="26"/>
       <c r="I236" s="26"/>
       <c r="J236" s="26"/>
@@ -10268,8 +11183,12 @@
       <c r="C237" s="34"/>
       <c r="D237" s="34"/>
       <c r="E237" s="34"/>
-      <c r="F237" s="27"/>
-      <c r="G237" s="27"/>
+      <c r="F237" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G237" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H237" s="26"/>
       <c r="I237" s="26"/>
       <c r="J237" s="26"/>
@@ -10286,8 +11205,12 @@
       <c r="C238" s="34"/>
       <c r="D238" s="34"/>
       <c r="E238" s="34"/>
-      <c r="F238" s="27"/>
-      <c r="G238" s="27"/>
+      <c r="F238" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G238" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H238" s="26"/>
       <c r="I238" s="26"/>
       <c r="J238" s="26"/>
@@ -10304,8 +11227,12 @@
       <c r="C239" s="34"/>
       <c r="D239" s="34"/>
       <c r="E239" s="34"/>
-      <c r="F239" s="27"/>
-      <c r="G239" s="27"/>
+      <c r="F239" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G239" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H239" s="26"/>
       <c r="I239" s="26"/>
       <c r="J239" s="26"/>
@@ -10322,8 +11249,12 @@
       <c r="C240" s="34"/>
       <c r="D240" s="34"/>
       <c r="E240" s="34"/>
-      <c r="F240" s="27"/>
-      <c r="G240" s="27"/>
+      <c r="F240" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G240" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H240" s="26"/>
       <c r="I240" s="26"/>
       <c r="J240" s="26"/>
@@ -10340,8 +11271,12 @@
       <c r="C241" s="34"/>
       <c r="D241" s="34"/>
       <c r="E241" s="34"/>
-      <c r="F241" s="27"/>
-      <c r="G241" s="27"/>
+      <c r="F241" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G241" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H241" s="26"/>
       <c r="I241" s="26"/>
       <c r="J241" s="26"/>
@@ -10358,8 +11293,12 @@
       <c r="C242" s="34"/>
       <c r="D242" s="34"/>
       <c r="E242" s="34"/>
-      <c r="F242" s="27"/>
-      <c r="G242" s="27"/>
+      <c r="F242" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G242" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H242" s="26"/>
       <c r="I242" s="26"/>
       <c r="J242" s="26"/>
@@ -10372,7 +11311,7 @@
     </row>
     <row r="243" s="25" customFormat="true" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A243" s="24" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B243" s="24"/>
       <c r="C243" s="24"/>
@@ -10396,8 +11335,12 @@
       <c r="C244" s="34"/>
       <c r="D244" s="34"/>
       <c r="E244" s="34"/>
-      <c r="F244" s="27"/>
-      <c r="G244" s="27"/>
+      <c r="F244" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G244" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H244" s="26"/>
       <c r="I244" s="26"/>
       <c r="J244" s="26"/>
@@ -10426,8 +11369,12 @@
       <c r="C245" s="34"/>
       <c r="D245" s="34"/>
       <c r="E245" s="34"/>
-      <c r="F245" s="27"/>
-      <c r="G245" s="27"/>
+      <c r="F245" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G245" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H245" s="26"/>
       <c r="I245" s="26"/>
       <c r="J245" s="26"/>
@@ -10456,8 +11403,12 @@
       <c r="C246" s="34"/>
       <c r="D246" s="34"/>
       <c r="E246" s="34"/>
-      <c r="F246" s="27"/>
-      <c r="G246" s="27"/>
+      <c r="F246" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G246" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H246" s="26"/>
       <c r="I246" s="26"/>
       <c r="J246" s="26"/>
@@ -10486,8 +11437,12 @@
       <c r="C247" s="34"/>
       <c r="D247" s="34"/>
       <c r="E247" s="34"/>
-      <c r="F247" s="27"/>
-      <c r="G247" s="27"/>
+      <c r="F247" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G247" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H247" s="26"/>
       <c r="I247" s="26"/>
       <c r="J247" s="26"/>
@@ -10516,8 +11471,12 @@
       <c r="C248" s="34"/>
       <c r="D248" s="34"/>
       <c r="E248" s="34"/>
-      <c r="F248" s="27"/>
-      <c r="G248" s="27"/>
+      <c r="F248" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G248" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H248" s="26"/>
       <c r="I248" s="26"/>
       <c r="J248" s="26"/>
@@ -10546,8 +11505,12 @@
       <c r="C249" s="34"/>
       <c r="D249" s="34"/>
       <c r="E249" s="34"/>
-      <c r="F249" s="27"/>
-      <c r="G249" s="27"/>
+      <c r="F249" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G249" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H249" s="26"/>
       <c r="I249" s="26"/>
       <c r="J249" s="26"/>
@@ -10576,8 +11539,12 @@
       <c r="C250" s="34"/>
       <c r="D250" s="34"/>
       <c r="E250" s="34"/>
-      <c r="F250" s="27"/>
-      <c r="G250" s="27"/>
+      <c r="F250" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G250" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H250" s="26"/>
       <c r="I250" s="26"/>
       <c r="J250" s="26"/>
@@ -10606,8 +11573,12 @@
       <c r="C251" s="34"/>
       <c r="D251" s="34"/>
       <c r="E251" s="34"/>
-      <c r="F251" s="27"/>
-      <c r="G251" s="27"/>
+      <c r="F251" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G251" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H251" s="26"/>
       <c r="I251" s="26"/>
       <c r="J251" s="26"/>
@@ -10636,8 +11607,12 @@
       <c r="C252" s="34"/>
       <c r="D252" s="34"/>
       <c r="E252" s="34"/>
-      <c r="F252" s="27"/>
-      <c r="G252" s="27"/>
+      <c r="F252" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G252" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H252" s="26"/>
       <c r="I252" s="26"/>
       <c r="J252" s="26"/>
@@ -10666,8 +11641,12 @@
       <c r="C253" s="34"/>
       <c r="D253" s="34"/>
       <c r="E253" s="34"/>
-      <c r="F253" s="27"/>
-      <c r="G253" s="27"/>
+      <c r="F253" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G253" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H253" s="26"/>
       <c r="I253" s="26"/>
       <c r="J253" s="26"/>
@@ -10696,8 +11675,12 @@
       <c r="C254" s="34"/>
       <c r="D254" s="34"/>
       <c r="E254" s="34"/>
-      <c r="F254" s="27"/>
-      <c r="G254" s="27"/>
+      <c r="F254" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G254" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H254" s="26"/>
       <c r="I254" s="26"/>
       <c r="J254" s="26"/>
@@ -10726,8 +11709,12 @@
       <c r="C255" s="34"/>
       <c r="D255" s="34"/>
       <c r="E255" s="34"/>
-      <c r="F255" s="27"/>
-      <c r="G255" s="27"/>
+      <c r="F255" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G255" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H255" s="26"/>
       <c r="I255" s="26"/>
       <c r="J255" s="26"/>
@@ -10756,8 +11743,12 @@
       <c r="C256" s="34"/>
       <c r="D256" s="34"/>
       <c r="E256" s="34"/>
-      <c r="F256" s="27"/>
-      <c r="G256" s="27"/>
+      <c r="F256" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G256" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H256" s="26"/>
       <c r="I256" s="26"/>
       <c r="J256" s="26"/>
@@ -10786,8 +11777,12 @@
       <c r="C257" s="34"/>
       <c r="D257" s="34"/>
       <c r="E257" s="34"/>
-      <c r="F257" s="27"/>
-      <c r="G257" s="27"/>
+      <c r="F257" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G257" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H257" s="26"/>
       <c r="I257" s="26"/>
       <c r="J257" s="26"/>
@@ -10816,8 +11811,12 @@
       <c r="C258" s="34"/>
       <c r="D258" s="34"/>
       <c r="E258" s="34"/>
-      <c r="F258" s="27"/>
-      <c r="G258" s="27"/>
+      <c r="F258" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G258" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H258" s="26"/>
       <c r="I258" s="26"/>
       <c r="J258" s="26"/>
@@ -10846,8 +11845,12 @@
       <c r="C259" s="34"/>
       <c r="D259" s="34"/>
       <c r="E259" s="34"/>
-      <c r="F259" s="27"/>
-      <c r="G259" s="27"/>
+      <c r="F259" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G259" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H259" s="26"/>
       <c r="I259" s="26"/>
       <c r="J259" s="26"/>
@@ -10876,8 +11879,12 @@
       <c r="C260" s="34"/>
       <c r="D260" s="34"/>
       <c r="E260" s="34"/>
-      <c r="F260" s="27"/>
-      <c r="G260" s="27"/>
+      <c r="F260" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G260" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H260" s="26"/>
       <c r="I260" s="26"/>
       <c r="J260" s="26"/>
@@ -10906,8 +11913,12 @@
       <c r="C261" s="34"/>
       <c r="D261" s="34"/>
       <c r="E261" s="34"/>
-      <c r="F261" s="27"/>
-      <c r="G261" s="27"/>
+      <c r="F261" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G261" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H261" s="26"/>
       <c r="I261" s="26"/>
       <c r="J261" s="26"/>
@@ -10936,8 +11947,12 @@
       <c r="C262" s="34"/>
       <c r="D262" s="34"/>
       <c r="E262" s="34"/>
-      <c r="F262" s="27"/>
-      <c r="G262" s="27"/>
+      <c r="F262" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G262" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H262" s="26"/>
       <c r="I262" s="26"/>
       <c r="J262" s="26"/>
@@ -10966,8 +11981,12 @@
       <c r="C263" s="34"/>
       <c r="D263" s="34"/>
       <c r="E263" s="34"/>
-      <c r="F263" s="27"/>
-      <c r="G263" s="27"/>
+      <c r="F263" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G263" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H263" s="26"/>
       <c r="I263" s="26"/>
       <c r="J263" s="26"/>
@@ -10984,8 +12003,12 @@
       <c r="C264" s="34"/>
       <c r="D264" s="34"/>
       <c r="E264" s="34"/>
-      <c r="F264" s="27"/>
-      <c r="G264" s="27"/>
+      <c r="F264" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G264" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H264" s="26"/>
       <c r="I264" s="26"/>
       <c r="J264" s="26"/>
@@ -11002,8 +12025,12 @@
       <c r="C265" s="34"/>
       <c r="D265" s="34"/>
       <c r="E265" s="34"/>
-      <c r="F265" s="27"/>
-      <c r="G265" s="27"/>
+      <c r="F265" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G265" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H265" s="26"/>
       <c r="I265" s="26"/>
       <c r="J265" s="26"/>
@@ -11020,8 +12047,12 @@
       <c r="C266" s="34"/>
       <c r="D266" s="34"/>
       <c r="E266" s="34"/>
-      <c r="F266" s="27"/>
-      <c r="G266" s="27"/>
+      <c r="F266" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G266" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H266" s="26"/>
       <c r="I266" s="26"/>
       <c r="J266" s="26"/>
@@ -11038,8 +12069,12 @@
       <c r="C267" s="34"/>
       <c r="D267" s="34"/>
       <c r="E267" s="34"/>
-      <c r="F267" s="27"/>
-      <c r="G267" s="27"/>
+      <c r="F267" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G267" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H267" s="26"/>
       <c r="I267" s="26"/>
       <c r="J267" s="26"/>
@@ -11056,8 +12091,12 @@
       <c r="C268" s="34"/>
       <c r="D268" s="34"/>
       <c r="E268" s="34"/>
-      <c r="F268" s="27"/>
-      <c r="G268" s="27"/>
+      <c r="F268" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G268" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H268" s="26"/>
       <c r="I268" s="26"/>
       <c r="J268" s="26"/>
@@ -11074,8 +12113,12 @@
       <c r="C269" s="34"/>
       <c r="D269" s="34"/>
       <c r="E269" s="34"/>
-      <c r="F269" s="27"/>
-      <c r="G269" s="27"/>
+      <c r="F269" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G269" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H269" s="26"/>
       <c r="I269" s="26"/>
       <c r="J269" s="26"/>
@@ -11092,8 +12135,12 @@
       <c r="C270" s="34"/>
       <c r="D270" s="34"/>
       <c r="E270" s="34"/>
-      <c r="F270" s="27"/>
-      <c r="G270" s="27"/>
+      <c r="F270" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G270" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H270" s="26"/>
       <c r="I270" s="26"/>
       <c r="J270" s="26"/>
@@ -11110,8 +12157,12 @@
       <c r="C271" s="34"/>
       <c r="D271" s="34"/>
       <c r="E271" s="34"/>
-      <c r="F271" s="27"/>
-      <c r="G271" s="27"/>
+      <c r="F271" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G271" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H271" s="26"/>
       <c r="I271" s="26"/>
       <c r="J271" s="26"/>
@@ -11128,8 +12179,12 @@
       <c r="C272" s="34"/>
       <c r="D272" s="34"/>
       <c r="E272" s="34"/>
-      <c r="F272" s="27"/>
-      <c r="G272" s="27"/>
+      <c r="F272" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G272" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H272" s="26"/>
       <c r="I272" s="26"/>
       <c r="J272" s="26"/>
@@ -11146,8 +12201,12 @@
       <c r="C273" s="34"/>
       <c r="D273" s="34"/>
       <c r="E273" s="34"/>
-      <c r="F273" s="27"/>
-      <c r="G273" s="27"/>
+      <c r="F273" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G273" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H273" s="26"/>
       <c r="I273" s="26"/>
       <c r="J273" s="26"/>
@@ -11164,8 +12223,12 @@
       <c r="C274" s="34"/>
       <c r="D274" s="34"/>
       <c r="E274" s="34"/>
-      <c r="F274" s="27"/>
-      <c r="G274" s="27"/>
+      <c r="F274" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G274" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H274" s="26"/>
       <c r="I274" s="26"/>
       <c r="J274" s="26"/>
@@ -11182,8 +12245,12 @@
       <c r="C275" s="34"/>
       <c r="D275" s="34"/>
       <c r="E275" s="34"/>
-      <c r="F275" s="27"/>
-      <c r="G275" s="27"/>
+      <c r="F275" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G275" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H275" s="26"/>
       <c r="I275" s="26"/>
       <c r="J275" s="26"/>
@@ -11200,8 +12267,12 @@
       <c r="C276" s="34"/>
       <c r="D276" s="34"/>
       <c r="E276" s="34"/>
-      <c r="F276" s="27"/>
-      <c r="G276" s="27"/>
+      <c r="F276" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G276" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H276" s="26"/>
       <c r="I276" s="26"/>
       <c r="J276" s="26"/>
@@ -11218,8 +12289,12 @@
       <c r="C277" s="34"/>
       <c r="D277" s="34"/>
       <c r="E277" s="34"/>
-      <c r="F277" s="27"/>
-      <c r="G277" s="27"/>
+      <c r="F277" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G277" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H277" s="26"/>
       <c r="I277" s="26"/>
       <c r="J277" s="26"/>
@@ -11236,8 +12311,12 @@
       <c r="C278" s="34"/>
       <c r="D278" s="34"/>
       <c r="E278" s="34"/>
-      <c r="F278" s="27"/>
-      <c r="G278" s="27"/>
+      <c r="F278" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G278" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H278" s="26"/>
       <c r="I278" s="26"/>
       <c r="J278" s="26"/>
@@ -11254,8 +12333,12 @@
       <c r="C279" s="34"/>
       <c r="D279" s="34"/>
       <c r="E279" s="34"/>
-      <c r="F279" s="27"/>
-      <c r="G279" s="27"/>
+      <c r="F279" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G279" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H279" s="26"/>
       <c r="I279" s="26"/>
       <c r="J279" s="26"/>
@@ -11272,8 +12355,12 @@
       <c r="C280" s="34"/>
       <c r="D280" s="34"/>
       <c r="E280" s="34"/>
-      <c r="F280" s="27"/>
-      <c r="G280" s="27"/>
+      <c r="F280" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G280" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H280" s="26"/>
       <c r="I280" s="26"/>
       <c r="J280" s="26"/>
@@ -11290,8 +12377,12 @@
       <c r="C281" s="34"/>
       <c r="D281" s="34"/>
       <c r="E281" s="34"/>
-      <c r="F281" s="27"/>
-      <c r="G281" s="27"/>
+      <c r="F281" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G281" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H281" s="26"/>
       <c r="I281" s="26"/>
       <c r="J281" s="26"/>
@@ -11308,8 +12399,12 @@
       <c r="C282" s="34"/>
       <c r="D282" s="34"/>
       <c r="E282" s="34"/>
-      <c r="F282" s="27"/>
-      <c r="G282" s="27"/>
+      <c r="F282" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G282" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H282" s="26"/>
       <c r="I282" s="26"/>
       <c r="J282" s="26"/>
@@ -11326,8 +12421,12 @@
       <c r="C283" s="34"/>
       <c r="D283" s="34"/>
       <c r="E283" s="34"/>
-      <c r="F283" s="27"/>
-      <c r="G283" s="27"/>
+      <c r="F283" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G283" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H283" s="26"/>
       <c r="I283" s="26"/>
       <c r="J283" s="26"/>
@@ -11344,8 +12443,12 @@
       <c r="C284" s="34"/>
       <c r="D284" s="34"/>
       <c r="E284" s="34"/>
-      <c r="F284" s="27"/>
-      <c r="G284" s="27"/>
+      <c r="F284" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G284" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H284" s="26"/>
       <c r="I284" s="26"/>
       <c r="J284" s="26"/>
@@ -11362,8 +12465,12 @@
       <c r="C285" s="34"/>
       <c r="D285" s="34"/>
       <c r="E285" s="34"/>
-      <c r="F285" s="27"/>
-      <c r="G285" s="27"/>
+      <c r="F285" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G285" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H285" s="26"/>
       <c r="I285" s="26"/>
       <c r="J285" s="26"/>
@@ -11380,8 +12487,12 @@
       <c r="C286" s="34"/>
       <c r="D286" s="34"/>
       <c r="E286" s="34"/>
-      <c r="F286" s="27"/>
-      <c r="G286" s="27"/>
+      <c r="F286" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G286" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H286" s="26"/>
       <c r="I286" s="26"/>
       <c r="J286" s="26"/>
@@ -11398,8 +12509,12 @@
       <c r="C287" s="34"/>
       <c r="D287" s="34"/>
       <c r="E287" s="34"/>
-      <c r="F287" s="27"/>
-      <c r="G287" s="27"/>
+      <c r="F287" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G287" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H287" s="26"/>
       <c r="I287" s="26"/>
       <c r="J287" s="26"/>
@@ -11416,8 +12531,12 @@
       <c r="C288" s="34"/>
       <c r="D288" s="34"/>
       <c r="E288" s="34"/>
-      <c r="F288" s="27"/>
-      <c r="G288" s="27"/>
+      <c r="F288" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G288" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H288" s="26"/>
       <c r="I288" s="26"/>
       <c r="J288" s="26"/>
@@ -11434,8 +12553,12 @@
       <c r="C289" s="34"/>
       <c r="D289" s="34"/>
       <c r="E289" s="34"/>
-      <c r="F289" s="27"/>
-      <c r="G289" s="27"/>
+      <c r="F289" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G289" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H289" s="26"/>
       <c r="I289" s="26"/>
       <c r="J289" s="26"/>
@@ -11452,8 +12575,12 @@
       <c r="C290" s="34"/>
       <c r="D290" s="34"/>
       <c r="E290" s="34"/>
-      <c r="F290" s="27"/>
-      <c r="G290" s="27"/>
+      <c r="F290" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G290" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H290" s="26"/>
       <c r="I290" s="26"/>
       <c r="J290" s="26"/>
@@ -11470,8 +12597,12 @@
       <c r="C291" s="34"/>
       <c r="D291" s="34"/>
       <c r="E291" s="34"/>
-      <c r="F291" s="27"/>
-      <c r="G291" s="27"/>
+      <c r="F291" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G291" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H291" s="26"/>
       <c r="I291" s="26"/>
       <c r="J291" s="26"/>
@@ -11488,8 +12619,12 @@
       <c r="C292" s="34"/>
       <c r="D292" s="34"/>
       <c r="E292" s="34"/>
-      <c r="F292" s="27"/>
-      <c r="G292" s="27"/>
+      <c r="F292" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G292" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H292" s="26"/>
       <c r="I292" s="26"/>
       <c r="J292" s="26"/>
@@ -11506,8 +12641,12 @@
       <c r="C293" s="34"/>
       <c r="D293" s="34"/>
       <c r="E293" s="34"/>
-      <c r="F293" s="27"/>
-      <c r="G293" s="27"/>
+      <c r="F293" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G293" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H293" s="26"/>
       <c r="I293" s="26"/>
       <c r="J293" s="26"/>
@@ -11524,8 +12663,12 @@
       <c r="C294" s="34"/>
       <c r="D294" s="34"/>
       <c r="E294" s="34"/>
-      <c r="F294" s="27"/>
-      <c r="G294" s="27"/>
+      <c r="F294" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G294" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H294" s="26"/>
       <c r="I294" s="26"/>
       <c r="J294" s="26"/>
@@ -11542,8 +12685,12 @@
       <c r="C295" s="34"/>
       <c r="D295" s="34"/>
       <c r="E295" s="34"/>
-      <c r="F295" s="27"/>
-      <c r="G295" s="27"/>
+      <c r="F295" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G295" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H295" s="26"/>
       <c r="I295" s="26"/>
       <c r="J295" s="26"/>
@@ -11572,8 +12719,12 @@
       <c r="C296" s="34"/>
       <c r="D296" s="34"/>
       <c r="E296" s="34"/>
-      <c r="F296" s="27"/>
-      <c r="G296" s="27"/>
+      <c r="F296" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G296" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H296" s="26"/>
       <c r="I296" s="26"/>
       <c r="J296" s="26"/>
@@ -11602,8 +12753,12 @@
       <c r="C297" s="34"/>
       <c r="D297" s="34"/>
       <c r="E297" s="34"/>
-      <c r="F297" s="27"/>
-      <c r="G297" s="27"/>
+      <c r="F297" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G297" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H297" s="26"/>
       <c r="I297" s="26"/>
       <c r="J297" s="26"/>
@@ -11632,8 +12787,12 @@
       <c r="C298" s="34"/>
       <c r="D298" s="34"/>
       <c r="E298" s="34"/>
-      <c r="F298" s="27"/>
-      <c r="G298" s="27"/>
+      <c r="F298" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G298" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H298" s="26"/>
       <c r="I298" s="26"/>
       <c r="J298" s="26"/>
@@ -11658,7 +12817,7 @@
     </row>
     <row r="299" s="25" customFormat="true" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A299" s="24" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B299" s="24"/>
       <c r="C299" s="24"/>
@@ -11682,8 +12841,12 @@
       <c r="C300" s="34"/>
       <c r="D300" s="34"/>
       <c r="E300" s="34"/>
-      <c r="F300" s="27"/>
-      <c r="G300" s="27"/>
+      <c r="F300" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G300" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H300" s="26"/>
       <c r="I300" s="26"/>
       <c r="J300" s="26"/>
@@ -11712,8 +12875,12 @@
       <c r="C301" s="34"/>
       <c r="D301" s="34"/>
       <c r="E301" s="34"/>
-      <c r="F301" s="27"/>
-      <c r="G301" s="27"/>
+      <c r="F301" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G301" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H301" s="26"/>
       <c r="I301" s="26"/>
       <c r="J301" s="26"/>
@@ -11730,8 +12897,12 @@
       <c r="C302" s="34"/>
       <c r="D302" s="34"/>
       <c r="E302" s="34"/>
-      <c r="F302" s="27"/>
-      <c r="G302" s="27"/>
+      <c r="F302" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G302" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H302" s="26"/>
       <c r="I302" s="26"/>
       <c r="J302" s="26"/>
@@ -11748,8 +12919,12 @@
       <c r="C303" s="34"/>
       <c r="D303" s="34"/>
       <c r="E303" s="34"/>
-      <c r="F303" s="27"/>
-      <c r="G303" s="27"/>
+      <c r="F303" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G303" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H303" s="26"/>
       <c r="I303" s="26"/>
       <c r="J303" s="26"/>
@@ -11766,8 +12941,12 @@
       <c r="C304" s="34"/>
       <c r="D304" s="34"/>
       <c r="E304" s="34"/>
-      <c r="F304" s="27"/>
-      <c r="G304" s="27"/>
+      <c r="F304" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G304" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H304" s="26"/>
       <c r="I304" s="26"/>
       <c r="J304" s="26"/>
@@ -11784,8 +12963,12 @@
       <c r="C305" s="34"/>
       <c r="D305" s="34"/>
       <c r="E305" s="34"/>
-      <c r="F305" s="27"/>
-      <c r="G305" s="27"/>
+      <c r="F305" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G305" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H305" s="26"/>
       <c r="I305" s="26"/>
       <c r="J305" s="26"/>
@@ -11802,8 +12985,12 @@
       <c r="C306" s="34"/>
       <c r="D306" s="34"/>
       <c r="E306" s="34"/>
-      <c r="F306" s="27"/>
-      <c r="G306" s="27"/>
+      <c r="F306" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G306" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H306" s="26"/>
       <c r="I306" s="26"/>
       <c r="J306" s="26"/>
@@ -11820,8 +13007,12 @@
       <c r="C307" s="34"/>
       <c r="D307" s="34"/>
       <c r="E307" s="34"/>
-      <c r="F307" s="27"/>
-      <c r="G307" s="27"/>
+      <c r="F307" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G307" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H307" s="26"/>
       <c r="I307" s="26"/>
       <c r="J307" s="26"/>
@@ -11838,8 +13029,12 @@
       <c r="C308" s="34"/>
       <c r="D308" s="34"/>
       <c r="E308" s="34"/>
-      <c r="F308" s="27"/>
-      <c r="G308" s="27"/>
+      <c r="F308" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G308" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H308" s="26"/>
       <c r="I308" s="26"/>
       <c r="J308" s="26"/>
@@ -11856,8 +13051,12 @@
       <c r="C309" s="34"/>
       <c r="D309" s="34"/>
       <c r="E309" s="34"/>
-      <c r="F309" s="27"/>
-      <c r="G309" s="27"/>
+      <c r="F309" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G309" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H309" s="26"/>
       <c r="I309" s="26"/>
       <c r="J309" s="26"/>
@@ -11874,8 +13073,12 @@
       <c r="C310" s="34"/>
       <c r="D310" s="34"/>
       <c r="E310" s="34"/>
-      <c r="F310" s="27"/>
-      <c r="G310" s="27"/>
+      <c r="F310" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G310" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H310" s="26"/>
       <c r="I310" s="26"/>
       <c r="J310" s="26"/>
@@ -11892,8 +13095,12 @@
       <c r="C311" s="34"/>
       <c r="D311" s="34"/>
       <c r="E311" s="34"/>
-      <c r="F311" s="27"/>
-      <c r="G311" s="27"/>
+      <c r="F311" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G311" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H311" s="26"/>
       <c r="I311" s="26"/>
       <c r="J311" s="26"/>
@@ -11910,8 +13117,12 @@
       <c r="C312" s="34"/>
       <c r="D312" s="34"/>
       <c r="E312" s="34"/>
-      <c r="F312" s="27"/>
-      <c r="G312" s="27"/>
+      <c r="F312" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G312" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H312" s="26"/>
       <c r="I312" s="26"/>
       <c r="J312" s="26"/>
@@ -11928,8 +13139,12 @@
       <c r="C313" s="34"/>
       <c r="D313" s="34"/>
       <c r="E313" s="34"/>
-      <c r="F313" s="27"/>
-      <c r="G313" s="27"/>
+      <c r="F313" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G313" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H313" s="26"/>
       <c r="I313" s="26"/>
       <c r="J313" s="26"/>
@@ -11946,8 +13161,12 @@
       <c r="C314" s="34"/>
       <c r="D314" s="34"/>
       <c r="E314" s="34"/>
-      <c r="F314" s="27"/>
-      <c r="G314" s="27"/>
+      <c r="F314" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G314" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H314" s="26"/>
       <c r="I314" s="26"/>
       <c r="J314" s="26"/>
@@ -11964,8 +13183,12 @@
       <c r="C315" s="34"/>
       <c r="D315" s="34"/>
       <c r="E315" s="34"/>
-      <c r="F315" s="27"/>
-      <c r="G315" s="27"/>
+      <c r="F315" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G315" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H315" s="26"/>
       <c r="I315" s="26"/>
       <c r="J315" s="26"/>
@@ -11982,8 +13205,12 @@
       <c r="C316" s="34"/>
       <c r="D316" s="34"/>
       <c r="E316" s="34"/>
-      <c r="F316" s="27"/>
-      <c r="G316" s="27"/>
+      <c r="F316" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G316" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H316" s="26"/>
       <c r="I316" s="26"/>
       <c r="J316" s="26"/>
@@ -12000,8 +13227,12 @@
       <c r="C317" s="34"/>
       <c r="D317" s="34"/>
       <c r="E317" s="34"/>
-      <c r="F317" s="27"/>
-      <c r="G317" s="27"/>
+      <c r="F317" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G317" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H317" s="26"/>
       <c r="I317" s="26"/>
       <c r="J317" s="26"/>
@@ -12018,8 +13249,12 @@
       <c r="C318" s="34"/>
       <c r="D318" s="34"/>
       <c r="E318" s="34"/>
-      <c r="F318" s="27"/>
-      <c r="G318" s="27"/>
+      <c r="F318" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G318" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H318" s="26"/>
       <c r="I318" s="26"/>
       <c r="J318" s="26"/>
@@ -12036,8 +13271,12 @@
       <c r="C319" s="34"/>
       <c r="D319" s="34"/>
       <c r="E319" s="34"/>
-      <c r="F319" s="27"/>
-      <c r="G319" s="27"/>
+      <c r="F319" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G319" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H319" s="26"/>
       <c r="I319" s="26"/>
       <c r="J319" s="26"/>
@@ -12054,8 +13293,12 @@
       <c r="C320" s="34"/>
       <c r="D320" s="34"/>
       <c r="E320" s="34"/>
-      <c r="F320" s="27"/>
-      <c r="G320" s="27"/>
+      <c r="F320" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G320" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H320" s="26"/>
       <c r="I320" s="26"/>
       <c r="J320" s="26"/>
@@ -12072,8 +13315,12 @@
       <c r="C321" s="34"/>
       <c r="D321" s="34"/>
       <c r="E321" s="34"/>
-      <c r="F321" s="27"/>
-      <c r="G321" s="27"/>
+      <c r="F321" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G321" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H321" s="26"/>
       <c r="I321" s="26"/>
       <c r="J321" s="26"/>
@@ -12090,8 +13337,12 @@
       <c r="C322" s="34"/>
       <c r="D322" s="34"/>
       <c r="E322" s="34"/>
-      <c r="F322" s="27"/>
-      <c r="G322" s="27"/>
+      <c r="F322" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G322" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H322" s="26"/>
       <c r="I322" s="26"/>
       <c r="J322" s="26"/>
@@ -12108,8 +13359,12 @@
       <c r="C323" s="34"/>
       <c r="D323" s="34"/>
       <c r="E323" s="34"/>
-      <c r="F323" s="27"/>
-      <c r="G323" s="27"/>
+      <c r="F323" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G323" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H323" s="26"/>
       <c r="I323" s="26"/>
       <c r="J323" s="26"/>
@@ -12126,8 +13381,12 @@
       <c r="C324" s="34"/>
       <c r="D324" s="34"/>
       <c r="E324" s="34"/>
-      <c r="F324" s="27"/>
-      <c r="G324" s="27"/>
+      <c r="F324" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G324" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H324" s="26"/>
       <c r="I324" s="26"/>
       <c r="J324" s="26"/>
@@ -12144,8 +13403,12 @@
       <c r="C325" s="34"/>
       <c r="D325" s="34"/>
       <c r="E325" s="34"/>
-      <c r="F325" s="27"/>
-      <c r="G325" s="27"/>
+      <c r="F325" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G325" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H325" s="26"/>
       <c r="I325" s="26"/>
       <c r="J325" s="26"/>
@@ -12162,8 +13425,12 @@
       <c r="C326" s="34"/>
       <c r="D326" s="34"/>
       <c r="E326" s="34"/>
-      <c r="F326" s="27"/>
-      <c r="G326" s="27"/>
+      <c r="F326" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G326" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H326" s="26"/>
       <c r="I326" s="26"/>
       <c r="J326" s="26"/>
@@ -12180,8 +13447,12 @@
       <c r="C327" s="34"/>
       <c r="D327" s="34"/>
       <c r="E327" s="34"/>
-      <c r="F327" s="27"/>
-      <c r="G327" s="27"/>
+      <c r="F327" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G327" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H327" s="26"/>
       <c r="I327" s="26"/>
       <c r="J327" s="26"/>
@@ -12198,8 +13469,12 @@
       <c r="C328" s="34"/>
       <c r="D328" s="34"/>
       <c r="E328" s="34"/>
-      <c r="F328" s="27"/>
-      <c r="G328" s="27"/>
+      <c r="F328" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G328" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H328" s="26"/>
       <c r="I328" s="26"/>
       <c r="J328" s="26"/>
@@ -12216,8 +13491,12 @@
       <c r="C329" s="34"/>
       <c r="D329" s="34"/>
       <c r="E329" s="34"/>
-      <c r="F329" s="27"/>
-      <c r="G329" s="27"/>
+      <c r="F329" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G329" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H329" s="26"/>
       <c r="I329" s="26"/>
       <c r="J329" s="26"/>
@@ -12234,8 +13513,12 @@
       <c r="C330" s="34"/>
       <c r="D330" s="34"/>
       <c r="E330" s="34"/>
-      <c r="F330" s="27"/>
-      <c r="G330" s="27"/>
+      <c r="F330" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G330" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H330" s="26"/>
       <c r="I330" s="26"/>
       <c r="J330" s="26"/>
@@ -12252,8 +13535,12 @@
       <c r="C331" s="34"/>
       <c r="D331" s="34"/>
       <c r="E331" s="34"/>
-      <c r="F331" s="27"/>
-      <c r="G331" s="27"/>
+      <c r="F331" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G331" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H331" s="26"/>
       <c r="I331" s="26"/>
       <c r="J331" s="26"/>
@@ -12266,7 +13553,7 @@
     </row>
     <row r="332" s="25" customFormat="true" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A332" s="24" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B332" s="24"/>
       <c r="C332" s="24"/>
@@ -12290,8 +13577,12 @@
       <c r="C333" s="34"/>
       <c r="D333" s="34"/>
       <c r="E333" s="34"/>
-      <c r="F333" s="27"/>
-      <c r="G333" s="27"/>
+      <c r="F333" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G333" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H333" s="26"/>
       <c r="I333" s="26"/>
       <c r="J333" s="26"/>
@@ -12320,8 +13611,12 @@
       <c r="C334" s="34"/>
       <c r="D334" s="34"/>
       <c r="E334" s="34"/>
-      <c r="F334" s="27"/>
-      <c r="G334" s="27"/>
+      <c r="F334" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G334" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H334" s="26"/>
       <c r="I334" s="26"/>
       <c r="J334" s="26"/>
@@ -12338,8 +13633,12 @@
       <c r="C335" s="34"/>
       <c r="D335" s="34"/>
       <c r="E335" s="34"/>
-      <c r="F335" s="27"/>
-      <c r="G335" s="27"/>
+      <c r="F335" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G335" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H335" s="26"/>
       <c r="I335" s="26"/>
       <c r="J335" s="26"/>
@@ -12356,8 +13655,12 @@
       <c r="C336" s="34"/>
       <c r="D336" s="34"/>
       <c r="E336" s="34"/>
-      <c r="F336" s="27"/>
-      <c r="G336" s="27"/>
+      <c r="F336" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G336" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H336" s="26"/>
       <c r="I336" s="26"/>
       <c r="J336" s="26"/>
@@ -12374,8 +13677,12 @@
       <c r="C337" s="34"/>
       <c r="D337" s="34"/>
       <c r="E337" s="34"/>
-      <c r="F337" s="27"/>
-      <c r="G337" s="27"/>
+      <c r="F337" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G337" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H337" s="26"/>
       <c r="I337" s="26"/>
       <c r="J337" s="26"/>
@@ -12392,8 +13699,12 @@
       <c r="C338" s="34"/>
       <c r="D338" s="34"/>
       <c r="E338" s="34"/>
-      <c r="F338" s="27"/>
-      <c r="G338" s="27"/>
+      <c r="F338" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G338" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H338" s="26"/>
       <c r="I338" s="26"/>
       <c r="J338" s="26"/>
@@ -12410,8 +13721,12 @@
       <c r="C339" s="34"/>
       <c r="D339" s="34"/>
       <c r="E339" s="34"/>
-      <c r="F339" s="27"/>
-      <c r="G339" s="27"/>
+      <c r="F339" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G339" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H339" s="26"/>
       <c r="I339" s="26"/>
       <c r="J339" s="26"/>
@@ -12428,8 +13743,12 @@
       <c r="C340" s="34"/>
       <c r="D340" s="34"/>
       <c r="E340" s="34"/>
-      <c r="F340" s="27"/>
-      <c r="G340" s="27"/>
+      <c r="F340" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G340" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H340" s="26"/>
       <c r="I340" s="26"/>
       <c r="J340" s="26"/>
@@ -12446,8 +13765,12 @@
       <c r="C341" s="34"/>
       <c r="D341" s="34"/>
       <c r="E341" s="34"/>
-      <c r="F341" s="27"/>
-      <c r="G341" s="27"/>
+      <c r="F341" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G341" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H341" s="26"/>
       <c r="I341" s="26"/>
       <c r="J341" s="26"/>
@@ -12464,8 +13787,12 @@
       <c r="C342" s="34"/>
       <c r="D342" s="34"/>
       <c r="E342" s="34"/>
-      <c r="F342" s="27"/>
-      <c r="G342" s="27"/>
+      <c r="F342" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G342" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H342" s="26"/>
       <c r="I342" s="26"/>
       <c r="J342" s="26"/>
@@ -12482,8 +13809,12 @@
       <c r="C343" s="34"/>
       <c r="D343" s="34"/>
       <c r="E343" s="34"/>
-      <c r="F343" s="27"/>
-      <c r="G343" s="27"/>
+      <c r="F343" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G343" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H343" s="26"/>
       <c r="I343" s="26"/>
       <c r="J343" s="26"/>
@@ -12500,8 +13831,12 @@
       <c r="C344" s="34"/>
       <c r="D344" s="34"/>
       <c r="E344" s="34"/>
-      <c r="F344" s="27"/>
-      <c r="G344" s="27"/>
+      <c r="F344" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G344" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H344" s="26"/>
       <c r="I344" s="26"/>
       <c r="J344" s="26"/>
@@ -12518,8 +13853,12 @@
       <c r="C345" s="34"/>
       <c r="D345" s="34"/>
       <c r="E345" s="34"/>
-      <c r="F345" s="27"/>
-      <c r="G345" s="27"/>
+      <c r="F345" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G345" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H345" s="26"/>
       <c r="I345" s="26"/>
       <c r="J345" s="26"/>
@@ -12532,7 +13871,7 @@
     </row>
     <row r="346" s="25" customFormat="true" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A346" s="24" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B346" s="24"/>
       <c r="C346" s="24"/>
@@ -12556,8 +13895,12 @@
       <c r="C347" s="34"/>
       <c r="D347" s="34"/>
       <c r="E347" s="34"/>
-      <c r="F347" s="27"/>
-      <c r="G347" s="27"/>
+      <c r="F347" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G347" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H347" s="26"/>
       <c r="I347" s="26"/>
       <c r="J347" s="26"/>
@@ -12586,8 +13929,12 @@
       <c r="C348" s="34"/>
       <c r="D348" s="34"/>
       <c r="E348" s="34"/>
-      <c r="F348" s="27"/>
-      <c r="G348" s="27"/>
+      <c r="F348" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G348" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H348" s="26"/>
       <c r="I348" s="26"/>
       <c r="J348" s="26"/>
@@ -12604,8 +13951,12 @@
       <c r="C349" s="34"/>
       <c r="D349" s="34"/>
       <c r="E349" s="34"/>
-      <c r="F349" s="27"/>
-      <c r="G349" s="27"/>
+      <c r="F349" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G349" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H349" s="26"/>
       <c r="I349" s="26"/>
       <c r="J349" s="26"/>
@@ -12622,8 +13973,12 @@
       <c r="C350" s="34"/>
       <c r="D350" s="34"/>
       <c r="E350" s="34"/>
-      <c r="F350" s="27"/>
-      <c r="G350" s="27"/>
+      <c r="F350" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G350" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H350" s="26"/>
       <c r="I350" s="26"/>
       <c r="J350" s="26"/>
@@ -12640,8 +13995,12 @@
       <c r="C351" s="34"/>
       <c r="D351" s="34"/>
       <c r="E351" s="34"/>
-      <c r="F351" s="27"/>
-      <c r="G351" s="27"/>
+      <c r="F351" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G351" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H351" s="26"/>
       <c r="I351" s="26"/>
       <c r="J351" s="26"/>
@@ -12658,8 +14017,12 @@
       <c r="C352" s="34"/>
       <c r="D352" s="34"/>
       <c r="E352" s="34"/>
-      <c r="F352" s="27"/>
-      <c r="G352" s="27"/>
+      <c r="F352" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G352" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H352" s="26"/>
       <c r="I352" s="26"/>
       <c r="J352" s="26"/>
@@ -12676,8 +14039,12 @@
       <c r="C353" s="34"/>
       <c r="D353" s="34"/>
       <c r="E353" s="34"/>
-      <c r="F353" s="27"/>
-      <c r="G353" s="27"/>
+      <c r="F353" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G353" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H353" s="26"/>
       <c r="I353" s="26"/>
       <c r="J353" s="26"/>
@@ -12694,8 +14061,12 @@
       <c r="C354" s="34"/>
       <c r="D354" s="34"/>
       <c r="E354" s="34"/>
-      <c r="F354" s="27"/>
-      <c r="G354" s="27"/>
+      <c r="F354" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G354" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H354" s="26"/>
       <c r="I354" s="26"/>
       <c r="J354" s="26"/>
@@ -12712,8 +14083,12 @@
       <c r="C355" s="34"/>
       <c r="D355" s="34"/>
       <c r="E355" s="34"/>
-      <c r="F355" s="27"/>
-      <c r="G355" s="27"/>
+      <c r="F355" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G355" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H355" s="26"/>
       <c r="I355" s="26"/>
       <c r="J355" s="26"/>
@@ -12730,8 +14105,12 @@
       <c r="C356" s="34"/>
       <c r="D356" s="34"/>
       <c r="E356" s="34"/>
-      <c r="F356" s="27"/>
-      <c r="G356" s="27"/>
+      <c r="F356" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G356" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H356" s="26"/>
       <c r="I356" s="26"/>
       <c r="J356" s="26"/>
@@ -12748,8 +14127,12 @@
       <c r="C357" s="34"/>
       <c r="D357" s="34"/>
       <c r="E357" s="34"/>
-      <c r="F357" s="27"/>
-      <c r="G357" s="27"/>
+      <c r="F357" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G357" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H357" s="26"/>
       <c r="I357" s="26"/>
       <c r="J357" s="26"/>
@@ -12766,8 +14149,12 @@
       <c r="C358" s="34"/>
       <c r="D358" s="34"/>
       <c r="E358" s="34"/>
-      <c r="F358" s="27"/>
-      <c r="G358" s="27"/>
+      <c r="F358" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G358" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H358" s="26"/>
       <c r="I358" s="26"/>
       <c r="J358" s="26"/>
@@ -12784,8 +14171,12 @@
       <c r="C359" s="34"/>
       <c r="D359" s="34"/>
       <c r="E359" s="34"/>
-      <c r="F359" s="27"/>
-      <c r="G359" s="27"/>
+      <c r="F359" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G359" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H359" s="26"/>
       <c r="I359" s="26"/>
       <c r="J359" s="26"/>
@@ -12802,8 +14193,12 @@
       <c r="C360" s="34"/>
       <c r="D360" s="34"/>
       <c r="E360" s="34"/>
-      <c r="F360" s="27"/>
-      <c r="G360" s="27"/>
+      <c r="F360" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G360" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H360" s="26"/>
       <c r="I360" s="26"/>
       <c r="J360" s="26"/>
@@ -12820,8 +14215,12 @@
       <c r="C361" s="34"/>
       <c r="D361" s="34"/>
       <c r="E361" s="34"/>
-      <c r="F361" s="27"/>
-      <c r="G361" s="27"/>
+      <c r="F361" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G361" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H361" s="26"/>
       <c r="I361" s="26"/>
       <c r="J361" s="26"/>
@@ -12838,8 +14237,12 @@
       <c r="C362" s="34"/>
       <c r="D362" s="34"/>
       <c r="E362" s="34"/>
-      <c r="F362" s="27"/>
-      <c r="G362" s="27"/>
+      <c r="F362" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G362" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H362" s="26"/>
       <c r="I362" s="26"/>
       <c r="J362" s="26"/>
@@ -12856,8 +14259,12 @@
       <c r="C363" s="34"/>
       <c r="D363" s="34"/>
       <c r="E363" s="34"/>
-      <c r="F363" s="27"/>
-      <c r="G363" s="27"/>
+      <c r="F363" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G363" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H363" s="26"/>
       <c r="I363" s="26"/>
       <c r="J363" s="26"/>
@@ -12874,8 +14281,12 @@
       <c r="C364" s="34"/>
       <c r="D364" s="34"/>
       <c r="E364" s="34"/>
-      <c r="F364" s="27"/>
-      <c r="G364" s="27"/>
+      <c r="F364" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G364" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H364" s="26"/>
       <c r="I364" s="26"/>
       <c r="J364" s="26"/>
@@ -12892,8 +14303,12 @@
       <c r="C365" s="34"/>
       <c r="D365" s="34"/>
       <c r="E365" s="34"/>
-      <c r="F365" s="27"/>
-      <c r="G365" s="27"/>
+      <c r="F365" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G365" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H365" s="26"/>
       <c r="I365" s="26"/>
       <c r="J365" s="26"/>
@@ -12910,8 +14325,12 @@
       <c r="C366" s="34"/>
       <c r="D366" s="34"/>
       <c r="E366" s="34"/>
-      <c r="F366" s="27"/>
-      <c r="G366" s="27"/>
+      <c r="F366" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G366" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H366" s="26"/>
       <c r="I366" s="26"/>
       <c r="J366" s="26"/>
@@ -12928,8 +14347,12 @@
       <c r="C367" s="34"/>
       <c r="D367" s="34"/>
       <c r="E367" s="34"/>
-      <c r="F367" s="27"/>
-      <c r="G367" s="27"/>
+      <c r="F367" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G367" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H367" s="26"/>
       <c r="I367" s="26"/>
       <c r="J367" s="26"/>
@@ -12946,8 +14369,12 @@
       <c r="C368" s="34"/>
       <c r="D368" s="34"/>
       <c r="E368" s="34"/>
-      <c r="F368" s="27"/>
-      <c r="G368" s="27"/>
+      <c r="F368" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G368" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H368" s="26"/>
       <c r="I368" s="26"/>
       <c r="J368" s="26"/>
@@ -12964,8 +14391,12 @@
       <c r="C369" s="34"/>
       <c r="D369" s="34"/>
       <c r="E369" s="34"/>
-      <c r="F369" s="27"/>
-      <c r="G369" s="27"/>
+      <c r="F369" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G369" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H369" s="26"/>
       <c r="I369" s="26"/>
       <c r="J369" s="26"/>
@@ -12982,8 +14413,12 @@
       <c r="C370" s="34"/>
       <c r="D370" s="34"/>
       <c r="E370" s="34"/>
-      <c r="F370" s="27"/>
-      <c r="G370" s="27"/>
+      <c r="F370" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G370" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H370" s="26"/>
       <c r="I370" s="26"/>
       <c r="J370" s="26"/>
@@ -13000,8 +14435,12 @@
       <c r="C371" s="34"/>
       <c r="D371" s="34"/>
       <c r="E371" s="34"/>
-      <c r="F371" s="27"/>
-      <c r="G371" s="27"/>
+      <c r="F371" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G371" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H371" s="26"/>
       <c r="I371" s="26"/>
       <c r="J371" s="26"/>
@@ -13018,8 +14457,12 @@
       <c r="C372" s="34"/>
       <c r="D372" s="34"/>
       <c r="E372" s="34"/>
-      <c r="F372" s="27"/>
-      <c r="G372" s="27"/>
+      <c r="F372" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G372" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H372" s="26"/>
       <c r="I372" s="26"/>
       <c r="J372" s="26"/>
@@ -13036,8 +14479,12 @@
       <c r="C373" s="34"/>
       <c r="D373" s="34"/>
       <c r="E373" s="34"/>
-      <c r="F373" s="27"/>
-      <c r="G373" s="27"/>
+      <c r="F373" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G373" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H373" s="26"/>
       <c r="I373" s="26"/>
       <c r="J373" s="26"/>
@@ -13054,8 +14501,12 @@
       <c r="C374" s="34"/>
       <c r="D374" s="34"/>
       <c r="E374" s="34"/>
-      <c r="F374" s="27"/>
-      <c r="G374" s="27"/>
+      <c r="F374" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G374" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H374" s="26"/>
       <c r="I374" s="26"/>
       <c r="J374" s="26"/>
@@ -13072,8 +14523,12 @@
       <c r="C375" s="34"/>
       <c r="D375" s="34"/>
       <c r="E375" s="34"/>
-      <c r="F375" s="27"/>
-      <c r="G375" s="27"/>
+      <c r="F375" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G375" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H375" s="26"/>
       <c r="I375" s="26"/>
       <c r="J375" s="26"/>
@@ -13090,8 +14545,12 @@
       <c r="C376" s="34"/>
       <c r="D376" s="34"/>
       <c r="E376" s="34"/>
-      <c r="F376" s="27"/>
-      <c r="G376" s="27"/>
+      <c r="F376" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G376" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H376" s="26"/>
       <c r="I376" s="26"/>
       <c r="J376" s="26"/>
@@ -13108,8 +14567,12 @@
       <c r="C377" s="34"/>
       <c r="D377" s="34"/>
       <c r="E377" s="34"/>
-      <c r="F377" s="27"/>
-      <c r="G377" s="27"/>
+      <c r="F377" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G377" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H377" s="26"/>
       <c r="I377" s="26"/>
       <c r="J377" s="26"/>
@@ -13126,8 +14589,12 @@
       <c r="C378" s="34"/>
       <c r="D378" s="34"/>
       <c r="E378" s="34"/>
-      <c r="F378" s="27"/>
-      <c r="G378" s="27"/>
+      <c r="F378" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G378" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H378" s="26"/>
       <c r="I378" s="26"/>
       <c r="J378" s="26"/>
@@ -13144,8 +14611,12 @@
       <c r="C379" s="34"/>
       <c r="D379" s="34"/>
       <c r="E379" s="34"/>
-      <c r="F379" s="27"/>
-      <c r="G379" s="27"/>
+      <c r="F379" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G379" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H379" s="26"/>
       <c r="I379" s="26"/>
       <c r="J379" s="26"/>
@@ -13162,8 +14633,12 @@
       <c r="C380" s="34"/>
       <c r="D380" s="34"/>
       <c r="E380" s="34"/>
-      <c r="F380" s="27"/>
-      <c r="G380" s="27"/>
+      <c r="F380" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G380" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H380" s="26"/>
       <c r="I380" s="26"/>
       <c r="J380" s="26"/>
@@ -13180,8 +14655,12 @@
       <c r="C381" s="34"/>
       <c r="D381" s="34"/>
       <c r="E381" s="34"/>
-      <c r="F381" s="27"/>
-      <c r="G381" s="27"/>
+      <c r="F381" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G381" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H381" s="26"/>
       <c r="I381" s="26"/>
       <c r="J381" s="26"/>
@@ -13198,8 +14677,12 @@
       <c r="C382" s="34"/>
       <c r="D382" s="34"/>
       <c r="E382" s="34"/>
-      <c r="F382" s="27"/>
-      <c r="G382" s="27"/>
+      <c r="F382" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G382" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H382" s="26"/>
       <c r="I382" s="26"/>
       <c r="J382" s="26"/>
@@ -13216,8 +14699,12 @@
       <c r="C383" s="34"/>
       <c r="D383" s="34"/>
       <c r="E383" s="34"/>
-      <c r="F383" s="27"/>
-      <c r="G383" s="27"/>
+      <c r="F383" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G383" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H383" s="26"/>
       <c r="I383" s="26"/>
       <c r="J383" s="26"/>
@@ -13234,8 +14721,12 @@
       <c r="C384" s="34"/>
       <c r="D384" s="34"/>
       <c r="E384" s="34"/>
-      <c r="F384" s="27"/>
-      <c r="G384" s="27"/>
+      <c r="F384" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G384" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H384" s="26"/>
       <c r="I384" s="26"/>
       <c r="J384" s="26"/>
@@ -13252,8 +14743,12 @@
       <c r="C385" s="34"/>
       <c r="D385" s="34"/>
       <c r="E385" s="34"/>
-      <c r="F385" s="27"/>
-      <c r="G385" s="27"/>
+      <c r="F385" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G385" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H385" s="26"/>
       <c r="I385" s="26"/>
       <c r="J385" s="26"/>
@@ -13270,8 +14765,12 @@
       <c r="C386" s="34"/>
       <c r="D386" s="34"/>
       <c r="E386" s="34"/>
-      <c r="F386" s="27"/>
-      <c r="G386" s="27"/>
+      <c r="F386" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G386" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H386" s="26"/>
       <c r="I386" s="26"/>
       <c r="J386" s="26"/>
@@ -13288,8 +14787,12 @@
       <c r="C387" s="34"/>
       <c r="D387" s="34"/>
       <c r="E387" s="34"/>
-      <c r="F387" s="27"/>
-      <c r="G387" s="27"/>
+      <c r="F387" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G387" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H387" s="26"/>
       <c r="I387" s="26"/>
       <c r="J387" s="26"/>
@@ -13306,8 +14809,12 @@
       <c r="C388" s="34"/>
       <c r="D388" s="34"/>
       <c r="E388" s="34"/>
-      <c r="F388" s="27"/>
-      <c r="G388" s="27"/>
+      <c r="F388" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G388" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H388" s="26"/>
       <c r="I388" s="26"/>
       <c r="J388" s="26"/>
@@ -13324,8 +14831,12 @@
       <c r="C389" s="34"/>
       <c r="D389" s="34"/>
       <c r="E389" s="34"/>
-      <c r="F389" s="27"/>
-      <c r="G389" s="27"/>
+      <c r="F389" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G389" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H389" s="26"/>
       <c r="I389" s="26"/>
       <c r="J389" s="26"/>
@@ -13342,8 +14853,12 @@
       <c r="C390" s="34"/>
       <c r="D390" s="34"/>
       <c r="E390" s="34"/>
-      <c r="F390" s="27"/>
-      <c r="G390" s="27"/>
+      <c r="F390" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G390" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H390" s="26"/>
       <c r="I390" s="26"/>
       <c r="J390" s="26"/>
@@ -13360,8 +14875,12 @@
       <c r="C391" s="34"/>
       <c r="D391" s="34"/>
       <c r="E391" s="34"/>
-      <c r="F391" s="27"/>
-      <c r="G391" s="27"/>
+      <c r="F391" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G391" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H391" s="26"/>
       <c r="I391" s="26"/>
       <c r="J391" s="26"/>
@@ -13378,8 +14897,12 @@
       <c r="C392" s="34"/>
       <c r="D392" s="34"/>
       <c r="E392" s="34"/>
-      <c r="F392" s="27"/>
-      <c r="G392" s="27"/>
+      <c r="F392" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G392" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H392" s="26"/>
       <c r="I392" s="26"/>
       <c r="J392" s="26"/>
@@ -13396,8 +14919,12 @@
       <c r="C393" s="34"/>
       <c r="D393" s="34"/>
       <c r="E393" s="34"/>
-      <c r="F393" s="27"/>
-      <c r="G393" s="27"/>
+      <c r="F393" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G393" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H393" s="26"/>
       <c r="I393" s="26"/>
       <c r="J393" s="26"/>
@@ -13414,8 +14941,12 @@
       <c r="C394" s="34"/>
       <c r="D394" s="34"/>
       <c r="E394" s="34"/>
-      <c r="F394" s="27"/>
-      <c r="G394" s="27"/>
+      <c r="F394" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G394" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H394" s="26"/>
       <c r="I394" s="26"/>
       <c r="J394" s="26"/>
@@ -13428,7 +14959,7 @@
     </row>
     <row r="395" s="25" customFormat="true" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A395" s="24" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B395" s="24"/>
       <c r="C395" s="24"/>
@@ -13452,8 +14983,12 @@
       <c r="C396" s="34"/>
       <c r="D396" s="34"/>
       <c r="E396" s="34"/>
-      <c r="F396" s="27"/>
-      <c r="G396" s="27"/>
+      <c r="F396" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G396" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H396" s="26"/>
       <c r="I396" s="26"/>
       <c r="J396" s="26"/>
@@ -13482,8 +15017,12 @@
       <c r="C397" s="34"/>
       <c r="D397" s="34"/>
       <c r="E397" s="34"/>
-      <c r="F397" s="27"/>
-      <c r="G397" s="27"/>
+      <c r="F397" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G397" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H397" s="26"/>
       <c r="I397" s="26"/>
       <c r="J397" s="26"/>
@@ -13512,8 +15051,12 @@
       <c r="C398" s="34"/>
       <c r="D398" s="34"/>
       <c r="E398" s="34"/>
-      <c r="F398" s="27"/>
-      <c r="G398" s="27"/>
+      <c r="F398" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G398" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H398" s="26"/>
       <c r="I398" s="26"/>
       <c r="J398" s="26"/>
@@ -13542,8 +15085,12 @@
       <c r="C399" s="34"/>
       <c r="D399" s="34"/>
       <c r="E399" s="34"/>
-      <c r="F399" s="27"/>
-      <c r="G399" s="27"/>
+      <c r="F399" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G399" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H399" s="26"/>
       <c r="I399" s="26"/>
       <c r="J399" s="26"/>
@@ -13572,8 +15119,12 @@
       <c r="C400" s="34"/>
       <c r="D400" s="34"/>
       <c r="E400" s="34"/>
-      <c r="F400" s="27"/>
-      <c r="G400" s="27"/>
+      <c r="F400" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G400" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H400" s="26"/>
       <c r="I400" s="26"/>
       <c r="J400" s="26"/>
@@ -13602,8 +15153,12 @@
       <c r="C401" s="34"/>
       <c r="D401" s="34"/>
       <c r="E401" s="34"/>
-      <c r="F401" s="27"/>
-      <c r="G401" s="27"/>
+      <c r="F401" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G401" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H401" s="26"/>
       <c r="I401" s="26"/>
       <c r="J401" s="26"/>
@@ -13632,8 +15187,12 @@
       <c r="C402" s="34"/>
       <c r="D402" s="34"/>
       <c r="E402" s="34"/>
-      <c r="F402" s="27"/>
-      <c r="G402" s="27"/>
+      <c r="F402" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G402" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H402" s="26"/>
       <c r="I402" s="26"/>
       <c r="J402" s="26"/>
@@ -13662,8 +15221,12 @@
       <c r="C403" s="34"/>
       <c r="D403" s="34"/>
       <c r="E403" s="34"/>
-      <c r="F403" s="27"/>
-      <c r="G403" s="27"/>
+      <c r="F403" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G403" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H403" s="26"/>
       <c r="I403" s="26"/>
       <c r="J403" s="26"/>
@@ -13692,8 +15255,12 @@
       <c r="C404" s="34"/>
       <c r="D404" s="34"/>
       <c r="E404" s="34"/>
-      <c r="F404" s="27"/>
-      <c r="G404" s="27"/>
+      <c r="F404" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G404" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H404" s="26"/>
       <c r="I404" s="26"/>
       <c r="J404" s="26"/>
@@ -13722,8 +15289,12 @@
       <c r="C405" s="34"/>
       <c r="D405" s="34"/>
       <c r="E405" s="34"/>
-      <c r="F405" s="27"/>
-      <c r="G405" s="27"/>
+      <c r="F405" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G405" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H405" s="26"/>
       <c r="I405" s="26"/>
       <c r="J405" s="26"/>
@@ -13740,8 +15311,12 @@
       <c r="C406" s="34"/>
       <c r="D406" s="34"/>
       <c r="E406" s="34"/>
-      <c r="F406" s="27"/>
-      <c r="G406" s="27"/>
+      <c r="F406" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G406" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H406" s="26"/>
       <c r="I406" s="26"/>
       <c r="J406" s="26"/>
@@ -13758,8 +15333,12 @@
       <c r="C407" s="34"/>
       <c r="D407" s="34"/>
       <c r="E407" s="34"/>
-      <c r="F407" s="27"/>
-      <c r="G407" s="27"/>
+      <c r="F407" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G407" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H407" s="26"/>
       <c r="I407" s="26"/>
       <c r="J407" s="26"/>
@@ -13776,8 +15355,12 @@
       <c r="C408" s="34"/>
       <c r="D408" s="34"/>
       <c r="E408" s="34"/>
-      <c r="F408" s="27"/>
-      <c r="G408" s="27"/>
+      <c r="F408" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G408" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H408" s="26"/>
       <c r="I408" s="26"/>
       <c r="J408" s="26"/>
@@ -13794,8 +15377,12 @@
       <c r="C409" s="34"/>
       <c r="D409" s="34"/>
       <c r="E409" s="34"/>
-      <c r="F409" s="27"/>
-      <c r="G409" s="27"/>
+      <c r="F409" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G409" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H409" s="26"/>
       <c r="I409" s="26"/>
       <c r="J409" s="26"/>
@@ -13812,8 +15399,12 @@
       <c r="C410" s="34"/>
       <c r="D410" s="34"/>
       <c r="E410" s="34"/>
-      <c r="F410" s="27"/>
-      <c r="G410" s="27"/>
+      <c r="F410" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G410" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H410" s="26"/>
       <c r="I410" s="26"/>
       <c r="J410" s="26"/>
@@ -13830,8 +15421,12 @@
       <c r="C411" s="34"/>
       <c r="D411" s="34"/>
       <c r="E411" s="34"/>
-      <c r="F411" s="27"/>
-      <c r="G411" s="27"/>
+      <c r="F411" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G411" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H411" s="26"/>
       <c r="I411" s="26"/>
       <c r="J411" s="26"/>
@@ -13848,8 +15443,12 @@
       <c r="C412" s="34"/>
       <c r="D412" s="34"/>
       <c r="E412" s="34"/>
-      <c r="F412" s="27"/>
-      <c r="G412" s="27"/>
+      <c r="F412" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G412" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H412" s="26"/>
       <c r="I412" s="26"/>
       <c r="J412" s="26"/>
@@ -13862,7 +15461,7 @@
     </row>
     <row r="413" s="25" customFormat="true" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A413" s="24" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B413" s="24"/>
       <c r="C413" s="24"/>
@@ -13886,8 +15485,12 @@
       <c r="C414" s="34"/>
       <c r="D414" s="34"/>
       <c r="E414" s="34"/>
-      <c r="F414" s="27"/>
-      <c r="G414" s="27"/>
+      <c r="F414" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G414" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H414" s="26"/>
       <c r="I414" s="26"/>
       <c r="J414" s="26"/>
@@ -13916,8 +15519,12 @@
       <c r="C415" s="34"/>
       <c r="D415" s="34"/>
       <c r="E415" s="34"/>
-      <c r="F415" s="27"/>
-      <c r="G415" s="27"/>
+      <c r="F415" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G415" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H415" s="26"/>
       <c r="I415" s="26"/>
       <c r="J415" s="26"/>
@@ -13946,8 +15553,12 @@
       <c r="C416" s="34"/>
       <c r="D416" s="34"/>
       <c r="E416" s="34"/>
-      <c r="F416" s="27"/>
-      <c r="G416" s="27"/>
+      <c r="F416" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G416" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H416" s="26"/>
       <c r="I416" s="26"/>
       <c r="J416" s="26"/>
@@ -13976,8 +15587,12 @@
       <c r="C417" s="34"/>
       <c r="D417" s="34"/>
       <c r="E417" s="34"/>
-      <c r="F417" s="27"/>
-      <c r="G417" s="27"/>
+      <c r="F417" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G417" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H417" s="26"/>
       <c r="I417" s="26"/>
       <c r="J417" s="26"/>
@@ -14006,8 +15621,12 @@
       <c r="C418" s="34"/>
       <c r="D418" s="34"/>
       <c r="E418" s="34"/>
-      <c r="F418" s="27"/>
-      <c r="G418" s="27"/>
+      <c r="F418" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G418" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H418" s="26"/>
       <c r="I418" s="26"/>
       <c r="J418" s="26"/>
@@ -14036,8 +15655,12 @@
       <c r="C419" s="34"/>
       <c r="D419" s="34"/>
       <c r="E419" s="34"/>
-      <c r="F419" s="27"/>
-      <c r="G419" s="27"/>
+      <c r="F419" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G419" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H419" s="26"/>
       <c r="I419" s="26"/>
       <c r="J419" s="26"/>
@@ -14066,8 +15689,12 @@
       <c r="C420" s="34"/>
       <c r="D420" s="34"/>
       <c r="E420" s="34"/>
-      <c r="F420" s="27"/>
-      <c r="G420" s="27"/>
+      <c r="F420" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G420" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H420" s="26"/>
       <c r="I420" s="26"/>
       <c r="J420" s="26"/>
@@ -14096,8 +15723,12 @@
       <c r="C421" s="34"/>
       <c r="D421" s="34"/>
       <c r="E421" s="34"/>
-      <c r="F421" s="27"/>
-      <c r="G421" s="27"/>
+      <c r="F421" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G421" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H421" s="26"/>
       <c r="I421" s="26"/>
       <c r="J421" s="26"/>
@@ -14126,8 +15757,12 @@
       <c r="C422" s="34"/>
       <c r="D422" s="34"/>
       <c r="E422" s="34"/>
-      <c r="F422" s="27"/>
-      <c r="G422" s="27"/>
+      <c r="F422" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G422" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H422" s="26"/>
       <c r="I422" s="26"/>
       <c r="J422" s="26"/>
@@ -14156,8 +15791,12 @@
       <c r="C423" s="34"/>
       <c r="D423" s="34"/>
       <c r="E423" s="34"/>
-      <c r="F423" s="27"/>
-      <c r="G423" s="27"/>
+      <c r="F423" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G423" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H423" s="26"/>
       <c r="I423" s="26"/>
       <c r="J423" s="26"/>
@@ -14186,8 +15825,12 @@
       <c r="C424" s="34"/>
       <c r="D424" s="34"/>
       <c r="E424" s="34"/>
-      <c r="F424" s="27"/>
-      <c r="G424" s="27"/>
+      <c r="F424" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G424" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H424" s="26"/>
       <c r="I424" s="26"/>
       <c r="J424" s="26"/>
@@ -14216,8 +15859,12 @@
       <c r="C425" s="34"/>
       <c r="D425" s="34"/>
       <c r="E425" s="34"/>
-      <c r="F425" s="27"/>
-      <c r="G425" s="27"/>
+      <c r="F425" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G425" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H425" s="26"/>
       <c r="I425" s="26"/>
       <c r="J425" s="26"/>
@@ -14246,8 +15893,12 @@
       <c r="C426" s="34"/>
       <c r="D426" s="34"/>
       <c r="E426" s="34"/>
-      <c r="F426" s="27"/>
-      <c r="G426" s="27"/>
+      <c r="F426" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G426" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H426" s="26"/>
       <c r="I426" s="26"/>
       <c r="J426" s="26"/>
@@ -14276,8 +15927,12 @@
       <c r="C427" s="34"/>
       <c r="D427" s="34"/>
       <c r="E427" s="34"/>
-      <c r="F427" s="27"/>
-      <c r="G427" s="27"/>
+      <c r="F427" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G427" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H427" s="26"/>
       <c r="I427" s="26"/>
       <c r="J427" s="26"/>
@@ -14306,8 +15961,12 @@
       <c r="C428" s="34"/>
       <c r="D428" s="34"/>
       <c r="E428" s="34"/>
-      <c r="F428" s="27"/>
-      <c r="G428" s="27"/>
+      <c r="F428" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G428" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H428" s="26"/>
       <c r="I428" s="26"/>
       <c r="J428" s="26"/>
@@ -14324,8 +15983,12 @@
       <c r="C429" s="34"/>
       <c r="D429" s="34"/>
       <c r="E429" s="34"/>
-      <c r="F429" s="27"/>
-      <c r="G429" s="27"/>
+      <c r="F429" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G429" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H429" s="26"/>
       <c r="I429" s="26"/>
       <c r="J429" s="26"/>
@@ -14342,8 +16005,12 @@
       <c r="C430" s="34"/>
       <c r="D430" s="34"/>
       <c r="E430" s="34"/>
-      <c r="F430" s="27"/>
-      <c r="G430" s="27"/>
+      <c r="F430" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G430" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H430" s="26"/>
       <c r="I430" s="26"/>
       <c r="J430" s="26"/>
@@ -14360,8 +16027,12 @@
       <c r="C431" s="34"/>
       <c r="D431" s="34"/>
       <c r="E431" s="34"/>
-      <c r="F431" s="27"/>
-      <c r="G431" s="27"/>
+      <c r="F431" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G431" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H431" s="26"/>
       <c r="I431" s="26"/>
       <c r="J431" s="26"/>
@@ -14378,8 +16049,12 @@
       <c r="C432" s="34"/>
       <c r="D432" s="34"/>
       <c r="E432" s="34"/>
-      <c r="F432" s="27"/>
-      <c r="G432" s="27"/>
+      <c r="F432" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G432" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H432" s="26"/>
       <c r="I432" s="26"/>
       <c r="J432" s="26"/>
@@ -14396,8 +16071,12 @@
       <c r="C433" s="34"/>
       <c r="D433" s="34"/>
       <c r="E433" s="34"/>
-      <c r="F433" s="27"/>
-      <c r="G433" s="27"/>
+      <c r="F433" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G433" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H433" s="26"/>
       <c r="I433" s="26"/>
       <c r="J433" s="26"/>
@@ -14414,8 +16093,12 @@
       <c r="C434" s="34"/>
       <c r="D434" s="34"/>
       <c r="E434" s="34"/>
-      <c r="F434" s="27"/>
-      <c r="G434" s="27"/>
+      <c r="F434" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G434" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H434" s="26"/>
       <c r="I434" s="26"/>
       <c r="J434" s="26"/>
@@ -14432,8 +16115,12 @@
       <c r="C435" s="34"/>
       <c r="D435" s="34"/>
       <c r="E435" s="34"/>
-      <c r="F435" s="27"/>
-      <c r="G435" s="27"/>
+      <c r="F435" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G435" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H435" s="26"/>
       <c r="I435" s="26"/>
       <c r="J435" s="26"/>
@@ -14450,8 +16137,12 @@
       <c r="C436" s="34"/>
       <c r="D436" s="34"/>
       <c r="E436" s="34"/>
-      <c r="F436" s="27"/>
-      <c r="G436" s="27"/>
+      <c r="F436" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G436" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H436" s="26"/>
       <c r="I436" s="26"/>
       <c r="J436" s="26"/>
@@ -14468,8 +16159,12 @@
       <c r="C437" s="34"/>
       <c r="D437" s="34"/>
       <c r="E437" s="34"/>
-      <c r="F437" s="27"/>
-      <c r="G437" s="27"/>
+      <c r="F437" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G437" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H437" s="26"/>
       <c r="I437" s="26"/>
       <c r="J437" s="26"/>
@@ -14486,8 +16181,12 @@
       <c r="C438" s="34"/>
       <c r="D438" s="34"/>
       <c r="E438" s="34"/>
-      <c r="F438" s="27"/>
-      <c r="G438" s="27"/>
+      <c r="F438" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G438" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H438" s="26"/>
       <c r="I438" s="26"/>
       <c r="J438" s="26"/>
@@ -14504,8 +16203,12 @@
       <c r="C439" s="34"/>
       <c r="D439" s="34"/>
       <c r="E439" s="34"/>
-      <c r="F439" s="27"/>
-      <c r="G439" s="27"/>
+      <c r="F439" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G439" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H439" s="26"/>
       <c r="I439" s="26"/>
       <c r="J439" s="26"/>
@@ -14522,8 +16225,12 @@
       <c r="C440" s="34"/>
       <c r="D440" s="34"/>
       <c r="E440" s="34"/>
-      <c r="F440" s="27"/>
-      <c r="G440" s="27"/>
+      <c r="F440" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G440" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H440" s="26"/>
       <c r="I440" s="26"/>
       <c r="J440" s="26"/>
@@ -14540,8 +16247,12 @@
       <c r="C441" s="34"/>
       <c r="D441" s="34"/>
       <c r="E441" s="34"/>
-      <c r="F441" s="27"/>
-      <c r="G441" s="27"/>
+      <c r="F441" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G441" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H441" s="26"/>
       <c r="I441" s="26"/>
       <c r="J441" s="26"/>
@@ -14558,8 +16269,12 @@
       <c r="C442" s="34"/>
       <c r="D442" s="34"/>
       <c r="E442" s="34"/>
-      <c r="F442" s="27"/>
-      <c r="G442" s="27"/>
+      <c r="F442" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G442" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H442" s="26"/>
       <c r="I442" s="26"/>
       <c r="J442" s="26"/>
@@ -14576,8 +16291,12 @@
       <c r="C443" s="34"/>
       <c r="D443" s="34"/>
       <c r="E443" s="34"/>
-      <c r="F443" s="27"/>
-      <c r="G443" s="27"/>
+      <c r="F443" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G443" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H443" s="26"/>
       <c r="I443" s="26"/>
       <c r="J443" s="26"/>
@@ -14594,8 +16313,12 @@
       <c r="C444" s="34"/>
       <c r="D444" s="34"/>
       <c r="E444" s="34"/>
-      <c r="F444" s="27"/>
-      <c r="G444" s="27"/>
+      <c r="F444" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G444" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H444" s="26"/>
       <c r="I444" s="26"/>
       <c r="J444" s="26"/>
@@ -14612,8 +16335,12 @@
       <c r="C445" s="34"/>
       <c r="D445" s="34"/>
       <c r="E445" s="34"/>
-      <c r="F445" s="27"/>
-      <c r="G445" s="27"/>
+      <c r="F445" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G445" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H445" s="26"/>
       <c r="I445" s="26"/>
       <c r="J445" s="26"/>
@@ -14630,8 +16357,12 @@
       <c r="C446" s="34"/>
       <c r="D446" s="34"/>
       <c r="E446" s="34"/>
-      <c r="F446" s="27"/>
-      <c r="G446" s="27"/>
+      <c r="F446" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G446" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H446" s="26"/>
       <c r="I446" s="26"/>
       <c r="J446" s="26"/>
@@ -14648,8 +16379,12 @@
       <c r="C447" s="34"/>
       <c r="D447" s="34"/>
       <c r="E447" s="34"/>
-      <c r="F447" s="27"/>
-      <c r="G447" s="27"/>
+      <c r="F447" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G447" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H447" s="26"/>
       <c r="I447" s="26"/>
       <c r="J447" s="26"/>
@@ -14666,8 +16401,12 @@
       <c r="C448" s="34"/>
       <c r="D448" s="34"/>
       <c r="E448" s="34"/>
-      <c r="F448" s="27"/>
-      <c r="G448" s="27"/>
+      <c r="F448" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G448" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H448" s="26"/>
       <c r="I448" s="26"/>
       <c r="J448" s="26"/>
@@ -14684,8 +16423,12 @@
       <c r="C449" s="34"/>
       <c r="D449" s="34"/>
       <c r="E449" s="34"/>
-      <c r="F449" s="27"/>
-      <c r="G449" s="27"/>
+      <c r="F449" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G449" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H449" s="26"/>
       <c r="I449" s="26"/>
       <c r="J449" s="26"/>
@@ -14702,8 +16445,12 @@
       <c r="C450" s="34"/>
       <c r="D450" s="34"/>
       <c r="E450" s="34"/>
-      <c r="F450" s="27"/>
-      <c r="G450" s="27"/>
+      <c r="F450" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G450" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H450" s="26"/>
       <c r="I450" s="26"/>
       <c r="J450" s="26"/>
@@ -14720,8 +16467,12 @@
       <c r="C451" s="34"/>
       <c r="D451" s="34"/>
       <c r="E451" s="34"/>
-      <c r="F451" s="27"/>
-      <c r="G451" s="27"/>
+      <c r="F451" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G451" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H451" s="26"/>
       <c r="I451" s="26"/>
       <c r="J451" s="26"/>
@@ -14738,8 +16489,12 @@
       <c r="C452" s="34"/>
       <c r="D452" s="34"/>
       <c r="E452" s="34"/>
-      <c r="F452" s="27"/>
-      <c r="G452" s="27"/>
+      <c r="F452" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G452" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H452" s="26"/>
       <c r="I452" s="26"/>
       <c r="J452" s="26"/>
@@ -14768,8 +16523,12 @@
       <c r="C453" s="34"/>
       <c r="D453" s="34"/>
       <c r="E453" s="34"/>
-      <c r="F453" s="27"/>
-      <c r="G453" s="27"/>
+      <c r="F453" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G453" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H453" s="26"/>
       <c r="I453" s="26"/>
       <c r="J453" s="26"/>
@@ -14798,8 +16557,12 @@
       <c r="C454" s="34"/>
       <c r="D454" s="34"/>
       <c r="E454" s="34"/>
-      <c r="F454" s="27"/>
-      <c r="G454" s="27"/>
+      <c r="F454" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G454" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H454" s="26"/>
       <c r="I454" s="26"/>
       <c r="J454" s="26"/>
@@ -14824,7 +16587,7 @@
     </row>
     <row r="455" s="25" customFormat="true" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A455" s="24" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B455" s="24"/>
       <c r="C455" s="24"/>
@@ -14848,8 +16611,12 @@
       <c r="C456" s="34"/>
       <c r="D456" s="34"/>
       <c r="E456" s="34"/>
-      <c r="F456" s="27"/>
-      <c r="G456" s="27"/>
+      <c r="F456" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G456" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H456" s="26"/>
       <c r="I456" s="26"/>
       <c r="J456" s="26"/>
@@ -14878,8 +16645,12 @@
       <c r="C457" s="34"/>
       <c r="D457" s="34"/>
       <c r="E457" s="34"/>
-      <c r="F457" s="27"/>
-      <c r="G457" s="27"/>
+      <c r="F457" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G457" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H457" s="26"/>
       <c r="I457" s="26"/>
       <c r="J457" s="26"/>
@@ -14908,8 +16679,12 @@
       <c r="C458" s="34"/>
       <c r="D458" s="34"/>
       <c r="E458" s="34"/>
-      <c r="F458" s="27"/>
-      <c r="G458" s="27"/>
+      <c r="F458" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G458" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H458" s="26"/>
       <c r="I458" s="26"/>
       <c r="J458" s="26"/>
@@ -14938,8 +16713,12 @@
       <c r="C459" s="34"/>
       <c r="D459" s="34"/>
       <c r="E459" s="34"/>
-      <c r="F459" s="27"/>
-      <c r="G459" s="27"/>
+      <c r="F459" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G459" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H459" s="26"/>
       <c r="I459" s="26"/>
       <c r="J459" s="26"/>
@@ -14968,8 +16747,12 @@
       <c r="C460" s="34"/>
       <c r="D460" s="34"/>
       <c r="E460" s="34"/>
-      <c r="F460" s="27"/>
-      <c r="G460" s="27"/>
+      <c r="F460" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G460" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H460" s="26"/>
       <c r="I460" s="26"/>
       <c r="J460" s="26"/>
@@ -14998,8 +16781,12 @@
       <c r="C461" s="34"/>
       <c r="D461" s="34"/>
       <c r="E461" s="34"/>
-      <c r="F461" s="27"/>
-      <c r="G461" s="27"/>
+      <c r="F461" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G461" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H461" s="26"/>
       <c r="I461" s="26"/>
       <c r="J461" s="26"/>
@@ -15016,8 +16803,12 @@
       <c r="C462" s="34"/>
       <c r="D462" s="34"/>
       <c r="E462" s="34"/>
-      <c r="F462" s="27"/>
-      <c r="G462" s="27"/>
+      <c r="F462" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G462" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H462" s="26"/>
       <c r="I462" s="26"/>
       <c r="J462" s="26"/>
@@ -15034,8 +16825,12 @@
       <c r="C463" s="34"/>
       <c r="D463" s="34"/>
       <c r="E463" s="34"/>
-      <c r="F463" s="27"/>
-      <c r="G463" s="27"/>
+      <c r="F463" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G463" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H463" s="26"/>
       <c r="I463" s="26"/>
       <c r="J463" s="26"/>
@@ -15052,8 +16847,12 @@
       <c r="C464" s="34"/>
       <c r="D464" s="34"/>
       <c r="E464" s="34"/>
-      <c r="F464" s="27"/>
-      <c r="G464" s="27"/>
+      <c r="F464" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G464" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H464" s="26"/>
       <c r="I464" s="26"/>
       <c r="J464" s="26"/>
@@ -15070,8 +16869,12 @@
       <c r="C465" s="34"/>
       <c r="D465" s="34"/>
       <c r="E465" s="34"/>
-      <c r="F465" s="27"/>
-      <c r="G465" s="27"/>
+      <c r="F465" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G465" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H465" s="26"/>
       <c r="I465" s="26"/>
       <c r="J465" s="26"/>
@@ -15088,8 +16891,12 @@
       <c r="C466" s="34"/>
       <c r="D466" s="34"/>
       <c r="E466" s="34"/>
-      <c r="F466" s="27"/>
-      <c r="G466" s="27"/>
+      <c r="F466" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G466" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H466" s="26"/>
       <c r="I466" s="26"/>
       <c r="J466" s="26"/>
@@ -15106,8 +16913,12 @@
       <c r="C467" s="34"/>
       <c r="D467" s="34"/>
       <c r="E467" s="34"/>
-      <c r="F467" s="27"/>
-      <c r="G467" s="27"/>
+      <c r="F467" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G467" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H467" s="26"/>
       <c r="I467" s="26"/>
       <c r="J467" s="26"/>
@@ -15124,8 +16935,12 @@
       <c r="C468" s="34"/>
       <c r="D468" s="34"/>
       <c r="E468" s="34"/>
-      <c r="F468" s="27"/>
-      <c r="G468" s="27"/>
+      <c r="F468" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G468" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H468" s="26"/>
       <c r="I468" s="26"/>
       <c r="J468" s="26"/>
@@ -15142,8 +16957,12 @@
       <c r="C469" s="34"/>
       <c r="D469" s="34"/>
       <c r="E469" s="34"/>
-      <c r="F469" s="27"/>
-      <c r="G469" s="27"/>
+      <c r="F469" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G469" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H469" s="26"/>
       <c r="I469" s="26"/>
       <c r="J469" s="26"/>
@@ -15160,8 +16979,12 @@
       <c r="C470" s="34"/>
       <c r="D470" s="34"/>
       <c r="E470" s="34"/>
-      <c r="F470" s="27"/>
-      <c r="G470" s="27"/>
+      <c r="F470" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G470" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H470" s="26"/>
       <c r="I470" s="26"/>
       <c r="J470" s="26"/>
@@ -15178,8 +17001,12 @@
       <c r="C471" s="34"/>
       <c r="D471" s="34"/>
       <c r="E471" s="34"/>
-      <c r="F471" s="27"/>
-      <c r="G471" s="27"/>
+      <c r="F471" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G471" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H471" s="26"/>
       <c r="I471" s="26"/>
       <c r="J471" s="26"/>
@@ -15196,8 +17023,12 @@
       <c r="C472" s="34"/>
       <c r="D472" s="34"/>
       <c r="E472" s="34"/>
-      <c r="F472" s="27"/>
-      <c r="G472" s="27"/>
+      <c r="F472" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G472" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H472" s="26"/>
       <c r="I472" s="26"/>
       <c r="J472" s="26"/>
@@ -15214,8 +17045,12 @@
       <c r="C473" s="34"/>
       <c r="D473" s="34"/>
       <c r="E473" s="34"/>
-      <c r="F473" s="27"/>
-      <c r="G473" s="27"/>
+      <c r="F473" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G473" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H473" s="26"/>
       <c r="I473" s="26"/>
       <c r="J473" s="26"/>
@@ -15232,8 +17067,12 @@
       <c r="C474" s="34"/>
       <c r="D474" s="34"/>
       <c r="E474" s="34"/>
-      <c r="F474" s="27"/>
-      <c r="G474" s="27"/>
+      <c r="F474" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G474" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H474" s="26"/>
       <c r="I474" s="26"/>
       <c r="J474" s="26"/>
@@ -15250,8 +17089,12 @@
       <c r="C475" s="34"/>
       <c r="D475" s="34"/>
       <c r="E475" s="34"/>
-      <c r="F475" s="27"/>
-      <c r="G475" s="27"/>
+      <c r="F475" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G475" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H475" s="26"/>
       <c r="I475" s="26"/>
       <c r="J475" s="26"/>
@@ -15268,8 +17111,12 @@
       <c r="C476" s="34"/>
       <c r="D476" s="34"/>
       <c r="E476" s="34"/>
-      <c r="F476" s="27"/>
-      <c r="G476" s="27"/>
+      <c r="F476" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G476" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H476" s="26"/>
       <c r="I476" s="26"/>
       <c r="J476" s="26"/>
@@ -15286,8 +17133,12 @@
       <c r="C477" s="34"/>
       <c r="D477" s="34"/>
       <c r="E477" s="34"/>
-      <c r="F477" s="27"/>
-      <c r="G477" s="27"/>
+      <c r="F477" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G477" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H477" s="26"/>
       <c r="I477" s="26"/>
       <c r="J477" s="26"/>
@@ -15304,8 +17155,12 @@
       <c r="C478" s="34"/>
       <c r="D478" s="34"/>
       <c r="E478" s="34"/>
-      <c r="F478" s="27"/>
-      <c r="G478" s="27"/>
+      <c r="F478" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G478" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H478" s="26"/>
       <c r="I478" s="26"/>
       <c r="J478" s="26"/>
@@ -15322,8 +17177,12 @@
       <c r="C479" s="34"/>
       <c r="D479" s="34"/>
       <c r="E479" s="34"/>
-      <c r="F479" s="27"/>
-      <c r="G479" s="27"/>
+      <c r="F479" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G479" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H479" s="26"/>
       <c r="I479" s="26"/>
       <c r="J479" s="26"/>
@@ -15340,8 +17199,12 @@
       <c r="C480" s="34"/>
       <c r="D480" s="34"/>
       <c r="E480" s="34"/>
-      <c r="F480" s="27"/>
-      <c r="G480" s="27"/>
+      <c r="F480" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G480" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H480" s="26"/>
       <c r="I480" s="26"/>
       <c r="J480" s="26"/>
@@ -15358,8 +17221,12 @@
       <c r="C481" s="34"/>
       <c r="D481" s="34"/>
       <c r="E481" s="34"/>
-      <c r="F481" s="27"/>
-      <c r="G481" s="27"/>
+      <c r="F481" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G481" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H481" s="26"/>
       <c r="I481" s="26"/>
       <c r="J481" s="26"/>
@@ -15376,8 +17243,12 @@
       <c r="C482" s="34"/>
       <c r="D482" s="34"/>
       <c r="E482" s="34"/>
-      <c r="F482" s="27"/>
-      <c r="G482" s="27"/>
+      <c r="F482" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G482" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H482" s="26"/>
       <c r="I482" s="26"/>
       <c r="J482" s="26"/>
@@ -15394,8 +17265,12 @@
       <c r="C483" s="34"/>
       <c r="D483" s="34"/>
       <c r="E483" s="34"/>
-      <c r="F483" s="27"/>
-      <c r="G483" s="27"/>
+      <c r="F483" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G483" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H483" s="26"/>
       <c r="I483" s="26"/>
       <c r="J483" s="26"/>
@@ -15412,8 +17287,12 @@
       <c r="C484" s="34"/>
       <c r="D484" s="34"/>
       <c r="E484" s="34"/>
-      <c r="F484" s="27"/>
-      <c r="G484" s="27"/>
+      <c r="F484" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G484" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H484" s="26"/>
       <c r="I484" s="26"/>
       <c r="J484" s="26"/>
@@ -15430,8 +17309,12 @@
       <c r="C485" s="34"/>
       <c r="D485" s="34"/>
       <c r="E485" s="34"/>
-      <c r="F485" s="27"/>
-      <c r="G485" s="27"/>
+      <c r="F485" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G485" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H485" s="26"/>
       <c r="I485" s="26"/>
       <c r="J485" s="26"/>
@@ -15448,8 +17331,12 @@
       <c r="C486" s="34"/>
       <c r="D486" s="34"/>
       <c r="E486" s="34"/>
-      <c r="F486" s="27"/>
-      <c r="G486" s="27"/>
+      <c r="F486" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G486" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H486" s="26"/>
       <c r="I486" s="26"/>
       <c r="J486" s="26"/>
@@ -15466,8 +17353,12 @@
       <c r="C487" s="34"/>
       <c r="D487" s="34"/>
       <c r="E487" s="34"/>
-      <c r="F487" s="27"/>
-      <c r="G487" s="27"/>
+      <c r="F487" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G487" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H487" s="26"/>
       <c r="I487" s="26"/>
       <c r="J487" s="26"/>
@@ -15484,8 +17375,12 @@
       <c r="C488" s="34"/>
       <c r="D488" s="34"/>
       <c r="E488" s="34"/>
-      <c r="F488" s="27"/>
-      <c r="G488" s="27"/>
+      <c r="F488" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G488" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H488" s="26"/>
       <c r="I488" s="26"/>
       <c r="J488" s="26"/>
@@ -15502,8 +17397,12 @@
       <c r="C489" s="34"/>
       <c r="D489" s="34"/>
       <c r="E489" s="34"/>
-      <c r="F489" s="27"/>
-      <c r="G489" s="27"/>
+      <c r="F489" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G489" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H489" s="26"/>
       <c r="I489" s="26"/>
       <c r="J489" s="26"/>
@@ -15520,8 +17419,12 @@
       <c r="C490" s="34"/>
       <c r="D490" s="34"/>
       <c r="E490" s="34"/>
-      <c r="F490" s="27"/>
-      <c r="G490" s="27"/>
+      <c r="F490" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G490" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H490" s="26"/>
       <c r="I490" s="26"/>
       <c r="J490" s="26"/>
@@ -15538,8 +17441,12 @@
       <c r="C491" s="34"/>
       <c r="D491" s="34"/>
       <c r="E491" s="34"/>
-      <c r="F491" s="27"/>
-      <c r="G491" s="27"/>
+      <c r="F491" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G491" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H491" s="26"/>
       <c r="I491" s="26"/>
       <c r="J491" s="26"/>
@@ -15556,8 +17463,12 @@
       <c r="C492" s="34"/>
       <c r="D492" s="34"/>
       <c r="E492" s="34"/>
-      <c r="F492" s="27"/>
-      <c r="G492" s="27"/>
+      <c r="F492" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G492" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H492" s="26"/>
       <c r="I492" s="26"/>
       <c r="J492" s="26"/>
@@ -15574,8 +17485,12 @@
       <c r="C493" s="34"/>
       <c r="D493" s="34"/>
       <c r="E493" s="34"/>
-      <c r="F493" s="27"/>
-      <c r="G493" s="27"/>
+      <c r="F493" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G493" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H493" s="26"/>
       <c r="I493" s="26"/>
       <c r="J493" s="26"/>
@@ -15604,8 +17519,12 @@
       <c r="C494" s="34"/>
       <c r="D494" s="34"/>
       <c r="E494" s="34"/>
-      <c r="F494" s="27"/>
-      <c r="G494" s="27"/>
+      <c r="F494" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G494" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H494" s="26"/>
       <c r="I494" s="26"/>
       <c r="J494" s="26"/>
@@ -15634,8 +17553,12 @@
       <c r="C495" s="34"/>
       <c r="D495" s="34"/>
       <c r="E495" s="34"/>
-      <c r="F495" s="27"/>
-      <c r="G495" s="27"/>
+      <c r="F495" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G495" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H495" s="26"/>
       <c r="I495" s="26"/>
       <c r="J495" s="26"/>
@@ -15664,8 +17587,12 @@
       <c r="C496" s="34"/>
       <c r="D496" s="34"/>
       <c r="E496" s="34"/>
-      <c r="F496" s="27"/>
-      <c r="G496" s="27"/>
+      <c r="F496" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G496" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H496" s="26"/>
       <c r="I496" s="26"/>
       <c r="J496" s="26"/>
@@ -15694,8 +17621,12 @@
       <c r="C497" s="34"/>
       <c r="D497" s="34"/>
       <c r="E497" s="34"/>
-      <c r="F497" s="27"/>
-      <c r="G497" s="27"/>
+      <c r="F497" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G497" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H497" s="26"/>
       <c r="I497" s="26"/>
       <c r="J497" s="26"/>
@@ -15720,7 +17651,7 @@
     </row>
     <row r="498" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A498" s="24" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B498" s="24"/>
       <c r="C498" s="24"/>
@@ -15744,8 +17675,12 @@
       <c r="C499" s="26"/>
       <c r="D499" s="26"/>
       <c r="E499" s="26"/>
-      <c r="F499" s="27"/>
-      <c r="G499" s="27"/>
+      <c r="F499" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G499" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H499" s="26"/>
       <c r="I499" s="28"/>
       <c r="J499" s="26"/>
@@ -15774,8 +17709,12 @@
       <c r="C500" s="34"/>
       <c r="D500" s="34"/>
       <c r="E500" s="34"/>
-      <c r="F500" s="27"/>
-      <c r="G500" s="27"/>
+      <c r="F500" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G500" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H500" s="26"/>
       <c r="I500" s="26"/>
       <c r="J500" s="26"/>
@@ -15792,8 +17731,12 @@
       <c r="C501" s="34"/>
       <c r="D501" s="34"/>
       <c r="E501" s="34"/>
-      <c r="F501" s="27"/>
-      <c r="G501" s="27"/>
+      <c r="F501" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G501" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H501" s="26"/>
       <c r="I501" s="26"/>
       <c r="J501" s="26"/>
@@ -15810,8 +17753,12 @@
       <c r="C502" s="34"/>
       <c r="D502" s="34"/>
       <c r="E502" s="34"/>
-      <c r="F502" s="27"/>
-      <c r="G502" s="27"/>
+      <c r="F502" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G502" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H502" s="26"/>
       <c r="I502" s="26"/>
       <c r="J502" s="26"/>
@@ -15828,8 +17775,12 @@
       <c r="C503" s="34"/>
       <c r="D503" s="34"/>
       <c r="E503" s="34"/>
-      <c r="F503" s="27"/>
-      <c r="G503" s="27"/>
+      <c r="F503" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G503" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H503" s="26"/>
       <c r="I503" s="26"/>
       <c r="J503" s="26"/>
@@ -15846,8 +17797,12 @@
       <c r="C504" s="34"/>
       <c r="D504" s="34"/>
       <c r="E504" s="34"/>
-      <c r="F504" s="27"/>
-      <c r="G504" s="27"/>
+      <c r="F504" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G504" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H504" s="26"/>
       <c r="I504" s="26"/>
       <c r="J504" s="26"/>
@@ -15864,8 +17819,12 @@
       <c r="C505" s="34"/>
       <c r="D505" s="34"/>
       <c r="E505" s="34"/>
-      <c r="F505" s="27"/>
-      <c r="G505" s="27"/>
+      <c r="F505" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G505" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H505" s="26"/>
       <c r="I505" s="26"/>
       <c r="J505" s="26"/>
@@ -15882,8 +17841,12 @@
       <c r="C506" s="34"/>
       <c r="D506" s="34"/>
       <c r="E506" s="34"/>
-      <c r="F506" s="27"/>
-      <c r="G506" s="27"/>
+      <c r="F506" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G506" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H506" s="26"/>
       <c r="I506" s="26"/>
       <c r="J506" s="26"/>
@@ -15900,8 +17863,12 @@
       <c r="C507" s="34"/>
       <c r="D507" s="34"/>
       <c r="E507" s="34"/>
-      <c r="F507" s="27"/>
-      <c r="G507" s="27"/>
+      <c r="F507" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G507" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H507" s="26"/>
       <c r="I507" s="26"/>
       <c r="J507" s="26"/>
@@ -15918,8 +17885,12 @@
       <c r="C508" s="34"/>
       <c r="D508" s="34"/>
       <c r="E508" s="34"/>
-      <c r="F508" s="27"/>
-      <c r="G508" s="27"/>
+      <c r="F508" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G508" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H508" s="26"/>
       <c r="I508" s="26"/>
       <c r="J508" s="26"/>
@@ -15932,7 +17903,7 @@
     </row>
     <row r="509" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A509" s="24" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B509" s="24"/>
       <c r="C509" s="24"/>
@@ -15956,8 +17927,12 @@
       <c r="C510" s="26"/>
       <c r="D510" s="26"/>
       <c r="E510" s="26"/>
-      <c r="F510" s="27"/>
-      <c r="G510" s="27"/>
+      <c r="F510" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G510" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H510" s="26"/>
       <c r="I510" s="28"/>
       <c r="J510" s="26"/>
@@ -15986,8 +17961,12 @@
       <c r="C511" s="34"/>
       <c r="D511" s="34"/>
       <c r="E511" s="34"/>
-      <c r="F511" s="27"/>
-      <c r="G511" s="27"/>
+      <c r="F511" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G511" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H511" s="26"/>
       <c r="I511" s="26"/>
       <c r="J511" s="26"/>
@@ -16004,8 +17983,12 @@
       <c r="C512" s="34"/>
       <c r="D512" s="34"/>
       <c r="E512" s="34"/>
-      <c r="F512" s="27"/>
-      <c r="G512" s="27"/>
+      <c r="F512" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G512" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H512" s="26"/>
       <c r="I512" s="26"/>
       <c r="J512" s="26"/>
@@ -16022,8 +18005,12 @@
       <c r="C513" s="34"/>
       <c r="D513" s="34"/>
       <c r="E513" s="34"/>
-      <c r="F513" s="27"/>
-      <c r="G513" s="27"/>
+      <c r="F513" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G513" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H513" s="26"/>
       <c r="I513" s="26"/>
       <c r="J513" s="26"/>
@@ -16040,8 +18027,12 @@
       <c r="C514" s="34"/>
       <c r="D514" s="34"/>
       <c r="E514" s="34"/>
-      <c r="F514" s="27"/>
-      <c r="G514" s="27"/>
+      <c r="F514" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G514" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H514" s="26"/>
       <c r="I514" s="26"/>
       <c r="J514" s="26"/>
@@ -16058,8 +18049,12 @@
       <c r="C515" s="34"/>
       <c r="D515" s="34"/>
       <c r="E515" s="34"/>
-      <c r="F515" s="27"/>
-      <c r="G515" s="27"/>
+      <c r="F515" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G515" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H515" s="26"/>
       <c r="I515" s="26"/>
       <c r="J515" s="26"/>
@@ -16076,8 +18071,12 @@
       <c r="C516" s="34"/>
       <c r="D516" s="34"/>
       <c r="E516" s="34"/>
-      <c r="F516" s="27"/>
-      <c r="G516" s="27"/>
+      <c r="F516" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G516" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H516" s="26"/>
       <c r="I516" s="26"/>
       <c r="J516" s="26"/>
@@ -16094,8 +18093,12 @@
       <c r="C517" s="34"/>
       <c r="D517" s="34"/>
       <c r="E517" s="34"/>
-      <c r="F517" s="27"/>
-      <c r="G517" s="27"/>
+      <c r="F517" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G517" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H517" s="26"/>
       <c r="I517" s="26"/>
       <c r="J517" s="26"/>
@@ -16112,8 +18115,12 @@
       <c r="C518" s="34"/>
       <c r="D518" s="34"/>
       <c r="E518" s="34"/>
-      <c r="F518" s="27"/>
-      <c r="G518" s="27"/>
+      <c r="F518" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G518" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H518" s="26"/>
       <c r="I518" s="26"/>
       <c r="J518" s="26"/>
@@ -16130,8 +18137,12 @@
       <c r="C519" s="34"/>
       <c r="D519" s="34"/>
       <c r="E519" s="34"/>
-      <c r="F519" s="27"/>
-      <c r="G519" s="27"/>
+      <c r="F519" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G519" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="H519" s="26"/>
       <c r="I519" s="26"/>
       <c r="J519" s="26"/>
@@ -16143,8 +18154,12 @@
       <c r="P519" s="26"/>
     </row>
     <row r="520" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="F520" s="27"/>
-      <c r="G520" s="27"/>
+      <c r="F520" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G520" s="27" t="s">
+        <v>69</v>
+      </c>
     </row>
     <row r="521" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A521" s="35" t="s">
@@ -16181,12 +18196,12 @@
     </row>
     <row r="523" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A523" s="38" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="524" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A524" s="38" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
   </sheetData>
@@ -16229,12 +18244,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16245,7 +18260,7 @@
         <v>36</v>
       </c>
       <c r="C4" s="12" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D4" s="12" t="s">
         <v>37</v>
@@ -16266,18 +18281,18 @@
         <v>42</v>
       </c>
       <c r="J4" s="12" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K4" s="12" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="8" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C5" s="14" t="n">
         <f aca="false">COUNTIF('Count Sheet'!$A$5:$A$160,$A5)</f>
@@ -16318,10 +18333,10 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="8" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C6" s="14" t="n">
         <f aca="false">COUNTIF('Count Sheet'!$A$5:$A$160,$A6)</f>
@@ -16362,10 +18377,10 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="8" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C7" s="14" t="n">
         <f aca="false">COUNTIF('Count Sheet'!$A$5:$A$160,$A7)</f>
@@ -16406,10 +18421,10 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="8" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C8" s="14" t="n">
         <f aca="false">COUNTIF('Count Sheet'!$A$5:$A$160,$A8)</f>
@@ -16494,10 +18509,10 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="8" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C10" s="14" t="n">
         <f aca="false">COUNTIF('Count Sheet'!$A$5:$A$160,$A10)</f>
@@ -16538,10 +18553,10 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="8" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C11" s="14" t="n">
         <f aca="false">COUNTIF('Count Sheet'!$A$5:$A$160,$A11)</f>
@@ -16582,10 +18597,10 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="8" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C12" s="14" t="n">
         <f aca="false">COUNTIF('Count Sheet'!$A$5:$A$160,$A12)</f>
@@ -16626,10 +18641,10 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="8" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C13" s="14" t="n">
         <f aca="false">COUNTIF('Count Sheet'!$A$5:$A$160,$A13)</f>
@@ -16670,10 +18685,10 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="8" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C14" s="14" t="n">
         <f aca="false">COUNTIF('Count Sheet'!$A$5:$A$160,$A14)</f>
@@ -16714,10 +18729,10 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="8" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C15" s="14" t="n">
         <f aca="false">COUNTIF('Count Sheet'!$A$5:$A$160,$A15)</f>
@@ -16758,10 +18773,10 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="8" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C16" s="14" t="n">
         <f aca="false">COUNTIF('Count Sheet'!$A$5:$A$160,$A16)</f>
@@ -16802,10 +18817,10 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="8" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C17" s="14" t="n">
         <f aca="false">COUNTIF('Count Sheet'!$A$5:$A$160,$A17)</f>
@@ -16846,10 +18861,10 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="8" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C18" s="14" t="n">
         <f aca="false">COUNTIF('Count Sheet'!$A$5:$A$160,$A18)</f>
@@ -16929,17 +18944,17 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="45" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="45" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="45" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
   </sheetData>

--- a/public/templates/inventory-count-template.xlsx
+++ b/public/templates/inventory-count-template.xlsx
@@ -27,7 +27,7 @@
     <numFmt numFmtId="165" formatCode="#,##0.000"/>
     <numFmt numFmtId="166" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="21">
     <font>
       <name val="Calibri"/>
       <charset val="1"/>
@@ -171,8 +171,14 @@
       <color rgb="FF595959"/>
       <sz val="9"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="FF1F3B2C"/>
+      <sz val="16"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -209,8 +215,18 @@
         <bgColor rgb="FFEDE7DC"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4CCCC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD9EAD3"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -248,6 +264,20 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB0B0B0"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB0B0B0"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB0B0B0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB0B0B0"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
@@ -259,7 +289,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="92">
+  <cellXfs count="94">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -533,6 +563,12 @@
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -1293,7 +1329,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:N161"/>
+  <dimension ref="A1:P161"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.66796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="18" customWidth="1" style="46" min="1" max="1"/>
@@ -1304,7 +1340,8 @@
     <col width="10" customWidth="1" style="46" min="6" max="6"/>
     <col width="15" customWidth="1" style="46" min="7" max="7"/>
     <col width="10" customWidth="1" style="46" min="8" max="8"/>
-    <col width="11" customWidth="1" style="46" min="9" max="10"/>
+    <col width="9" customWidth="1" style="46" min="9" max="10"/>
+    <col width="11" customWidth="1" style="47" min="10" max="10"/>
     <col width="10" customWidth="1" style="46" min="11" max="11"/>
     <col width="9" customWidth="1" style="46" min="12" max="12"/>
     <col width="18" customWidth="1" style="46" min="13" max="13"/>
@@ -1368,30 +1405,40 @@
       </c>
       <c r="I4" s="58" t="inlineStr">
         <is>
+          <t>Out</t>
+        </is>
+      </c>
+      <c r="J4" s="58" t="inlineStr">
+        <is>
+          <t>New Count</t>
+        </is>
+      </c>
+      <c r="K4" s="58" t="inlineStr">
+        <is>
           <t>Counted kg</t>
         </is>
       </c>
-      <c r="J4" s="58" t="inlineStr">
+      <c r="L4" s="58" t="inlineStr">
         <is>
           <t>Counted pcs</t>
         </is>
       </c>
-      <c r="K4" s="58" t="inlineStr">
+      <c r="M4" s="58" t="inlineStr">
         <is>
           <t>Var kg</t>
         </is>
       </c>
-      <c r="L4" s="58" t="inlineStr">
+      <c r="N4" s="58" t="inlineStr">
         <is>
           <t>Var pcs</t>
         </is>
       </c>
-      <c r="M4" s="58" t="inlineStr">
+      <c r="O4" s="58" t="inlineStr">
         <is>
           <t>Reason</t>
         </is>
       </c>
-      <c r="N4" s="58" t="inlineStr">
+      <c r="P4" s="58" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
@@ -1405,18 +1452,20 @@
       <c r="E5" s="59" t="n"/>
       <c r="F5" s="60" t="n"/>
       <c r="G5" s="54" t="n"/>
-      <c r="I5" s="61" t="n"/>
-      <c r="J5" s="62" t="n"/>
-      <c r="K5" s="59">
-        <f>IF(I5="","",ROUND(I5-E5,2))</f>
-        <v/>
-      </c>
-      <c r="L5" s="60">
-        <f>IF(J5="","",J5-F5)</f>
-        <v/>
-      </c>
-      <c r="M5" s="56" t="n"/>
-      <c r="N5" s="56" t="n"/>
+      <c r="I5" s="92" t="n"/>
+      <c r="J5" s="93" t="n"/>
+      <c r="K5" s="61" t="n"/>
+      <c r="L5" s="62" t="n"/>
+      <c r="M5" s="59">
+        <f>IF(K5="","",ROUND(K5-E5,2))</f>
+        <v/>
+      </c>
+      <c r="N5" s="60">
+        <f>IF(L5="","",L5-F5)</f>
+        <v/>
+      </c>
+      <c r="O5" s="56" t="n"/>
+      <c r="P5" s="56" t="n"/>
     </row>
     <row r="6" ht="15" customHeight="1" s="47">
       <c r="A6" s="54" t="n"/>
@@ -1426,18 +1475,20 @@
       <c r="E6" s="59" t="n"/>
       <c r="F6" s="60" t="n"/>
       <c r="G6" s="54" t="n"/>
-      <c r="I6" s="61" t="n"/>
-      <c r="J6" s="62" t="n"/>
-      <c r="K6" s="59">
+      <c r="I6" s="92" t="n"/>
+      <c r="J6" s="93" t="n"/>
+      <c r="K6" s="61" t="n"/>
+      <c r="L6" s="62" t="n"/>
+      <c r="M6" s="59">
         <f>IF(I6="","",ROUND(I6-E6,2))</f>
         <v/>
       </c>
-      <c r="L6" s="60">
+      <c r="N6" s="60">
         <f>IF(J6="","",J6-F6)</f>
         <v/>
       </c>
-      <c r="M6" s="56" t="n"/>
-      <c r="N6" s="56" t="n"/>
+      <c r="O6" s="56" t="n"/>
+      <c r="P6" s="56" t="n"/>
     </row>
     <row r="7" ht="15" customHeight="1" s="47">
       <c r="A7" s="54" t="n"/>
@@ -1447,18 +1498,20 @@
       <c r="E7" s="59" t="n"/>
       <c r="F7" s="60" t="n"/>
       <c r="G7" s="54" t="n"/>
-      <c r="I7" s="61" t="n"/>
-      <c r="J7" s="62" t="n"/>
-      <c r="K7" s="59">
+      <c r="I7" s="92" t="n"/>
+      <c r="J7" s="93" t="n"/>
+      <c r="K7" s="61" t="n"/>
+      <c r="L7" s="62" t="n"/>
+      <c r="M7" s="59">
         <f>IF(I7="","",ROUND(I7-E7,2))</f>
         <v/>
       </c>
-      <c r="L7" s="60">
+      <c r="N7" s="60">
         <f>IF(J7="","",J7-F7)</f>
         <v/>
       </c>
-      <c r="M7" s="56" t="n"/>
-      <c r="N7" s="56" t="n"/>
+      <c r="O7" s="56" t="n"/>
+      <c r="P7" s="56" t="n"/>
     </row>
     <row r="8" ht="15" customHeight="1" s="47">
       <c r="A8" s="54" t="n"/>
@@ -1468,18 +1521,20 @@
       <c r="E8" s="59" t="n"/>
       <c r="F8" s="60" t="n"/>
       <c r="G8" s="54" t="n"/>
-      <c r="I8" s="61" t="n"/>
-      <c r="J8" s="62" t="n"/>
-      <c r="K8" s="59">
+      <c r="I8" s="92" t="n"/>
+      <c r="J8" s="93" t="n"/>
+      <c r="K8" s="61" t="n"/>
+      <c r="L8" s="62" t="n"/>
+      <c r="M8" s="59">
         <f>IF(I8="","",ROUND(I8-E8,2))</f>
         <v/>
       </c>
-      <c r="L8" s="60">
+      <c r="N8" s="60">
         <f>IF(J8="","",J8-F8)</f>
         <v/>
       </c>
-      <c r="M8" s="56" t="n"/>
-      <c r="N8" s="56" t="n"/>
+      <c r="O8" s="56" t="n"/>
+      <c r="P8" s="56" t="n"/>
     </row>
     <row r="9" ht="15" customHeight="1" s="47">
       <c r="A9" s="54" t="n"/>
@@ -1489,18 +1544,20 @@
       <c r="E9" s="59" t="n"/>
       <c r="F9" s="60" t="n"/>
       <c r="G9" s="54" t="n"/>
-      <c r="I9" s="61" t="n"/>
-      <c r="J9" s="62" t="n"/>
-      <c r="K9" s="59">
+      <c r="I9" s="92" t="n"/>
+      <c r="J9" s="93" t="n"/>
+      <c r="K9" s="61" t="n"/>
+      <c r="L9" s="62" t="n"/>
+      <c r="M9" s="59">
         <f>IF(I9="","",ROUND(I9-E9,2))</f>
         <v/>
       </c>
-      <c r="L9" s="60">
+      <c r="N9" s="60">
         <f>IF(J9="","",J9-F9)</f>
         <v/>
       </c>
-      <c r="M9" s="56" t="n"/>
-      <c r="N9" s="56" t="n"/>
+      <c r="O9" s="56" t="n"/>
+      <c r="P9" s="56" t="n"/>
     </row>
     <row r="10" ht="15" customHeight="1" s="47">
       <c r="A10" s="54" t="n"/>
@@ -1510,18 +1567,20 @@
       <c r="E10" s="59" t="n"/>
       <c r="F10" s="60" t="n"/>
       <c r="G10" s="54" t="n"/>
-      <c r="I10" s="61" t="n"/>
-      <c r="J10" s="62" t="n"/>
-      <c r="K10" s="59">
+      <c r="I10" s="92" t="n"/>
+      <c r="J10" s="93" t="n"/>
+      <c r="K10" s="61" t="n"/>
+      <c r="L10" s="62" t="n"/>
+      <c r="M10" s="59">
         <f>IF(I10="","",ROUND(I10-E10,2))</f>
         <v/>
       </c>
-      <c r="L10" s="60">
+      <c r="N10" s="60">
         <f>IF(J10="","",J10-F10)</f>
         <v/>
       </c>
-      <c r="M10" s="56" t="n"/>
-      <c r="N10" s="56" t="n"/>
+      <c r="O10" s="56" t="n"/>
+      <c r="P10" s="56" t="n"/>
     </row>
     <row r="11" ht="15" customHeight="1" s="47">
       <c r="A11" s="54" t="n"/>
@@ -1531,18 +1590,20 @@
       <c r="E11" s="59" t="n"/>
       <c r="F11" s="60" t="n"/>
       <c r="G11" s="54" t="n"/>
-      <c r="I11" s="61" t="n"/>
-      <c r="J11" s="62" t="n"/>
-      <c r="K11" s="59">
+      <c r="I11" s="92" t="n"/>
+      <c r="J11" s="93" t="n"/>
+      <c r="K11" s="61" t="n"/>
+      <c r="L11" s="62" t="n"/>
+      <c r="M11" s="59">
         <f>IF(I11="","",ROUND(I11-E11,2))</f>
         <v/>
       </c>
-      <c r="L11" s="60">
+      <c r="N11" s="60">
         <f>IF(J11="","",J11-F11)</f>
         <v/>
       </c>
-      <c r="M11" s="56" t="n"/>
-      <c r="N11" s="56" t="n"/>
+      <c r="O11" s="56" t="n"/>
+      <c r="P11" s="56" t="n"/>
     </row>
     <row r="12" ht="15" customHeight="1" s="47">
       <c r="A12" s="54" t="n"/>
@@ -1552,18 +1613,20 @@
       <c r="E12" s="59" t="n"/>
       <c r="F12" s="60" t="n"/>
       <c r="G12" s="54" t="n"/>
-      <c r="I12" s="61" t="n"/>
-      <c r="J12" s="62" t="n"/>
-      <c r="K12" s="59">
+      <c r="I12" s="92" t="n"/>
+      <c r="J12" s="93" t="n"/>
+      <c r="K12" s="61" t="n"/>
+      <c r="L12" s="62" t="n"/>
+      <c r="M12" s="59">
         <f>IF(I12="","",ROUND(I12-E12,2))</f>
         <v/>
       </c>
-      <c r="L12" s="60">
+      <c r="N12" s="60">
         <f>IF(J12="","",J12-F12)</f>
         <v/>
       </c>
-      <c r="M12" s="56" t="n"/>
-      <c r="N12" s="56" t="n"/>
+      <c r="O12" s="56" t="n"/>
+      <c r="P12" s="56" t="n"/>
     </row>
     <row r="13" ht="15" customHeight="1" s="47">
       <c r="A13" s="54" t="n"/>
@@ -1573,18 +1636,20 @@
       <c r="E13" s="59" t="n"/>
       <c r="F13" s="60" t="n"/>
       <c r="G13" s="54" t="n"/>
-      <c r="I13" s="61" t="n"/>
-      <c r="J13" s="62" t="n"/>
-      <c r="K13" s="59">
+      <c r="I13" s="92" t="n"/>
+      <c r="J13" s="93" t="n"/>
+      <c r="K13" s="61" t="n"/>
+      <c r="L13" s="62" t="n"/>
+      <c r="M13" s="59">
         <f>IF(I13="","",ROUND(I13-E13,2))</f>
         <v/>
       </c>
-      <c r="L13" s="60">
+      <c r="N13" s="60">
         <f>IF(J13="","",J13-F13)</f>
         <v/>
       </c>
-      <c r="M13" s="56" t="n"/>
-      <c r="N13" s="56" t="n"/>
+      <c r="O13" s="56" t="n"/>
+      <c r="P13" s="56" t="n"/>
     </row>
     <row r="14" ht="15" customHeight="1" s="47">
       <c r="A14" s="54" t="n"/>
@@ -1594,18 +1659,20 @@
       <c r="E14" s="59" t="n"/>
       <c r="F14" s="60" t="n"/>
       <c r="G14" s="54" t="n"/>
-      <c r="I14" s="61" t="n"/>
-      <c r="J14" s="62" t="n"/>
-      <c r="K14" s="59">
+      <c r="I14" s="92" t="n"/>
+      <c r="J14" s="93" t="n"/>
+      <c r="K14" s="61" t="n"/>
+      <c r="L14" s="62" t="n"/>
+      <c r="M14" s="59">
         <f>IF(I14="","",ROUND(I14-E14,2))</f>
         <v/>
       </c>
-      <c r="L14" s="60">
+      <c r="N14" s="60">
         <f>IF(J14="","",J14-F14)</f>
         <v/>
       </c>
-      <c r="M14" s="56" t="n"/>
-      <c r="N14" s="56" t="n"/>
+      <c r="O14" s="56" t="n"/>
+      <c r="P14" s="56" t="n"/>
     </row>
     <row r="15" ht="15" customHeight="1" s="47">
       <c r="A15" s="54" t="n"/>
@@ -1615,18 +1682,20 @@
       <c r="E15" s="59" t="n"/>
       <c r="F15" s="60" t="n"/>
       <c r="G15" s="54" t="n"/>
-      <c r="I15" s="61" t="n"/>
-      <c r="J15" s="62" t="n"/>
-      <c r="K15" s="59">
+      <c r="I15" s="92" t="n"/>
+      <c r="J15" s="93" t="n"/>
+      <c r="K15" s="61" t="n"/>
+      <c r="L15" s="62" t="n"/>
+      <c r="M15" s="59">
         <f>IF(I15="","",ROUND(I15-E15,2))</f>
         <v/>
       </c>
-      <c r="L15" s="60">
+      <c r="N15" s="60">
         <f>IF(J15="","",J15-F15)</f>
         <v/>
       </c>
-      <c r="M15" s="56" t="n"/>
-      <c r="N15" s="56" t="n"/>
+      <c r="O15" s="56" t="n"/>
+      <c r="P15" s="56" t="n"/>
     </row>
     <row r="16" ht="15" customHeight="1" s="47">
       <c r="A16" s="54" t="n"/>
@@ -1636,18 +1705,20 @@
       <c r="E16" s="59" t="n"/>
       <c r="F16" s="60" t="n"/>
       <c r="G16" s="54" t="n"/>
-      <c r="I16" s="61" t="n"/>
-      <c r="J16" s="62" t="n"/>
-      <c r="K16" s="59">
+      <c r="I16" s="92" t="n"/>
+      <c r="J16" s="93" t="n"/>
+      <c r="K16" s="61" t="n"/>
+      <c r="L16" s="62" t="n"/>
+      <c r="M16" s="59">
         <f>IF(I16="","",ROUND(I16-E16,2))</f>
         <v/>
       </c>
-      <c r="L16" s="60">
+      <c r="N16" s="60">
         <f>IF(J16="","",J16-F16)</f>
         <v/>
       </c>
-      <c r="M16" s="56" t="n"/>
-      <c r="N16" s="56" t="n"/>
+      <c r="O16" s="56" t="n"/>
+      <c r="P16" s="56" t="n"/>
     </row>
     <row r="17" ht="15" customHeight="1" s="47">
       <c r="A17" s="54" t="n"/>
@@ -1657,18 +1728,20 @@
       <c r="E17" s="59" t="n"/>
       <c r="F17" s="60" t="n"/>
       <c r="G17" s="54" t="n"/>
-      <c r="I17" s="61" t="n"/>
-      <c r="J17" s="62" t="n"/>
-      <c r="K17" s="59">
+      <c r="I17" s="92" t="n"/>
+      <c r="J17" s="93" t="n"/>
+      <c r="K17" s="61" t="n"/>
+      <c r="L17" s="62" t="n"/>
+      <c r="M17" s="59">
         <f>IF(I17="","",ROUND(I17-E17,2))</f>
         <v/>
       </c>
-      <c r="L17" s="60">
+      <c r="N17" s="60">
         <f>IF(J17="","",J17-F17)</f>
         <v/>
       </c>
-      <c r="M17" s="56" t="n"/>
-      <c r="N17" s="56" t="n"/>
+      <c r="O17" s="56" t="n"/>
+      <c r="P17" s="56" t="n"/>
     </row>
     <row r="18" ht="15" customHeight="1" s="47">
       <c r="A18" s="54" t="n"/>
@@ -1678,18 +1751,20 @@
       <c r="E18" s="59" t="n"/>
       <c r="F18" s="60" t="n"/>
       <c r="G18" s="54" t="n"/>
-      <c r="I18" s="61" t="n"/>
-      <c r="J18" s="62" t="n"/>
-      <c r="K18" s="59">
+      <c r="I18" s="92" t="n"/>
+      <c r="J18" s="93" t="n"/>
+      <c r="K18" s="61" t="n"/>
+      <c r="L18" s="62" t="n"/>
+      <c r="M18" s="59">
         <f>IF(I18="","",ROUND(I18-E18,2))</f>
         <v/>
       </c>
-      <c r="L18" s="60">
+      <c r="N18" s="60">
         <f>IF(J18="","",J18-F18)</f>
         <v/>
       </c>
-      <c r="M18" s="56" t="n"/>
-      <c r="N18" s="56" t="n"/>
+      <c r="O18" s="56" t="n"/>
+      <c r="P18" s="56" t="n"/>
     </row>
     <row r="19" ht="15" customHeight="1" s="47">
       <c r="A19" s="54" t="n"/>
@@ -1699,18 +1774,20 @@
       <c r="E19" s="59" t="n"/>
       <c r="F19" s="60" t="n"/>
       <c r="G19" s="54" t="n"/>
-      <c r="I19" s="61" t="n"/>
-      <c r="J19" s="62" t="n"/>
-      <c r="K19" s="59">
+      <c r="I19" s="92" t="n"/>
+      <c r="J19" s="93" t="n"/>
+      <c r="K19" s="61" t="n"/>
+      <c r="L19" s="62" t="n"/>
+      <c r="M19" s="59">
         <f>IF(I19="","",ROUND(I19-E19,2))</f>
         <v/>
       </c>
-      <c r="L19" s="60">
+      <c r="N19" s="60">
         <f>IF(J19="","",J19-F19)</f>
         <v/>
       </c>
-      <c r="M19" s="56" t="n"/>
-      <c r="N19" s="56" t="n"/>
+      <c r="O19" s="56" t="n"/>
+      <c r="P19" s="56" t="n"/>
     </row>
     <row r="20" ht="15" customHeight="1" s="47">
       <c r="A20" s="54" t="n"/>
@@ -1720,18 +1797,20 @@
       <c r="E20" s="59" t="n"/>
       <c r="F20" s="60" t="n"/>
       <c r="G20" s="54" t="n"/>
-      <c r="I20" s="61" t="n"/>
-      <c r="J20" s="62" t="n"/>
-      <c r="K20" s="59">
+      <c r="I20" s="92" t="n"/>
+      <c r="J20" s="93" t="n"/>
+      <c r="K20" s="61" t="n"/>
+      <c r="L20" s="62" t="n"/>
+      <c r="M20" s="59">
         <f>IF(I20="","",ROUND(I20-E20,2))</f>
         <v/>
       </c>
-      <c r="L20" s="60">
+      <c r="N20" s="60">
         <f>IF(J20="","",J20-F20)</f>
         <v/>
       </c>
-      <c r="M20" s="56" t="n"/>
-      <c r="N20" s="56" t="n"/>
+      <c r="O20" s="56" t="n"/>
+      <c r="P20" s="56" t="n"/>
     </row>
     <row r="21" ht="15" customHeight="1" s="47">
       <c r="A21" s="54" t="n"/>
@@ -1741,18 +1820,20 @@
       <c r="E21" s="59" t="n"/>
       <c r="F21" s="60" t="n"/>
       <c r="G21" s="54" t="n"/>
-      <c r="I21" s="61" t="n"/>
-      <c r="J21" s="62" t="n"/>
-      <c r="K21" s="59">
+      <c r="I21" s="92" t="n"/>
+      <c r="J21" s="93" t="n"/>
+      <c r="K21" s="61" t="n"/>
+      <c r="L21" s="62" t="n"/>
+      <c r="M21" s="59">
         <f>IF(I21="","",ROUND(I21-E21,2))</f>
         <v/>
       </c>
-      <c r="L21" s="60">
+      <c r="N21" s="60">
         <f>IF(J21="","",J21-F21)</f>
         <v/>
       </c>
-      <c r="M21" s="56" t="n"/>
-      <c r="N21" s="56" t="n"/>
+      <c r="O21" s="56" t="n"/>
+      <c r="P21" s="56" t="n"/>
     </row>
     <row r="22" ht="15" customHeight="1" s="47">
       <c r="A22" s="54" t="n"/>
@@ -1762,18 +1843,20 @@
       <c r="E22" s="59" t="n"/>
       <c r="F22" s="60" t="n"/>
       <c r="G22" s="54" t="n"/>
-      <c r="I22" s="61" t="n"/>
-      <c r="J22" s="62" t="n"/>
-      <c r="K22" s="59">
+      <c r="I22" s="92" t="n"/>
+      <c r="J22" s="93" t="n"/>
+      <c r="K22" s="61" t="n"/>
+      <c r="L22" s="62" t="n"/>
+      <c r="M22" s="59">
         <f>IF(I22="","",ROUND(I22-E22,2))</f>
         <v/>
       </c>
-      <c r="L22" s="60">
+      <c r="N22" s="60">
         <f>IF(J22="","",J22-F22)</f>
         <v/>
       </c>
-      <c r="M22" s="56" t="n"/>
-      <c r="N22" s="56" t="n"/>
+      <c r="O22" s="56" t="n"/>
+      <c r="P22" s="56" t="n"/>
     </row>
     <row r="23" ht="15" customHeight="1" s="47">
       <c r="A23" s="54" t="n"/>
@@ -1783,18 +1866,20 @@
       <c r="E23" s="59" t="n"/>
       <c r="F23" s="60" t="n"/>
       <c r="G23" s="54" t="n"/>
-      <c r="I23" s="61" t="n"/>
-      <c r="J23" s="62" t="n"/>
-      <c r="K23" s="59">
+      <c r="I23" s="92" t="n"/>
+      <c r="J23" s="93" t="n"/>
+      <c r="K23" s="61" t="n"/>
+      <c r="L23" s="62" t="n"/>
+      <c r="M23" s="59">
         <f>IF(I23="","",ROUND(I23-E23,2))</f>
         <v/>
       </c>
-      <c r="L23" s="60">
+      <c r="N23" s="60">
         <f>IF(J23="","",J23-F23)</f>
         <v/>
       </c>
-      <c r="M23" s="56" t="n"/>
-      <c r="N23" s="56" t="n"/>
+      <c r="O23" s="56" t="n"/>
+      <c r="P23" s="56" t="n"/>
     </row>
     <row r="24" ht="15" customHeight="1" s="47">
       <c r="A24" s="54" t="n"/>
@@ -1804,18 +1889,20 @@
       <c r="E24" s="59" t="n"/>
       <c r="F24" s="60" t="n"/>
       <c r="G24" s="54" t="n"/>
-      <c r="I24" s="61" t="n"/>
-      <c r="J24" s="62" t="n"/>
-      <c r="K24" s="59">
+      <c r="I24" s="92" t="n"/>
+      <c r="J24" s="93" t="n"/>
+      <c r="K24" s="61" t="n"/>
+      <c r="L24" s="62" t="n"/>
+      <c r="M24" s="59">
         <f>IF(I24="","",ROUND(I24-E24,2))</f>
         <v/>
       </c>
-      <c r="L24" s="60">
+      <c r="N24" s="60">
         <f>IF(J24="","",J24-F24)</f>
         <v/>
       </c>
-      <c r="M24" s="56" t="n"/>
-      <c r="N24" s="56" t="n"/>
+      <c r="O24" s="56" t="n"/>
+      <c r="P24" s="56" t="n"/>
     </row>
     <row r="25" ht="15" customHeight="1" s="47">
       <c r="A25" s="54" t="n"/>
@@ -1825,18 +1912,20 @@
       <c r="E25" s="59" t="n"/>
       <c r="F25" s="60" t="n"/>
       <c r="G25" s="54" t="n"/>
-      <c r="I25" s="61" t="n"/>
-      <c r="J25" s="62" t="n"/>
-      <c r="K25" s="59">
+      <c r="I25" s="92" t="n"/>
+      <c r="J25" s="93" t="n"/>
+      <c r="K25" s="61" t="n"/>
+      <c r="L25" s="62" t="n"/>
+      <c r="M25" s="59">
         <f>IF(I25="","",ROUND(I25-E25,2))</f>
         <v/>
       </c>
-      <c r="L25" s="60">
+      <c r="N25" s="60">
         <f>IF(J25="","",J25-F25)</f>
         <v/>
       </c>
-      <c r="M25" s="56" t="n"/>
-      <c r="N25" s="56" t="n"/>
+      <c r="O25" s="56" t="n"/>
+      <c r="P25" s="56" t="n"/>
     </row>
     <row r="26" ht="15" customHeight="1" s="47">
       <c r="A26" s="54" t="n"/>
@@ -1846,18 +1935,20 @@
       <c r="E26" s="59" t="n"/>
       <c r="F26" s="60" t="n"/>
       <c r="G26" s="54" t="n"/>
-      <c r="I26" s="61" t="n"/>
-      <c r="J26" s="62" t="n"/>
-      <c r="K26" s="59">
+      <c r="I26" s="92" t="n"/>
+      <c r="J26" s="93" t="n"/>
+      <c r="K26" s="61" t="n"/>
+      <c r="L26" s="62" t="n"/>
+      <c r="M26" s="59">
         <f>IF(I26="","",ROUND(I26-E26,2))</f>
         <v/>
       </c>
-      <c r="L26" s="60">
+      <c r="N26" s="60">
         <f>IF(J26="","",J26-F26)</f>
         <v/>
       </c>
-      <c r="M26" s="56" t="n"/>
-      <c r="N26" s="56" t="n"/>
+      <c r="O26" s="56" t="n"/>
+      <c r="P26" s="56" t="n"/>
     </row>
     <row r="27" ht="15" customHeight="1" s="47">
       <c r="A27" s="54" t="n"/>
@@ -1867,18 +1958,20 @@
       <c r="E27" s="59" t="n"/>
       <c r="F27" s="60" t="n"/>
       <c r="G27" s="54" t="n"/>
-      <c r="I27" s="61" t="n"/>
-      <c r="J27" s="62" t="n"/>
-      <c r="K27" s="59">
+      <c r="I27" s="92" t="n"/>
+      <c r="J27" s="93" t="n"/>
+      <c r="K27" s="61" t="n"/>
+      <c r="L27" s="62" t="n"/>
+      <c r="M27" s="59">
         <f>IF(I27="","",ROUND(I27-E27,2))</f>
         <v/>
       </c>
-      <c r="L27" s="60">
+      <c r="N27" s="60">
         <f>IF(J27="","",J27-F27)</f>
         <v/>
       </c>
-      <c r="M27" s="56" t="n"/>
-      <c r="N27" s="56" t="n"/>
+      <c r="O27" s="56" t="n"/>
+      <c r="P27" s="56" t="n"/>
     </row>
     <row r="28" ht="15" customHeight="1" s="47">
       <c r="A28" s="54" t="n"/>
@@ -1888,18 +1981,20 @@
       <c r="E28" s="59" t="n"/>
       <c r="F28" s="60" t="n"/>
       <c r="G28" s="54" t="n"/>
-      <c r="I28" s="61" t="n"/>
-      <c r="J28" s="62" t="n"/>
-      <c r="K28" s="59">
+      <c r="I28" s="92" t="n"/>
+      <c r="J28" s="93" t="n"/>
+      <c r="K28" s="61" t="n"/>
+      <c r="L28" s="62" t="n"/>
+      <c r="M28" s="59">
         <f>IF(I28="","",ROUND(I28-E28,2))</f>
         <v/>
       </c>
-      <c r="L28" s="60">
+      <c r="N28" s="60">
         <f>IF(J28="","",J28-F28)</f>
         <v/>
       </c>
-      <c r="M28" s="56" t="n"/>
-      <c r="N28" s="56" t="n"/>
+      <c r="O28" s="56" t="n"/>
+      <c r="P28" s="56" t="n"/>
     </row>
     <row r="29" ht="15" customHeight="1" s="47">
       <c r="A29" s="54" t="n"/>
@@ -1909,18 +2004,20 @@
       <c r="E29" s="59" t="n"/>
       <c r="F29" s="60" t="n"/>
       <c r="G29" s="54" t="n"/>
-      <c r="I29" s="61" t="n"/>
-      <c r="J29" s="62" t="n"/>
-      <c r="K29" s="59">
+      <c r="I29" s="92" t="n"/>
+      <c r="J29" s="93" t="n"/>
+      <c r="K29" s="61" t="n"/>
+      <c r="L29" s="62" t="n"/>
+      <c r="M29" s="59">
         <f>IF(I29="","",ROUND(I29-E29,2))</f>
         <v/>
       </c>
-      <c r="L29" s="60">
+      <c r="N29" s="60">
         <f>IF(J29="","",J29-F29)</f>
         <v/>
       </c>
-      <c r="M29" s="56" t="n"/>
-      <c r="N29" s="56" t="n"/>
+      <c r="O29" s="56" t="n"/>
+      <c r="P29" s="56" t="n"/>
     </row>
     <row r="30" ht="15" customHeight="1" s="47">
       <c r="A30" s="54" t="n"/>
@@ -1930,18 +2027,20 @@
       <c r="E30" s="59" t="n"/>
       <c r="F30" s="60" t="n"/>
       <c r="G30" s="54" t="n"/>
-      <c r="I30" s="61" t="n"/>
-      <c r="J30" s="62" t="n"/>
-      <c r="K30" s="59">
+      <c r="I30" s="92" t="n"/>
+      <c r="J30" s="93" t="n"/>
+      <c r="K30" s="61" t="n"/>
+      <c r="L30" s="62" t="n"/>
+      <c r="M30" s="59">
         <f>IF(I30="","",ROUND(I30-E30,2))</f>
         <v/>
       </c>
-      <c r="L30" s="60">
+      <c r="N30" s="60">
         <f>IF(J30="","",J30-F30)</f>
         <v/>
       </c>
-      <c r="M30" s="56" t="n"/>
-      <c r="N30" s="56" t="n"/>
+      <c r="O30" s="56" t="n"/>
+      <c r="P30" s="56" t="n"/>
     </row>
     <row r="31" ht="15" customHeight="1" s="47">
       <c r="A31" s="54" t="n"/>
@@ -1951,18 +2050,20 @@
       <c r="E31" s="59" t="n"/>
       <c r="F31" s="60" t="n"/>
       <c r="G31" s="54" t="n"/>
-      <c r="I31" s="61" t="n"/>
-      <c r="J31" s="62" t="n"/>
-      <c r="K31" s="59">
+      <c r="I31" s="92" t="n"/>
+      <c r="J31" s="93" t="n"/>
+      <c r="K31" s="61" t="n"/>
+      <c r="L31" s="62" t="n"/>
+      <c r="M31" s="59">
         <f>IF(I31="","",ROUND(I31-E31,2))</f>
         <v/>
       </c>
-      <c r="L31" s="60">
+      <c r="N31" s="60">
         <f>IF(J31="","",J31-F31)</f>
         <v/>
       </c>
-      <c r="M31" s="56" t="n"/>
-      <c r="N31" s="56" t="n"/>
+      <c r="O31" s="56" t="n"/>
+      <c r="P31" s="56" t="n"/>
     </row>
     <row r="32" ht="15" customHeight="1" s="47">
       <c r="A32" s="54" t="n"/>
@@ -1972,18 +2073,20 @@
       <c r="E32" s="59" t="n"/>
       <c r="F32" s="60" t="n"/>
       <c r="G32" s="54" t="n"/>
-      <c r="I32" s="61" t="n"/>
-      <c r="J32" s="62" t="n"/>
-      <c r="K32" s="59">
+      <c r="I32" s="92" t="n"/>
+      <c r="J32" s="93" t="n"/>
+      <c r="K32" s="61" t="n"/>
+      <c r="L32" s="62" t="n"/>
+      <c r="M32" s="59">
         <f>IF(I32="","",ROUND(I32-E32,2))</f>
         <v/>
       </c>
-      <c r="L32" s="60">
+      <c r="N32" s="60">
         <f>IF(J32="","",J32-F32)</f>
         <v/>
       </c>
-      <c r="M32" s="56" t="n"/>
-      <c r="N32" s="56" t="n"/>
+      <c r="O32" s="56" t="n"/>
+      <c r="P32" s="56" t="n"/>
     </row>
     <row r="33" ht="15" customHeight="1" s="47">
       <c r="A33" s="54" t="n"/>
@@ -1993,18 +2096,20 @@
       <c r="E33" s="59" t="n"/>
       <c r="F33" s="60" t="n"/>
       <c r="G33" s="54" t="n"/>
-      <c r="I33" s="61" t="n"/>
-      <c r="J33" s="62" t="n"/>
-      <c r="K33" s="59">
+      <c r="I33" s="92" t="n"/>
+      <c r="J33" s="93" t="n"/>
+      <c r="K33" s="61" t="n"/>
+      <c r="L33" s="62" t="n"/>
+      <c r="M33" s="59">
         <f>IF(I33="","",ROUND(I33-E33,2))</f>
         <v/>
       </c>
-      <c r="L33" s="60">
+      <c r="N33" s="60">
         <f>IF(J33="","",J33-F33)</f>
         <v/>
       </c>
-      <c r="M33" s="56" t="n"/>
-      <c r="N33" s="56" t="n"/>
+      <c r="O33" s="56" t="n"/>
+      <c r="P33" s="56" t="n"/>
     </row>
     <row r="34" ht="15" customHeight="1" s="47">
       <c r="A34" s="54" t="n"/>
@@ -2014,18 +2119,20 @@
       <c r="E34" s="59" t="n"/>
       <c r="F34" s="60" t="n"/>
       <c r="G34" s="54" t="n"/>
-      <c r="I34" s="61" t="n"/>
-      <c r="J34" s="62" t="n"/>
-      <c r="K34" s="59">
+      <c r="I34" s="92" t="n"/>
+      <c r="J34" s="93" t="n"/>
+      <c r="K34" s="61" t="n"/>
+      <c r="L34" s="62" t="n"/>
+      <c r="M34" s="59">
         <f>IF(I34="","",ROUND(I34-E34,2))</f>
         <v/>
       </c>
-      <c r="L34" s="60">
+      <c r="N34" s="60">
         <f>IF(J34="","",J34-F34)</f>
         <v/>
       </c>
-      <c r="M34" s="56" t="n"/>
-      <c r="N34" s="56" t="n"/>
+      <c r="O34" s="56" t="n"/>
+      <c r="P34" s="56" t="n"/>
     </row>
     <row r="35" ht="15" customHeight="1" s="47">
       <c r="A35" s="54" t="n"/>
@@ -2035,18 +2142,20 @@
       <c r="E35" s="59" t="n"/>
       <c r="F35" s="60" t="n"/>
       <c r="G35" s="54" t="n"/>
-      <c r="I35" s="61" t="n"/>
-      <c r="J35" s="62" t="n"/>
-      <c r="K35" s="59">
+      <c r="I35" s="92" t="n"/>
+      <c r="J35" s="93" t="n"/>
+      <c r="K35" s="61" t="n"/>
+      <c r="L35" s="62" t="n"/>
+      <c r="M35" s="59">
         <f>IF(I35="","",ROUND(I35-E35,2))</f>
         <v/>
       </c>
-      <c r="L35" s="60">
+      <c r="N35" s="60">
         <f>IF(J35="","",J35-F35)</f>
         <v/>
       </c>
-      <c r="M35" s="56" t="n"/>
-      <c r="N35" s="56" t="n"/>
+      <c r="O35" s="56" t="n"/>
+      <c r="P35" s="56" t="n"/>
     </row>
     <row r="36" ht="15" customHeight="1" s="47">
       <c r="A36" s="54" t="n"/>
@@ -2056,18 +2165,20 @@
       <c r="E36" s="59" t="n"/>
       <c r="F36" s="60" t="n"/>
       <c r="G36" s="54" t="n"/>
-      <c r="I36" s="61" t="n"/>
-      <c r="J36" s="62" t="n"/>
-      <c r="K36" s="59">
+      <c r="I36" s="92" t="n"/>
+      <c r="J36" s="93" t="n"/>
+      <c r="K36" s="61" t="n"/>
+      <c r="L36" s="62" t="n"/>
+      <c r="M36" s="59">
         <f>IF(I36="","",ROUND(I36-E36,2))</f>
         <v/>
       </c>
-      <c r="L36" s="60">
+      <c r="N36" s="60">
         <f>IF(J36="","",J36-F36)</f>
         <v/>
       </c>
-      <c r="M36" s="56" t="n"/>
-      <c r="N36" s="56" t="n"/>
+      <c r="O36" s="56" t="n"/>
+      <c r="P36" s="56" t="n"/>
     </row>
     <row r="37" ht="15" customHeight="1" s="47">
       <c r="A37" s="54" t="n"/>
@@ -2077,18 +2188,20 @@
       <c r="E37" s="59" t="n"/>
       <c r="F37" s="60" t="n"/>
       <c r="G37" s="54" t="n"/>
-      <c r="I37" s="61" t="n"/>
-      <c r="J37" s="62" t="n"/>
-      <c r="K37" s="59">
+      <c r="I37" s="92" t="n"/>
+      <c r="J37" s="93" t="n"/>
+      <c r="K37" s="61" t="n"/>
+      <c r="L37" s="62" t="n"/>
+      <c r="M37" s="59">
         <f>IF(I37="","",ROUND(I37-E37,2))</f>
         <v/>
       </c>
-      <c r="L37" s="60">
+      <c r="N37" s="60">
         <f>IF(J37="","",J37-F37)</f>
         <v/>
       </c>
-      <c r="M37" s="56" t="n"/>
-      <c r="N37" s="56" t="n"/>
+      <c r="O37" s="56" t="n"/>
+      <c r="P37" s="56" t="n"/>
     </row>
     <row r="38" ht="15" customHeight="1" s="47">
       <c r="A38" s="54" t="n"/>
@@ -2098,18 +2211,20 @@
       <c r="E38" s="59" t="n"/>
       <c r="F38" s="60" t="n"/>
       <c r="G38" s="54" t="n"/>
-      <c r="I38" s="61" t="n"/>
-      <c r="J38" s="62" t="n"/>
-      <c r="K38" s="59">
+      <c r="I38" s="92" t="n"/>
+      <c r="J38" s="93" t="n"/>
+      <c r="K38" s="61" t="n"/>
+      <c r="L38" s="62" t="n"/>
+      <c r="M38" s="59">
         <f>IF(I38="","",ROUND(I38-E38,2))</f>
         <v/>
       </c>
-      <c r="L38" s="60">
+      <c r="N38" s="60">
         <f>IF(J38="","",J38-F38)</f>
         <v/>
       </c>
-      <c r="M38" s="56" t="n"/>
-      <c r="N38" s="56" t="n"/>
+      <c r="O38" s="56" t="n"/>
+      <c r="P38" s="56" t="n"/>
     </row>
     <row r="39" ht="15" customHeight="1" s="47">
       <c r="A39" s="54" t="n"/>
@@ -2119,18 +2234,20 @@
       <c r="E39" s="59" t="n"/>
       <c r="F39" s="60" t="n"/>
       <c r="G39" s="54" t="n"/>
-      <c r="I39" s="61" t="n"/>
-      <c r="J39" s="62" t="n"/>
-      <c r="K39" s="59">
+      <c r="I39" s="92" t="n"/>
+      <c r="J39" s="93" t="n"/>
+      <c r="K39" s="61" t="n"/>
+      <c r="L39" s="62" t="n"/>
+      <c r="M39" s="59">
         <f>IF(I39="","",ROUND(I39-E39,2))</f>
         <v/>
       </c>
-      <c r="L39" s="60">
+      <c r="N39" s="60">
         <f>IF(J39="","",J39-F39)</f>
         <v/>
       </c>
-      <c r="M39" s="56" t="n"/>
-      <c r="N39" s="56" t="n"/>
+      <c r="O39" s="56" t="n"/>
+      <c r="P39" s="56" t="n"/>
     </row>
     <row r="40" ht="15" customHeight="1" s="47">
       <c r="A40" s="54" t="n"/>
@@ -2140,18 +2257,20 @@
       <c r="E40" s="59" t="n"/>
       <c r="F40" s="60" t="n"/>
       <c r="G40" s="54" t="n"/>
-      <c r="I40" s="61" t="n"/>
-      <c r="J40" s="62" t="n"/>
-      <c r="K40" s="59">
+      <c r="I40" s="92" t="n"/>
+      <c r="J40" s="93" t="n"/>
+      <c r="K40" s="61" t="n"/>
+      <c r="L40" s="62" t="n"/>
+      <c r="M40" s="59">
         <f>IF(I40="","",ROUND(I40-E40,2))</f>
         <v/>
       </c>
-      <c r="L40" s="60">
+      <c r="N40" s="60">
         <f>IF(J40="","",J40-F40)</f>
         <v/>
       </c>
-      <c r="M40" s="56" t="n"/>
-      <c r="N40" s="56" t="n"/>
+      <c r="O40" s="56" t="n"/>
+      <c r="P40" s="56" t="n"/>
     </row>
     <row r="41" ht="15" customHeight="1" s="47">
       <c r="A41" s="54" t="n"/>
@@ -2161,18 +2280,20 @@
       <c r="E41" s="59" t="n"/>
       <c r="F41" s="60" t="n"/>
       <c r="G41" s="54" t="n"/>
-      <c r="I41" s="61" t="n"/>
-      <c r="J41" s="62" t="n"/>
-      <c r="K41" s="59">
+      <c r="I41" s="92" t="n"/>
+      <c r="J41" s="93" t="n"/>
+      <c r="K41" s="61" t="n"/>
+      <c r="L41" s="62" t="n"/>
+      <c r="M41" s="59">
         <f>IF(I41="","",ROUND(I41-E41,2))</f>
         <v/>
       </c>
-      <c r="L41" s="60">
+      <c r="N41" s="60">
         <f>IF(J41="","",J41-F41)</f>
         <v/>
       </c>
-      <c r="M41" s="56" t="n"/>
-      <c r="N41" s="56" t="n"/>
+      <c r="O41" s="56" t="n"/>
+      <c r="P41" s="56" t="n"/>
     </row>
     <row r="42" ht="15" customHeight="1" s="47">
       <c r="A42" s="54" t="n"/>
@@ -2182,18 +2303,20 @@
       <c r="E42" s="59" t="n"/>
       <c r="F42" s="60" t="n"/>
       <c r="G42" s="54" t="n"/>
-      <c r="I42" s="61" t="n"/>
-      <c r="J42" s="62" t="n"/>
-      <c r="K42" s="59">
+      <c r="I42" s="92" t="n"/>
+      <c r="J42" s="93" t="n"/>
+      <c r="K42" s="61" t="n"/>
+      <c r="L42" s="62" t="n"/>
+      <c r="M42" s="59">
         <f>IF(I42="","",ROUND(I42-E42,2))</f>
         <v/>
       </c>
-      <c r="L42" s="60">
+      <c r="N42" s="60">
         <f>IF(J42="","",J42-F42)</f>
         <v/>
       </c>
-      <c r="M42" s="56" t="n"/>
-      <c r="N42" s="56" t="n"/>
+      <c r="O42" s="56" t="n"/>
+      <c r="P42" s="56" t="n"/>
     </row>
     <row r="43" ht="15" customHeight="1" s="47">
       <c r="A43" s="54" t="n"/>
@@ -2203,18 +2326,20 @@
       <c r="E43" s="59" t="n"/>
       <c r="F43" s="60" t="n"/>
       <c r="G43" s="54" t="n"/>
-      <c r="I43" s="61" t="n"/>
-      <c r="J43" s="62" t="n"/>
-      <c r="K43" s="59">
+      <c r="I43" s="92" t="n"/>
+      <c r="J43" s="93" t="n"/>
+      <c r="K43" s="61" t="n"/>
+      <c r="L43" s="62" t="n"/>
+      <c r="M43" s="59">
         <f>IF(I43="","",ROUND(I43-E43,2))</f>
         <v/>
       </c>
-      <c r="L43" s="60">
+      <c r="N43" s="60">
         <f>IF(J43="","",J43-F43)</f>
         <v/>
       </c>
-      <c r="M43" s="56" t="n"/>
-      <c r="N43" s="56" t="n"/>
+      <c r="O43" s="56" t="n"/>
+      <c r="P43" s="56" t="n"/>
     </row>
     <row r="44" ht="15" customHeight="1" s="47">
       <c r="A44" s="54" t="n"/>
@@ -2224,18 +2349,20 @@
       <c r="E44" s="59" t="n"/>
       <c r="F44" s="60" t="n"/>
       <c r="G44" s="54" t="n"/>
-      <c r="I44" s="61" t="n"/>
-      <c r="J44" s="62" t="n"/>
-      <c r="K44" s="59">
+      <c r="I44" s="92" t="n"/>
+      <c r="J44" s="93" t="n"/>
+      <c r="K44" s="61" t="n"/>
+      <c r="L44" s="62" t="n"/>
+      <c r="M44" s="59">
         <f>IF(I44="","",ROUND(I44-E44,2))</f>
         <v/>
       </c>
-      <c r="L44" s="60">
+      <c r="N44" s="60">
         <f>IF(J44="","",J44-F44)</f>
         <v/>
       </c>
-      <c r="M44" s="56" t="n"/>
-      <c r="N44" s="56" t="n"/>
+      <c r="O44" s="56" t="n"/>
+      <c r="P44" s="56" t="n"/>
     </row>
     <row r="45" ht="15" customHeight="1" s="47">
       <c r="A45" s="54" t="n"/>
@@ -2245,18 +2372,20 @@
       <c r="E45" s="59" t="n"/>
       <c r="F45" s="60" t="n"/>
       <c r="G45" s="54" t="n"/>
-      <c r="I45" s="61" t="n"/>
-      <c r="J45" s="62" t="n"/>
-      <c r="K45" s="59">
+      <c r="I45" s="92" t="n"/>
+      <c r="J45" s="93" t="n"/>
+      <c r="K45" s="61" t="n"/>
+      <c r="L45" s="62" t="n"/>
+      <c r="M45" s="59">
         <f>IF(I45="","",ROUND(I45-E45,2))</f>
         <v/>
       </c>
-      <c r="L45" s="60">
+      <c r="N45" s="60">
         <f>IF(J45="","",J45-F45)</f>
         <v/>
       </c>
-      <c r="M45" s="56" t="n"/>
-      <c r="N45" s="56" t="n"/>
+      <c r="O45" s="56" t="n"/>
+      <c r="P45" s="56" t="n"/>
     </row>
     <row r="46" ht="15" customHeight="1" s="47">
       <c r="A46" s="54" t="n"/>
@@ -2266,18 +2395,20 @@
       <c r="E46" s="59" t="n"/>
       <c r="F46" s="60" t="n"/>
       <c r="G46" s="54" t="n"/>
-      <c r="I46" s="61" t="n"/>
-      <c r="J46" s="62" t="n"/>
-      <c r="K46" s="59">
+      <c r="I46" s="92" t="n"/>
+      <c r="J46" s="93" t="n"/>
+      <c r="K46" s="61" t="n"/>
+      <c r="L46" s="62" t="n"/>
+      <c r="M46" s="59">
         <f>IF(I46="","",ROUND(I46-E46,2))</f>
         <v/>
       </c>
-      <c r="L46" s="60">
+      <c r="N46" s="60">
         <f>IF(J46="","",J46-F46)</f>
         <v/>
       </c>
-      <c r="M46" s="56" t="n"/>
-      <c r="N46" s="56" t="n"/>
+      <c r="O46" s="56" t="n"/>
+      <c r="P46" s="56" t="n"/>
     </row>
     <row r="47" ht="15" customHeight="1" s="47">
       <c r="A47" s="54" t="n"/>
@@ -2287,18 +2418,20 @@
       <c r="E47" s="59" t="n"/>
       <c r="F47" s="60" t="n"/>
       <c r="G47" s="54" t="n"/>
-      <c r="I47" s="61" t="n"/>
-      <c r="J47" s="62" t="n"/>
-      <c r="K47" s="59">
+      <c r="I47" s="92" t="n"/>
+      <c r="J47" s="93" t="n"/>
+      <c r="K47" s="61" t="n"/>
+      <c r="L47" s="62" t="n"/>
+      <c r="M47" s="59">
         <f>IF(I47="","",ROUND(I47-E47,2))</f>
         <v/>
       </c>
-      <c r="L47" s="60">
+      <c r="N47" s="60">
         <f>IF(J47="","",J47-F47)</f>
         <v/>
       </c>
-      <c r="M47" s="56" t="n"/>
-      <c r="N47" s="56" t="n"/>
+      <c r="O47" s="56" t="n"/>
+      <c r="P47" s="56" t="n"/>
     </row>
     <row r="48" ht="15" customHeight="1" s="47">
       <c r="A48" s="54" t="n"/>
@@ -2308,18 +2441,20 @@
       <c r="E48" s="59" t="n"/>
       <c r="F48" s="60" t="n"/>
       <c r="G48" s="54" t="n"/>
-      <c r="I48" s="61" t="n"/>
-      <c r="J48" s="62" t="n"/>
-      <c r="K48" s="59">
+      <c r="I48" s="92" t="n"/>
+      <c r="J48" s="93" t="n"/>
+      <c r="K48" s="61" t="n"/>
+      <c r="L48" s="62" t="n"/>
+      <c r="M48" s="59">
         <f>IF(I48="","",ROUND(I48-E48,2))</f>
         <v/>
       </c>
-      <c r="L48" s="60">
+      <c r="N48" s="60">
         <f>IF(J48="","",J48-F48)</f>
         <v/>
       </c>
-      <c r="M48" s="56" t="n"/>
-      <c r="N48" s="56" t="n"/>
+      <c r="O48" s="56" t="n"/>
+      <c r="P48" s="56" t="n"/>
     </row>
     <row r="49" ht="15" customHeight="1" s="47">
       <c r="A49" s="54" t="n"/>
@@ -2329,18 +2464,20 @@
       <c r="E49" s="59" t="n"/>
       <c r="F49" s="60" t="n"/>
       <c r="G49" s="54" t="n"/>
-      <c r="I49" s="61" t="n"/>
-      <c r="J49" s="62" t="n"/>
-      <c r="K49" s="59">
+      <c r="I49" s="92" t="n"/>
+      <c r="J49" s="93" t="n"/>
+      <c r="K49" s="61" t="n"/>
+      <c r="L49" s="62" t="n"/>
+      <c r="M49" s="59">
         <f>IF(I49="","",ROUND(I49-E49,2))</f>
         <v/>
       </c>
-      <c r="L49" s="60">
+      <c r="N49" s="60">
         <f>IF(J49="","",J49-F49)</f>
         <v/>
       </c>
-      <c r="M49" s="56" t="n"/>
-      <c r="N49" s="56" t="n"/>
+      <c r="O49" s="56" t="n"/>
+      <c r="P49" s="56" t="n"/>
     </row>
     <row r="50" ht="15" customHeight="1" s="47">
       <c r="A50" s="54" t="n"/>
@@ -2350,18 +2487,20 @@
       <c r="E50" s="59" t="n"/>
       <c r="F50" s="60" t="n"/>
       <c r="G50" s="54" t="n"/>
-      <c r="I50" s="61" t="n"/>
-      <c r="J50" s="62" t="n"/>
-      <c r="K50" s="59">
+      <c r="I50" s="92" t="n"/>
+      <c r="J50" s="93" t="n"/>
+      <c r="K50" s="61" t="n"/>
+      <c r="L50" s="62" t="n"/>
+      <c r="M50" s="59">
         <f>IF(I50="","",ROUND(I50-E50,2))</f>
         <v/>
       </c>
-      <c r="L50" s="60">
+      <c r="N50" s="60">
         <f>IF(J50="","",J50-F50)</f>
         <v/>
       </c>
-      <c r="M50" s="56" t="n"/>
-      <c r="N50" s="56" t="inlineStr">
+      <c r="O50" s="56" t="n"/>
+      <c r="P50" s="56" t="inlineStr">
         <is>
           <t>Check reception date — dated in the future in the app</t>
         </is>
@@ -2375,18 +2514,20 @@
       <c r="E51" s="59" t="n"/>
       <c r="F51" s="60" t="n"/>
       <c r="G51" s="54" t="n"/>
-      <c r="I51" s="61" t="n"/>
-      <c r="J51" s="62" t="n"/>
-      <c r="K51" s="59">
+      <c r="I51" s="92" t="n"/>
+      <c r="J51" s="93" t="n"/>
+      <c r="K51" s="61" t="n"/>
+      <c r="L51" s="62" t="n"/>
+      <c r="M51" s="59">
         <f>IF(I51="","",ROUND(I51-E51,2))</f>
         <v/>
       </c>
-      <c r="L51" s="60">
+      <c r="N51" s="60">
         <f>IF(J51="","",J51-F51)</f>
         <v/>
       </c>
-      <c r="M51" s="56" t="n"/>
-      <c r="N51" s="56" t="n"/>
+      <c r="O51" s="56" t="n"/>
+      <c r="P51" s="56" t="n"/>
     </row>
     <row r="52" ht="15" customHeight="1" s="47">
       <c r="A52" s="54" t="n"/>
@@ -2396,18 +2537,20 @@
       <c r="E52" s="59" t="n"/>
       <c r="F52" s="60" t="n"/>
       <c r="G52" s="54" t="n"/>
-      <c r="I52" s="61" t="n"/>
-      <c r="J52" s="62" t="n"/>
-      <c r="K52" s="59">
+      <c r="I52" s="92" t="n"/>
+      <c r="J52" s="93" t="n"/>
+      <c r="K52" s="61" t="n"/>
+      <c r="L52" s="62" t="n"/>
+      <c r="M52" s="59">
         <f>IF(I52="","",ROUND(I52-E52,2))</f>
         <v/>
       </c>
-      <c r="L52" s="60">
+      <c r="N52" s="60">
         <f>IF(J52="","",J52-F52)</f>
         <v/>
       </c>
-      <c r="M52" s="56" t="n"/>
-      <c r="N52" s="56" t="n"/>
+      <c r="O52" s="56" t="n"/>
+      <c r="P52" s="56" t="n"/>
     </row>
     <row r="53" ht="15" customHeight="1" s="47">
       <c r="A53" s="54" t="n"/>
@@ -2417,18 +2560,20 @@
       <c r="E53" s="59" t="n"/>
       <c r="F53" s="60" t="n"/>
       <c r="G53" s="54" t="n"/>
-      <c r="I53" s="61" t="n"/>
-      <c r="J53" s="62" t="n"/>
-      <c r="K53" s="59">
+      <c r="I53" s="92" t="n"/>
+      <c r="J53" s="93" t="n"/>
+      <c r="K53" s="61" t="n"/>
+      <c r="L53" s="62" t="n"/>
+      <c r="M53" s="59">
         <f>IF(I53="","",ROUND(I53-E53,2))</f>
         <v/>
       </c>
-      <c r="L53" s="60">
+      <c r="N53" s="60">
         <f>IF(J53="","",J53-F53)</f>
         <v/>
       </c>
-      <c r="M53" s="56" t="n"/>
-      <c r="N53" s="56" t="n"/>
+      <c r="O53" s="56" t="n"/>
+      <c r="P53" s="56" t="n"/>
     </row>
     <row r="54" ht="15" customHeight="1" s="47">
       <c r="A54" s="54" t="n"/>
@@ -2438,18 +2583,20 @@
       <c r="E54" s="59" t="n"/>
       <c r="F54" s="60" t="n"/>
       <c r="G54" s="54" t="n"/>
-      <c r="I54" s="61" t="n"/>
-      <c r="J54" s="62" t="n"/>
-      <c r="K54" s="59">
+      <c r="I54" s="92" t="n"/>
+      <c r="J54" s="93" t="n"/>
+      <c r="K54" s="61" t="n"/>
+      <c r="L54" s="62" t="n"/>
+      <c r="M54" s="59">
         <f>IF(I54="","",ROUND(I54-E54,2))</f>
         <v/>
       </c>
-      <c r="L54" s="60">
+      <c r="N54" s="60">
         <f>IF(J54="","",J54-F54)</f>
         <v/>
       </c>
-      <c r="M54" s="56" t="n"/>
-      <c r="N54" s="56" t="n"/>
+      <c r="O54" s="56" t="n"/>
+      <c r="P54" s="56" t="n"/>
     </row>
     <row r="55" ht="15" customHeight="1" s="47">
       <c r="A55" s="54" t="n"/>
@@ -2459,18 +2606,20 @@
       <c r="E55" s="59" t="n"/>
       <c r="F55" s="60" t="n"/>
       <c r="G55" s="54" t="n"/>
-      <c r="I55" s="61" t="n"/>
-      <c r="J55" s="62" t="n"/>
-      <c r="K55" s="59">
+      <c r="I55" s="92" t="n"/>
+      <c r="J55" s="93" t="n"/>
+      <c r="K55" s="61" t="n"/>
+      <c r="L55" s="62" t="n"/>
+      <c r="M55" s="59">
         <f>IF(I55="","",ROUND(I55-E55,2))</f>
         <v/>
       </c>
-      <c r="L55" s="60">
+      <c r="N55" s="60">
         <f>IF(J55="","",J55-F55)</f>
         <v/>
       </c>
-      <c r="M55" s="56" t="n"/>
-      <c r="N55" s="56" t="n"/>
+      <c r="O55" s="56" t="n"/>
+      <c r="P55" s="56" t="n"/>
     </row>
     <row r="56" ht="15" customHeight="1" s="47">
       <c r="A56" s="54" t="n"/>
@@ -2480,18 +2629,20 @@
       <c r="E56" s="59" t="n"/>
       <c r="F56" s="60" t="n"/>
       <c r="G56" s="54" t="n"/>
-      <c r="I56" s="61" t="n"/>
-      <c r="J56" s="62" t="n"/>
-      <c r="K56" s="59">
+      <c r="I56" s="92" t="n"/>
+      <c r="J56" s="93" t="n"/>
+      <c r="K56" s="61" t="n"/>
+      <c r="L56" s="62" t="n"/>
+      <c r="M56" s="59">
         <f>IF(I56="","",ROUND(I56-E56,2))</f>
         <v/>
       </c>
-      <c r="L56" s="60">
+      <c r="N56" s="60">
         <f>IF(J56="","",J56-F56)</f>
         <v/>
       </c>
-      <c r="M56" s="56" t="n"/>
-      <c r="N56" s="56" t="n"/>
+      <c r="O56" s="56" t="n"/>
+      <c r="P56" s="56" t="n"/>
     </row>
     <row r="57" ht="15" customHeight="1" s="47">
       <c r="A57" s="54" t="n"/>
@@ -2501,18 +2652,20 @@
       <c r="E57" s="59" t="n"/>
       <c r="F57" s="60" t="n"/>
       <c r="G57" s="54" t="n"/>
-      <c r="I57" s="61" t="n"/>
-      <c r="J57" s="62" t="n"/>
-      <c r="K57" s="59">
+      <c r="I57" s="92" t="n"/>
+      <c r="J57" s="93" t="n"/>
+      <c r="K57" s="61" t="n"/>
+      <c r="L57" s="62" t="n"/>
+      <c r="M57" s="59">
         <f>IF(I57="","",ROUND(I57-E57,2))</f>
         <v/>
       </c>
-      <c r="L57" s="60">
+      <c r="N57" s="60">
         <f>IF(J57="","",J57-F57)</f>
         <v/>
       </c>
-      <c r="M57" s="56" t="n"/>
-      <c r="N57" s="56" t="n"/>
+      <c r="O57" s="56" t="n"/>
+      <c r="P57" s="56" t="n"/>
     </row>
     <row r="58" ht="15" customHeight="1" s="47">
       <c r="A58" s="54" t="n"/>
@@ -2522,18 +2675,20 @@
       <c r="E58" s="59" t="n"/>
       <c r="F58" s="60" t="n"/>
       <c r="G58" s="54" t="n"/>
-      <c r="I58" s="61" t="n"/>
-      <c r="J58" s="62" t="n"/>
-      <c r="K58" s="59">
+      <c r="I58" s="92" t="n"/>
+      <c r="J58" s="93" t="n"/>
+      <c r="K58" s="61" t="n"/>
+      <c r="L58" s="62" t="n"/>
+      <c r="M58" s="59">
         <f>IF(I58="","",ROUND(I58-E58,2))</f>
         <v/>
       </c>
-      <c r="L58" s="60">
+      <c r="N58" s="60">
         <f>IF(J58="","",J58-F58)</f>
         <v/>
       </c>
-      <c r="M58" s="56" t="n"/>
-      <c r="N58" s="56" t="n"/>
+      <c r="O58" s="56" t="n"/>
+      <c r="P58" s="56" t="n"/>
     </row>
     <row r="59" ht="15" customHeight="1" s="47">
       <c r="A59" s="54" t="n"/>
@@ -2543,18 +2698,20 @@
       <c r="E59" s="59" t="n"/>
       <c r="F59" s="60" t="n"/>
       <c r="G59" s="54" t="n"/>
-      <c r="I59" s="61" t="n"/>
-      <c r="J59" s="62" t="n"/>
-      <c r="K59" s="59">
+      <c r="I59" s="92" t="n"/>
+      <c r="J59" s="93" t="n"/>
+      <c r="K59" s="61" t="n"/>
+      <c r="L59" s="62" t="n"/>
+      <c r="M59" s="59">
         <f>IF(I59="","",ROUND(I59-E59,2))</f>
         <v/>
       </c>
-      <c r="L59" s="60">
+      <c r="N59" s="60">
         <f>IF(J59="","",J59-F59)</f>
         <v/>
       </c>
-      <c r="M59" s="56" t="n"/>
-      <c r="N59" s="56" t="n"/>
+      <c r="O59" s="56" t="n"/>
+      <c r="P59" s="56" t="n"/>
     </row>
     <row r="60" ht="15" customHeight="1" s="47">
       <c r="A60" s="54" t="n"/>
@@ -2564,18 +2721,20 @@
       <c r="E60" s="59" t="n"/>
       <c r="F60" s="60" t="n"/>
       <c r="G60" s="54" t="n"/>
-      <c r="I60" s="61" t="n"/>
-      <c r="J60" s="62" t="n"/>
-      <c r="K60" s="59">
+      <c r="I60" s="92" t="n"/>
+      <c r="J60" s="93" t="n"/>
+      <c r="K60" s="61" t="n"/>
+      <c r="L60" s="62" t="n"/>
+      <c r="M60" s="59">
         <f>IF(I60="","",ROUND(I60-E60,2))</f>
         <v/>
       </c>
-      <c r="L60" s="60">
+      <c r="N60" s="60">
         <f>IF(J60="","",J60-F60)</f>
         <v/>
       </c>
-      <c r="M60" s="56" t="n"/>
-      <c r="N60" s="56" t="n"/>
+      <c r="O60" s="56" t="n"/>
+      <c r="P60" s="56" t="n"/>
     </row>
     <row r="61" ht="15" customHeight="1" s="47">
       <c r="A61" s="54" t="n"/>
@@ -2585,18 +2744,20 @@
       <c r="E61" s="59" t="n"/>
       <c r="F61" s="60" t="n"/>
       <c r="G61" s="54" t="n"/>
-      <c r="I61" s="61" t="n"/>
-      <c r="J61" s="62" t="n"/>
-      <c r="K61" s="59">
+      <c r="I61" s="92" t="n"/>
+      <c r="J61" s="93" t="n"/>
+      <c r="K61" s="61" t="n"/>
+      <c r="L61" s="62" t="n"/>
+      <c r="M61" s="59">
         <f>IF(I61="","",ROUND(I61-E61,2))</f>
         <v/>
       </c>
-      <c r="L61" s="60">
+      <c r="N61" s="60">
         <f>IF(J61="","",J61-F61)</f>
         <v/>
       </c>
-      <c r="M61" s="56" t="n"/>
-      <c r="N61" s="56" t="n"/>
+      <c r="O61" s="56" t="n"/>
+      <c r="P61" s="56" t="n"/>
     </row>
     <row r="62" ht="15" customHeight="1" s="47">
       <c r="A62" s="54" t="n"/>
@@ -2606,18 +2767,20 @@
       <c r="E62" s="59" t="n"/>
       <c r="F62" s="60" t="n"/>
       <c r="G62" s="54" t="n"/>
-      <c r="I62" s="61" t="n"/>
-      <c r="J62" s="62" t="n"/>
-      <c r="K62" s="59">
+      <c r="I62" s="92" t="n"/>
+      <c r="J62" s="93" t="n"/>
+      <c r="K62" s="61" t="n"/>
+      <c r="L62" s="62" t="n"/>
+      <c r="M62" s="59">
         <f>IF(I62="","",ROUND(I62-E62,2))</f>
         <v/>
       </c>
-      <c r="L62" s="60">
+      <c r="N62" s="60">
         <f>IF(J62="","",J62-F62)</f>
         <v/>
       </c>
-      <c r="M62" s="56" t="n"/>
-      <c r="N62" s="56" t="n"/>
+      <c r="O62" s="56" t="n"/>
+      <c r="P62" s="56" t="n"/>
     </row>
     <row r="63" ht="15" customHeight="1" s="47">
       <c r="A63" s="54" t="n"/>
@@ -2627,18 +2790,20 @@
       <c r="E63" s="59" t="n"/>
       <c r="F63" s="60" t="n"/>
       <c r="G63" s="54" t="n"/>
-      <c r="I63" s="61" t="n"/>
-      <c r="J63" s="62" t="n"/>
-      <c r="K63" s="59">
+      <c r="I63" s="92" t="n"/>
+      <c r="J63" s="93" t="n"/>
+      <c r="K63" s="61" t="n"/>
+      <c r="L63" s="62" t="n"/>
+      <c r="M63" s="59">
         <f>IF(I63="","",ROUND(I63-E63,2))</f>
         <v/>
       </c>
-      <c r="L63" s="60">
+      <c r="N63" s="60">
         <f>IF(J63="","",J63-F63)</f>
         <v/>
       </c>
-      <c r="M63" s="56" t="n"/>
-      <c r="N63" s="56" t="n"/>
+      <c r="O63" s="56" t="n"/>
+      <c r="P63" s="56" t="n"/>
     </row>
     <row r="64" ht="15" customHeight="1" s="47">
       <c r="A64" s="54" t="n"/>
@@ -2648,18 +2813,20 @@
       <c r="E64" s="59" t="n"/>
       <c r="F64" s="60" t="n"/>
       <c r="G64" s="54" t="n"/>
-      <c r="I64" s="61" t="n"/>
-      <c r="J64" s="62" t="n"/>
-      <c r="K64" s="59">
+      <c r="I64" s="92" t="n"/>
+      <c r="J64" s="93" t="n"/>
+      <c r="K64" s="61" t="n"/>
+      <c r="L64" s="62" t="n"/>
+      <c r="M64" s="59">
         <f>IF(I64="","",ROUND(I64-E64,2))</f>
         <v/>
       </c>
-      <c r="L64" s="60">
+      <c r="N64" s="60">
         <f>IF(J64="","",J64-F64)</f>
         <v/>
       </c>
-      <c r="M64" s="56" t="n"/>
-      <c r="N64" s="56" t="n"/>
+      <c r="O64" s="56" t="n"/>
+      <c r="P64" s="56" t="n"/>
     </row>
     <row r="65" ht="15" customHeight="1" s="47">
       <c r="A65" s="54" t="n"/>
@@ -2669,18 +2836,20 @@
       <c r="E65" s="59" t="n"/>
       <c r="F65" s="60" t="n"/>
       <c r="G65" s="54" t="n"/>
-      <c r="I65" s="61" t="n"/>
-      <c r="J65" s="62" t="n"/>
-      <c r="K65" s="59">
+      <c r="I65" s="92" t="n"/>
+      <c r="J65" s="93" t="n"/>
+      <c r="K65" s="61" t="n"/>
+      <c r="L65" s="62" t="n"/>
+      <c r="M65" s="59">
         <f>IF(I65="","",ROUND(I65-E65,2))</f>
         <v/>
       </c>
-      <c r="L65" s="60">
+      <c r="N65" s="60">
         <f>IF(J65="","",J65-F65)</f>
         <v/>
       </c>
-      <c r="M65" s="56" t="n"/>
-      <c r="N65" s="56" t="n"/>
+      <c r="O65" s="56" t="n"/>
+      <c r="P65" s="56" t="n"/>
     </row>
     <row r="66" ht="15" customHeight="1" s="47">
       <c r="A66" s="54" t="n"/>
@@ -2690,18 +2859,20 @@
       <c r="E66" s="59" t="n"/>
       <c r="F66" s="60" t="n"/>
       <c r="G66" s="54" t="n"/>
-      <c r="I66" s="61" t="n"/>
-      <c r="J66" s="62" t="n"/>
-      <c r="K66" s="59">
+      <c r="I66" s="92" t="n"/>
+      <c r="J66" s="93" t="n"/>
+      <c r="K66" s="61" t="n"/>
+      <c r="L66" s="62" t="n"/>
+      <c r="M66" s="59">
         <f>IF(I66="","",ROUND(I66-E66,2))</f>
         <v/>
       </c>
-      <c r="L66" s="60">
+      <c r="N66" s="60">
         <f>IF(J66="","",J66-F66)</f>
         <v/>
       </c>
-      <c r="M66" s="56" t="n"/>
-      <c r="N66" s="56" t="n"/>
+      <c r="O66" s="56" t="n"/>
+      <c r="P66" s="56" t="n"/>
     </row>
     <row r="67" ht="15" customHeight="1" s="47">
       <c r="A67" s="54" t="n"/>
@@ -2711,18 +2882,20 @@
       <c r="E67" s="59" t="n"/>
       <c r="F67" s="60" t="n"/>
       <c r="G67" s="54" t="n"/>
-      <c r="I67" s="61" t="n"/>
-      <c r="J67" s="62" t="n"/>
-      <c r="K67" s="59">
+      <c r="I67" s="92" t="n"/>
+      <c r="J67" s="93" t="n"/>
+      <c r="K67" s="61" t="n"/>
+      <c r="L67" s="62" t="n"/>
+      <c r="M67" s="59">
         <f>IF(I67="","",ROUND(I67-E67,2))</f>
         <v/>
       </c>
-      <c r="L67" s="60">
+      <c r="N67" s="60">
         <f>IF(J67="","",J67-F67)</f>
         <v/>
       </c>
-      <c r="M67" s="56" t="n"/>
-      <c r="N67" s="56" t="n"/>
+      <c r="O67" s="56" t="n"/>
+      <c r="P67" s="56" t="n"/>
     </row>
     <row r="68" ht="15" customHeight="1" s="47">
       <c r="A68" s="54" t="n"/>
@@ -2732,18 +2905,20 @@
       <c r="E68" s="59" t="n"/>
       <c r="F68" s="60" t="n"/>
       <c r="G68" s="54" t="n"/>
-      <c r="I68" s="61" t="n"/>
-      <c r="J68" s="62" t="n"/>
-      <c r="K68" s="59">
+      <c r="I68" s="92" t="n"/>
+      <c r="J68" s="93" t="n"/>
+      <c r="K68" s="61" t="n"/>
+      <c r="L68" s="62" t="n"/>
+      <c r="M68" s="59">
         <f>IF(I68="","",ROUND(I68-E68,2))</f>
         <v/>
       </c>
-      <c r="L68" s="60">
+      <c r="N68" s="60">
         <f>IF(J68="","",J68-F68)</f>
         <v/>
       </c>
-      <c r="M68" s="56" t="n"/>
-      <c r="N68" s="56" t="n"/>
+      <c r="O68" s="56" t="n"/>
+      <c r="P68" s="56" t="n"/>
     </row>
     <row r="69" ht="15" customHeight="1" s="47">
       <c r="A69" s="54" t="n"/>
@@ -2753,18 +2928,20 @@
       <c r="E69" s="59" t="n"/>
       <c r="F69" s="60" t="n"/>
       <c r="G69" s="54" t="n"/>
-      <c r="I69" s="61" t="n"/>
-      <c r="J69" s="62" t="n"/>
-      <c r="K69" s="59">
+      <c r="I69" s="92" t="n"/>
+      <c r="J69" s="93" t="n"/>
+      <c r="K69" s="61" t="n"/>
+      <c r="L69" s="62" t="n"/>
+      <c r="M69" s="59">
         <f>IF(I69="","",ROUND(I69-E69,2))</f>
         <v/>
       </c>
-      <c r="L69" s="60">
+      <c r="N69" s="60">
         <f>IF(J69="","",J69-F69)</f>
         <v/>
       </c>
-      <c r="M69" s="56" t="n"/>
-      <c r="N69" s="56" t="n"/>
+      <c r="O69" s="56" t="n"/>
+      <c r="P69" s="56" t="n"/>
     </row>
     <row r="70" ht="15" customHeight="1" s="47">
       <c r="A70" s="54" t="n"/>
@@ -2774,18 +2951,20 @@
       <c r="E70" s="59" t="n"/>
       <c r="F70" s="60" t="n"/>
       <c r="G70" s="54" t="n"/>
-      <c r="I70" s="61" t="n"/>
-      <c r="J70" s="62" t="n"/>
-      <c r="K70" s="59">
+      <c r="I70" s="92" t="n"/>
+      <c r="J70" s="93" t="n"/>
+      <c r="K70" s="61" t="n"/>
+      <c r="L70" s="62" t="n"/>
+      <c r="M70" s="59">
         <f>IF(I70="","",ROUND(I70-E70,2))</f>
         <v/>
       </c>
-      <c r="L70" s="60">
+      <c r="N70" s="60">
         <f>IF(J70="","",J70-F70)</f>
         <v/>
       </c>
-      <c r="M70" s="56" t="n"/>
-      <c r="N70" s="56" t="n"/>
+      <c r="O70" s="56" t="n"/>
+      <c r="P70" s="56" t="n"/>
     </row>
     <row r="71" ht="15" customHeight="1" s="47">
       <c r="A71" s="54" t="n"/>
@@ -2795,18 +2974,20 @@
       <c r="E71" s="59" t="n"/>
       <c r="F71" s="60" t="n"/>
       <c r="G71" s="54" t="n"/>
-      <c r="I71" s="61" t="n"/>
-      <c r="J71" s="62" t="n"/>
-      <c r="K71" s="59">
+      <c r="I71" s="92" t="n"/>
+      <c r="J71" s="93" t="n"/>
+      <c r="K71" s="61" t="n"/>
+      <c r="L71" s="62" t="n"/>
+      <c r="M71" s="59">
         <f>IF(I71="","",ROUND(I71-E71,2))</f>
         <v/>
       </c>
-      <c r="L71" s="60">
+      <c r="N71" s="60">
         <f>IF(J71="","",J71-F71)</f>
         <v/>
       </c>
-      <c r="M71" s="56" t="n"/>
-      <c r="N71" s="56" t="n"/>
+      <c r="O71" s="56" t="n"/>
+      <c r="P71" s="56" t="n"/>
     </row>
     <row r="72" ht="15" customHeight="1" s="47">
       <c r="A72" s="54" t="n"/>
@@ -2816,18 +2997,20 @@
       <c r="E72" s="59" t="n"/>
       <c r="F72" s="60" t="n"/>
       <c r="G72" s="54" t="n"/>
-      <c r="I72" s="61" t="n"/>
-      <c r="J72" s="62" t="n"/>
-      <c r="K72" s="59">
+      <c r="I72" s="92" t="n"/>
+      <c r="J72" s="93" t="n"/>
+      <c r="K72" s="61" t="n"/>
+      <c r="L72" s="62" t="n"/>
+      <c r="M72" s="59">
         <f>IF(I72="","",ROUND(I72-E72,2))</f>
         <v/>
       </c>
-      <c r="L72" s="60">
+      <c r="N72" s="60">
         <f>IF(J72="","",J72-F72)</f>
         <v/>
       </c>
-      <c r="M72" s="56" t="n"/>
-      <c r="N72" s="56" t="n"/>
+      <c r="O72" s="56" t="n"/>
+      <c r="P72" s="56" t="n"/>
     </row>
     <row r="73" ht="15" customHeight="1" s="47">
       <c r="A73" s="54" t="n"/>
@@ -2837,18 +3020,20 @@
       <c r="E73" s="59" t="n"/>
       <c r="F73" s="60" t="n"/>
       <c r="G73" s="54" t="n"/>
-      <c r="I73" s="61" t="n"/>
-      <c r="J73" s="62" t="n"/>
-      <c r="K73" s="59">
+      <c r="I73" s="92" t="n"/>
+      <c r="J73" s="93" t="n"/>
+      <c r="K73" s="61" t="n"/>
+      <c r="L73" s="62" t="n"/>
+      <c r="M73" s="59">
         <f>IF(I73="","",ROUND(I73-E73,2))</f>
         <v/>
       </c>
-      <c r="L73" s="60">
+      <c r="N73" s="60">
         <f>IF(J73="","",J73-F73)</f>
         <v/>
       </c>
-      <c r="M73" s="56" t="n"/>
-      <c r="N73" s="56" t="n"/>
+      <c r="O73" s="56" t="n"/>
+      <c r="P73" s="56" t="n"/>
     </row>
     <row r="74" ht="15" customHeight="1" s="47">
       <c r="A74" s="54" t="n"/>
@@ -2858,18 +3043,20 @@
       <c r="E74" s="59" t="n"/>
       <c r="F74" s="60" t="n"/>
       <c r="G74" s="54" t="n"/>
-      <c r="I74" s="61" t="n"/>
-      <c r="J74" s="62" t="n"/>
-      <c r="K74" s="59">
+      <c r="I74" s="92" t="n"/>
+      <c r="J74" s="93" t="n"/>
+      <c r="K74" s="61" t="n"/>
+      <c r="L74" s="62" t="n"/>
+      <c r="M74" s="59">
         <f>IF(I74="","",ROUND(I74-E74,2))</f>
         <v/>
       </c>
-      <c r="L74" s="60">
+      <c r="N74" s="60">
         <f>IF(J74="","",J74-F74)</f>
         <v/>
       </c>
-      <c r="M74" s="56" t="n"/>
-      <c r="N74" s="56" t="n"/>
+      <c r="O74" s="56" t="n"/>
+      <c r="P74" s="56" t="n"/>
     </row>
     <row r="75" ht="15" customHeight="1" s="47">
       <c r="A75" s="54" t="n"/>
@@ -2879,18 +3066,20 @@
       <c r="E75" s="59" t="n"/>
       <c r="F75" s="60" t="n"/>
       <c r="G75" s="54" t="n"/>
-      <c r="I75" s="61" t="n"/>
-      <c r="J75" s="62" t="n"/>
-      <c r="K75" s="59">
+      <c r="I75" s="92" t="n"/>
+      <c r="J75" s="93" t="n"/>
+      <c r="K75" s="61" t="n"/>
+      <c r="L75" s="62" t="n"/>
+      <c r="M75" s="59">
         <f>IF(I75="","",ROUND(I75-E75,2))</f>
         <v/>
       </c>
-      <c r="L75" s="60">
+      <c r="N75" s="60">
         <f>IF(J75="","",J75-F75)</f>
         <v/>
       </c>
-      <c r="M75" s="56" t="n"/>
-      <c r="N75" s="56" t="n"/>
+      <c r="O75" s="56" t="n"/>
+      <c r="P75" s="56" t="n"/>
     </row>
     <row r="76" ht="15" customHeight="1" s="47">
       <c r="A76" s="54" t="n"/>
@@ -2900,18 +3089,20 @@
       <c r="E76" s="59" t="n"/>
       <c r="F76" s="60" t="n"/>
       <c r="G76" s="54" t="n"/>
-      <c r="I76" s="61" t="n"/>
-      <c r="J76" s="62" t="n"/>
-      <c r="K76" s="59">
+      <c r="I76" s="92" t="n"/>
+      <c r="J76" s="93" t="n"/>
+      <c r="K76" s="61" t="n"/>
+      <c r="L76" s="62" t="n"/>
+      <c r="M76" s="59">
         <f>IF(I76="","",ROUND(I76-E76,2))</f>
         <v/>
       </c>
-      <c r="L76" s="60">
+      <c r="N76" s="60">
         <f>IF(J76="","",J76-F76)</f>
         <v/>
       </c>
-      <c r="M76" s="56" t="n"/>
-      <c r="N76" s="56" t="n"/>
+      <c r="O76" s="56" t="n"/>
+      <c r="P76" s="56" t="n"/>
     </row>
     <row r="77" ht="15" customHeight="1" s="47">
       <c r="A77" s="54" t="n"/>
@@ -2921,18 +3112,20 @@
       <c r="E77" s="59" t="n"/>
       <c r="F77" s="60" t="n"/>
       <c r="G77" s="54" t="n"/>
-      <c r="I77" s="61" t="n"/>
-      <c r="J77" s="62" t="n"/>
-      <c r="K77" s="59">
+      <c r="I77" s="92" t="n"/>
+      <c r="J77" s="93" t="n"/>
+      <c r="K77" s="61" t="n"/>
+      <c r="L77" s="62" t="n"/>
+      <c r="M77" s="59">
         <f>IF(I77="","",ROUND(I77-E77,2))</f>
         <v/>
       </c>
-      <c r="L77" s="60">
+      <c r="N77" s="60">
         <f>IF(J77="","",J77-F77)</f>
         <v/>
       </c>
-      <c r="M77" s="56" t="n"/>
-      <c r="N77" s="56" t="n"/>
+      <c r="O77" s="56" t="n"/>
+      <c r="P77" s="56" t="n"/>
     </row>
     <row r="78" ht="15" customHeight="1" s="47">
       <c r="A78" s="54" t="n"/>
@@ -2942,18 +3135,20 @@
       <c r="E78" s="59" t="n"/>
       <c r="F78" s="60" t="n"/>
       <c r="G78" s="54" t="n"/>
-      <c r="I78" s="61" t="n"/>
-      <c r="J78" s="62" t="n"/>
-      <c r="K78" s="59">
+      <c r="I78" s="92" t="n"/>
+      <c r="J78" s="93" t="n"/>
+      <c r="K78" s="61" t="n"/>
+      <c r="L78" s="62" t="n"/>
+      <c r="M78" s="59">
         <f>IF(I78="","",ROUND(I78-E78,2))</f>
         <v/>
       </c>
-      <c r="L78" s="60">
+      <c r="N78" s="60">
         <f>IF(J78="","",J78-F78)</f>
         <v/>
       </c>
-      <c r="M78" s="56" t="n"/>
-      <c r="N78" s="56" t="n"/>
+      <c r="O78" s="56" t="n"/>
+      <c r="P78" s="56" t="n"/>
     </row>
     <row r="79" ht="15" customHeight="1" s="47">
       <c r="A79" s="54" t="n"/>
@@ -2963,18 +3158,20 @@
       <c r="E79" s="59" t="n"/>
       <c r="F79" s="60" t="n"/>
       <c r="G79" s="54" t="n"/>
-      <c r="I79" s="61" t="n"/>
-      <c r="J79" s="62" t="n"/>
-      <c r="K79" s="59">
+      <c r="I79" s="92" t="n"/>
+      <c r="J79" s="93" t="n"/>
+      <c r="K79" s="61" t="n"/>
+      <c r="L79" s="62" t="n"/>
+      <c r="M79" s="59">
         <f>IF(I79="","",ROUND(I79-E79,2))</f>
         <v/>
       </c>
-      <c r="L79" s="60">
+      <c r="N79" s="60">
         <f>IF(J79="","",J79-F79)</f>
         <v/>
       </c>
-      <c r="M79" s="56" t="n"/>
-      <c r="N79" s="56" t="n"/>
+      <c r="O79" s="56" t="n"/>
+      <c r="P79" s="56" t="n"/>
     </row>
     <row r="80" ht="15" customHeight="1" s="47">
       <c r="A80" s="54" t="n"/>
@@ -2984,18 +3181,20 @@
       <c r="E80" s="59" t="n"/>
       <c r="F80" s="60" t="n"/>
       <c r="G80" s="54" t="n"/>
-      <c r="I80" s="61" t="n"/>
-      <c r="J80" s="62" t="n"/>
-      <c r="K80" s="59">
+      <c r="I80" s="92" t="n"/>
+      <c r="J80" s="93" t="n"/>
+      <c r="K80" s="61" t="n"/>
+      <c r="L80" s="62" t="n"/>
+      <c r="M80" s="59">
         <f>IF(I80="","",ROUND(I80-E80,2))</f>
         <v/>
       </c>
-      <c r="L80" s="60">
+      <c r="N80" s="60">
         <f>IF(J80="","",J80-F80)</f>
         <v/>
       </c>
-      <c r="M80" s="56" t="n"/>
-      <c r="N80" s="56" t="n"/>
+      <c r="O80" s="56" t="n"/>
+      <c r="P80" s="56" t="n"/>
     </row>
     <row r="81" ht="15" customHeight="1" s="47">
       <c r="A81" s="54" t="n"/>
@@ -3005,18 +3204,20 @@
       <c r="E81" s="59" t="n"/>
       <c r="F81" s="60" t="n"/>
       <c r="G81" s="54" t="n"/>
-      <c r="I81" s="61" t="n"/>
-      <c r="J81" s="62" t="n"/>
-      <c r="K81" s="59">
+      <c r="I81" s="92" t="n"/>
+      <c r="J81" s="93" t="n"/>
+      <c r="K81" s="61" t="n"/>
+      <c r="L81" s="62" t="n"/>
+      <c r="M81" s="59">
         <f>IF(I81="","",ROUND(I81-E81,2))</f>
         <v/>
       </c>
-      <c r="L81" s="60">
+      <c r="N81" s="60">
         <f>IF(J81="","",J81-F81)</f>
         <v/>
       </c>
-      <c r="M81" s="56" t="n"/>
-      <c r="N81" s="56" t="n"/>
+      <c r="O81" s="56" t="n"/>
+      <c r="P81" s="56" t="n"/>
     </row>
     <row r="82" ht="15" customHeight="1" s="47">
       <c r="A82" s="54" t="n"/>
@@ -3026,18 +3227,20 @@
       <c r="E82" s="59" t="n"/>
       <c r="F82" s="60" t="n"/>
       <c r="G82" s="54" t="n"/>
-      <c r="I82" s="61" t="n"/>
-      <c r="J82" s="62" t="n"/>
-      <c r="K82" s="59">
+      <c r="I82" s="92" t="n"/>
+      <c r="J82" s="93" t="n"/>
+      <c r="K82" s="61" t="n"/>
+      <c r="L82" s="62" t="n"/>
+      <c r="M82" s="59">
         <f>IF(I82="","",ROUND(I82-E82,2))</f>
         <v/>
       </c>
-      <c r="L82" s="60">
+      <c r="N82" s="60">
         <f>IF(J82="","",J82-F82)</f>
         <v/>
       </c>
-      <c r="M82" s="56" t="n"/>
-      <c r="N82" s="56" t="n"/>
+      <c r="O82" s="56" t="n"/>
+      <c r="P82" s="56" t="n"/>
     </row>
     <row r="83" ht="15" customHeight="1" s="47">
       <c r="A83" s="54" t="n"/>
@@ -3047,18 +3250,20 @@
       <c r="E83" s="59" t="n"/>
       <c r="F83" s="60" t="n"/>
       <c r="G83" s="54" t="n"/>
-      <c r="I83" s="61" t="n"/>
-      <c r="J83" s="62" t="n"/>
-      <c r="K83" s="59">
+      <c r="I83" s="92" t="n"/>
+      <c r="J83" s="93" t="n"/>
+      <c r="K83" s="61" t="n"/>
+      <c r="L83" s="62" t="n"/>
+      <c r="M83" s="59">
         <f>IF(I83="","",ROUND(I83-E83,2))</f>
         <v/>
       </c>
-      <c r="L83" s="60">
+      <c r="N83" s="60">
         <f>IF(J83="","",J83-F83)</f>
         <v/>
       </c>
-      <c r="M83" s="56" t="n"/>
-      <c r="N83" s="56" t="n"/>
+      <c r="O83" s="56" t="n"/>
+      <c r="P83" s="56" t="n"/>
     </row>
     <row r="84" ht="15" customHeight="1" s="47">
       <c r="A84" s="54" t="n"/>
@@ -3068,18 +3273,20 @@
       <c r="E84" s="59" t="n"/>
       <c r="F84" s="60" t="n"/>
       <c r="G84" s="54" t="n"/>
-      <c r="I84" s="61" t="n"/>
-      <c r="J84" s="62" t="n"/>
-      <c r="K84" s="59">
+      <c r="I84" s="92" t="n"/>
+      <c r="J84" s="93" t="n"/>
+      <c r="K84" s="61" t="n"/>
+      <c r="L84" s="62" t="n"/>
+      <c r="M84" s="59">
         <f>IF(I84="","",ROUND(I84-E84,2))</f>
         <v/>
       </c>
-      <c r="L84" s="60">
+      <c r="N84" s="60">
         <f>IF(J84="","",J84-F84)</f>
         <v/>
       </c>
-      <c r="M84" s="56" t="n"/>
-      <c r="N84" s="56" t="n"/>
+      <c r="O84" s="56" t="n"/>
+      <c r="P84" s="56" t="n"/>
     </row>
     <row r="85" ht="15" customHeight="1" s="47">
       <c r="A85" s="54" t="n"/>
@@ -3089,18 +3296,20 @@
       <c r="E85" s="59" t="n"/>
       <c r="F85" s="60" t="n"/>
       <c r="G85" s="54" t="n"/>
-      <c r="I85" s="61" t="n"/>
-      <c r="J85" s="62" t="n"/>
-      <c r="K85" s="59">
+      <c r="I85" s="92" t="n"/>
+      <c r="J85" s="93" t="n"/>
+      <c r="K85" s="61" t="n"/>
+      <c r="L85" s="62" t="n"/>
+      <c r="M85" s="59">
         <f>IF(I85="","",ROUND(I85-E85,2))</f>
         <v/>
       </c>
-      <c r="L85" s="60">
+      <c r="N85" s="60">
         <f>IF(J85="","",J85-F85)</f>
         <v/>
       </c>
-      <c r="M85" s="56" t="n"/>
-      <c r="N85" s="56" t="n"/>
+      <c r="O85" s="56" t="n"/>
+      <c r="P85" s="56" t="n"/>
     </row>
     <row r="86" ht="15" customHeight="1" s="47">
       <c r="A86" s="54" t="n"/>
@@ -3110,18 +3319,20 @@
       <c r="E86" s="59" t="n"/>
       <c r="F86" s="60" t="n"/>
       <c r="G86" s="54" t="n"/>
-      <c r="I86" s="61" t="n"/>
-      <c r="J86" s="62" t="n"/>
-      <c r="K86" s="59">
+      <c r="I86" s="92" t="n"/>
+      <c r="J86" s="93" t="n"/>
+      <c r="K86" s="61" t="n"/>
+      <c r="L86" s="62" t="n"/>
+      <c r="M86" s="59">
         <f>IF(I86="","",ROUND(I86-E86,2))</f>
         <v/>
       </c>
-      <c r="L86" s="60">
+      <c r="N86" s="60">
         <f>IF(J86="","",J86-F86)</f>
         <v/>
       </c>
-      <c r="M86" s="56" t="n"/>
-      <c r="N86" s="56" t="n"/>
+      <c r="O86" s="56" t="n"/>
+      <c r="P86" s="56" t="n"/>
     </row>
     <row r="87" ht="15" customHeight="1" s="47">
       <c r="A87" s="54" t="n"/>
@@ -3131,18 +3342,20 @@
       <c r="E87" s="59" t="n"/>
       <c r="F87" s="60" t="n"/>
       <c r="G87" s="54" t="n"/>
-      <c r="I87" s="61" t="n"/>
-      <c r="J87" s="62" t="n"/>
-      <c r="K87" s="59">
+      <c r="I87" s="92" t="n"/>
+      <c r="J87" s="93" t="n"/>
+      <c r="K87" s="61" t="n"/>
+      <c r="L87" s="62" t="n"/>
+      <c r="M87" s="59">
         <f>IF(I87="","",ROUND(I87-E87,2))</f>
         <v/>
       </c>
-      <c r="L87" s="60">
+      <c r="N87" s="60">
         <f>IF(J87="","",J87-F87)</f>
         <v/>
       </c>
-      <c r="M87" s="56" t="n"/>
-      <c r="N87" s="56" t="n"/>
+      <c r="O87" s="56" t="n"/>
+      <c r="P87" s="56" t="n"/>
     </row>
     <row r="88" ht="15" customHeight="1" s="47">
       <c r="A88" s="54" t="n"/>
@@ -3152,18 +3365,20 @@
       <c r="E88" s="59" t="n"/>
       <c r="F88" s="60" t="n"/>
       <c r="G88" s="54" t="n"/>
-      <c r="I88" s="61" t="n"/>
-      <c r="J88" s="62" t="n"/>
-      <c r="K88" s="59">
+      <c r="I88" s="92" t="n"/>
+      <c r="J88" s="93" t="n"/>
+      <c r="K88" s="61" t="n"/>
+      <c r="L88" s="62" t="n"/>
+      <c r="M88" s="59">
         <f>IF(I88="","",ROUND(I88-E88,2))</f>
         <v/>
       </c>
-      <c r="L88" s="60">
+      <c r="N88" s="60">
         <f>IF(J88="","",J88-F88)</f>
         <v/>
       </c>
-      <c r="M88" s="56" t="n"/>
-      <c r="N88" s="56" t="n"/>
+      <c r="O88" s="56" t="n"/>
+      <c r="P88" s="56" t="n"/>
     </row>
     <row r="89" ht="15" customHeight="1" s="47">
       <c r="A89" s="54" t="n"/>
@@ -3173,18 +3388,20 @@
       <c r="E89" s="59" t="n"/>
       <c r="F89" s="60" t="n"/>
       <c r="G89" s="54" t="n"/>
-      <c r="I89" s="61" t="n"/>
-      <c r="J89" s="62" t="n"/>
-      <c r="K89" s="59">
+      <c r="I89" s="92" t="n"/>
+      <c r="J89" s="93" t="n"/>
+      <c r="K89" s="61" t="n"/>
+      <c r="L89" s="62" t="n"/>
+      <c r="M89" s="59">
         <f>IF(I89="","",ROUND(I89-E89,2))</f>
         <v/>
       </c>
-      <c r="L89" s="60">
+      <c r="N89" s="60">
         <f>IF(J89="","",J89-F89)</f>
         <v/>
       </c>
-      <c r="M89" s="56" t="n"/>
-      <c r="N89" s="56" t="n"/>
+      <c r="O89" s="56" t="n"/>
+      <c r="P89" s="56" t="n"/>
     </row>
     <row r="90" ht="15" customHeight="1" s="47">
       <c r="A90" s="54" t="n"/>
@@ -3194,18 +3411,20 @@
       <c r="E90" s="59" t="n"/>
       <c r="F90" s="60" t="n"/>
       <c r="G90" s="54" t="n"/>
-      <c r="I90" s="61" t="n"/>
-      <c r="J90" s="62" t="n"/>
-      <c r="K90" s="59">
+      <c r="I90" s="92" t="n"/>
+      <c r="J90" s="93" t="n"/>
+      <c r="K90" s="61" t="n"/>
+      <c r="L90" s="62" t="n"/>
+      <c r="M90" s="59">
         <f>IF(I90="","",ROUND(I90-E90,2))</f>
         <v/>
       </c>
-      <c r="L90" s="60">
+      <c r="N90" s="60">
         <f>IF(J90="","",J90-F90)</f>
         <v/>
       </c>
-      <c r="M90" s="56" t="n"/>
-      <c r="N90" s="56" t="n"/>
+      <c r="O90" s="56" t="n"/>
+      <c r="P90" s="56" t="n"/>
     </row>
     <row r="91" ht="15" customHeight="1" s="47">
       <c r="A91" s="54" t="n"/>
@@ -3215,18 +3434,20 @@
       <c r="E91" s="59" t="n"/>
       <c r="F91" s="60" t="n"/>
       <c r="G91" s="54" t="n"/>
-      <c r="I91" s="61" t="n"/>
-      <c r="J91" s="62" t="n"/>
-      <c r="K91" s="59">
+      <c r="I91" s="92" t="n"/>
+      <c r="J91" s="93" t="n"/>
+      <c r="K91" s="61" t="n"/>
+      <c r="L91" s="62" t="n"/>
+      <c r="M91" s="59">
         <f>IF(I91="","",ROUND(I91-E91,2))</f>
         <v/>
       </c>
-      <c r="L91" s="60">
+      <c r="N91" s="60">
         <f>IF(J91="","",J91-F91)</f>
         <v/>
       </c>
-      <c r="M91" s="56" t="n"/>
-      <c r="N91" s="56" t="n"/>
+      <c r="O91" s="56" t="n"/>
+      <c r="P91" s="56" t="n"/>
     </row>
     <row r="92" ht="15" customHeight="1" s="47">
       <c r="A92" s="54" t="n"/>
@@ -3236,18 +3457,20 @@
       <c r="E92" s="59" t="n"/>
       <c r="F92" s="60" t="n"/>
       <c r="G92" s="54" t="n"/>
-      <c r="I92" s="61" t="n"/>
-      <c r="J92" s="62" t="n"/>
-      <c r="K92" s="59">
+      <c r="I92" s="92" t="n"/>
+      <c r="J92" s="93" t="n"/>
+      <c r="K92" s="61" t="n"/>
+      <c r="L92" s="62" t="n"/>
+      <c r="M92" s="59">
         <f>IF(I92="","",ROUND(I92-E92,2))</f>
         <v/>
       </c>
-      <c r="L92" s="60">
+      <c r="N92" s="60">
         <f>IF(J92="","",J92-F92)</f>
         <v/>
       </c>
-      <c r="M92" s="56" t="n"/>
-      <c r="N92" s="56" t="n"/>
+      <c r="O92" s="56" t="n"/>
+      <c r="P92" s="56" t="n"/>
     </row>
     <row r="93" ht="15" customHeight="1" s="47">
       <c r="A93" s="54" t="n"/>
@@ -3257,18 +3480,20 @@
       <c r="E93" s="59" t="n"/>
       <c r="F93" s="60" t="n"/>
       <c r="G93" s="54" t="n"/>
-      <c r="I93" s="61" t="n"/>
-      <c r="J93" s="62" t="n"/>
-      <c r="K93" s="59">
+      <c r="I93" s="92" t="n"/>
+      <c r="J93" s="93" t="n"/>
+      <c r="K93" s="61" t="n"/>
+      <c r="L93" s="62" t="n"/>
+      <c r="M93" s="59">
         <f>IF(I93="","",ROUND(I93-E93,2))</f>
         <v/>
       </c>
-      <c r="L93" s="60">
+      <c r="N93" s="60">
         <f>IF(J93="","",J93-F93)</f>
         <v/>
       </c>
-      <c r="M93" s="56" t="n"/>
-      <c r="N93" s="56" t="n"/>
+      <c r="O93" s="56" t="n"/>
+      <c r="P93" s="56" t="n"/>
     </row>
     <row r="94" ht="15" customHeight="1" s="47">
       <c r="A94" s="54" t="n"/>
@@ -3278,18 +3503,20 @@
       <c r="E94" s="59" t="n"/>
       <c r="F94" s="60" t="n"/>
       <c r="G94" s="54" t="n"/>
-      <c r="I94" s="61" t="n"/>
-      <c r="J94" s="62" t="n"/>
-      <c r="K94" s="59">
+      <c r="I94" s="92" t="n"/>
+      <c r="J94" s="93" t="n"/>
+      <c r="K94" s="61" t="n"/>
+      <c r="L94" s="62" t="n"/>
+      <c r="M94" s="59">
         <f>IF(I94="","",ROUND(I94-E94,2))</f>
         <v/>
       </c>
-      <c r="L94" s="60">
+      <c r="N94" s="60">
         <f>IF(J94="","",J94-F94)</f>
         <v/>
       </c>
-      <c r="M94" s="56" t="n"/>
-      <c r="N94" s="56" t="n"/>
+      <c r="O94" s="56" t="n"/>
+      <c r="P94" s="56" t="n"/>
     </row>
     <row r="95" ht="15" customHeight="1" s="47">
       <c r="A95" s="54" t="n"/>
@@ -3299,18 +3526,20 @@
       <c r="E95" s="59" t="n"/>
       <c r="F95" s="60" t="n"/>
       <c r="G95" s="54" t="n"/>
-      <c r="I95" s="61" t="n"/>
-      <c r="J95" s="62" t="n"/>
-      <c r="K95" s="59">
+      <c r="I95" s="92" t="n"/>
+      <c r="J95" s="93" t="n"/>
+      <c r="K95" s="61" t="n"/>
+      <c r="L95" s="62" t="n"/>
+      <c r="M95" s="59">
         <f>IF(I95="","",ROUND(I95-E95,2))</f>
         <v/>
       </c>
-      <c r="L95" s="60">
+      <c r="N95" s="60">
         <f>IF(J95="","",J95-F95)</f>
         <v/>
       </c>
-      <c r="M95" s="56" t="n"/>
-      <c r="N95" s="56" t="n"/>
+      <c r="O95" s="56" t="n"/>
+      <c r="P95" s="56" t="n"/>
     </row>
     <row r="96" ht="15" customHeight="1" s="47">
       <c r="A96" s="54" t="n"/>
@@ -3320,18 +3549,20 @@
       <c r="E96" s="59" t="n"/>
       <c r="F96" s="60" t="n"/>
       <c r="G96" s="54" t="n"/>
-      <c r="I96" s="61" t="n"/>
-      <c r="J96" s="62" t="n"/>
-      <c r="K96" s="59">
+      <c r="I96" s="92" t="n"/>
+      <c r="J96" s="93" t="n"/>
+      <c r="K96" s="61" t="n"/>
+      <c r="L96" s="62" t="n"/>
+      <c r="M96" s="59">
         <f>IF(I96="","",ROUND(I96-E96,2))</f>
         <v/>
       </c>
-      <c r="L96" s="60">
+      <c r="N96" s="60">
         <f>IF(J96="","",J96-F96)</f>
         <v/>
       </c>
-      <c r="M96" s="56" t="n"/>
-      <c r="N96" s="56" t="n"/>
+      <c r="O96" s="56" t="n"/>
+      <c r="P96" s="56" t="n"/>
     </row>
     <row r="97" ht="15" customHeight="1" s="47">
       <c r="A97" s="54" t="n"/>
@@ -3341,18 +3572,20 @@
       <c r="E97" s="59" t="n"/>
       <c r="F97" s="60" t="n"/>
       <c r="G97" s="54" t="n"/>
-      <c r="I97" s="61" t="n"/>
-      <c r="J97" s="62" t="n"/>
-      <c r="K97" s="59">
+      <c r="I97" s="92" t="n"/>
+      <c r="J97" s="93" t="n"/>
+      <c r="K97" s="61" t="n"/>
+      <c r="L97" s="62" t="n"/>
+      <c r="M97" s="59">
         <f>IF(I97="","",ROUND(I97-E97,2))</f>
         <v/>
       </c>
-      <c r="L97" s="60">
+      <c r="N97" s="60">
         <f>IF(J97="","",J97-F97)</f>
         <v/>
       </c>
-      <c r="M97" s="56" t="n"/>
-      <c r="N97" s="56" t="n"/>
+      <c r="O97" s="56" t="n"/>
+      <c r="P97" s="56" t="n"/>
     </row>
     <row r="98" ht="15" customHeight="1" s="47">
       <c r="A98" s="54" t="n"/>
@@ -3362,18 +3595,20 @@
       <c r="E98" s="59" t="n"/>
       <c r="F98" s="60" t="n"/>
       <c r="G98" s="54" t="n"/>
-      <c r="I98" s="61" t="n"/>
-      <c r="J98" s="62" t="n"/>
-      <c r="K98" s="59">
+      <c r="I98" s="92" t="n"/>
+      <c r="J98" s="93" t="n"/>
+      <c r="K98" s="61" t="n"/>
+      <c r="L98" s="62" t="n"/>
+      <c r="M98" s="59">
         <f>IF(I98="","",ROUND(I98-E98,2))</f>
         <v/>
       </c>
-      <c r="L98" s="60">
+      <c r="N98" s="60">
         <f>IF(J98="","",J98-F98)</f>
         <v/>
       </c>
-      <c r="M98" s="56" t="n"/>
-      <c r="N98" s="56" t="n"/>
+      <c r="O98" s="56" t="n"/>
+      <c r="P98" s="56" t="n"/>
     </row>
     <row r="99" ht="15" customHeight="1" s="47">
       <c r="A99" s="54" t="n"/>
@@ -3383,18 +3618,20 @@
       <c r="E99" s="59" t="n"/>
       <c r="F99" s="60" t="n"/>
       <c r="G99" s="54" t="n"/>
-      <c r="I99" s="61" t="n"/>
-      <c r="J99" s="62" t="n"/>
-      <c r="K99" s="59">
+      <c r="I99" s="92" t="n"/>
+      <c r="J99" s="93" t="n"/>
+      <c r="K99" s="61" t="n"/>
+      <c r="L99" s="62" t="n"/>
+      <c r="M99" s="59">
         <f>IF(I99="","",ROUND(I99-E99,2))</f>
         <v/>
       </c>
-      <c r="L99" s="60">
+      <c r="N99" s="60">
         <f>IF(J99="","",J99-F99)</f>
         <v/>
       </c>
-      <c r="M99" s="56" t="n"/>
-      <c r="N99" s="56" t="n"/>
+      <c r="O99" s="56" t="n"/>
+      <c r="P99" s="56" t="n"/>
     </row>
     <row r="100" ht="15" customHeight="1" s="47">
       <c r="A100" s="54" t="n"/>
@@ -3404,18 +3641,20 @@
       <c r="E100" s="59" t="n"/>
       <c r="F100" s="60" t="n"/>
       <c r="G100" s="54" t="n"/>
-      <c r="I100" s="61" t="n"/>
-      <c r="J100" s="62" t="n"/>
-      <c r="K100" s="59">
+      <c r="I100" s="92" t="n"/>
+      <c r="J100" s="93" t="n"/>
+      <c r="K100" s="61" t="n"/>
+      <c r="L100" s="62" t="n"/>
+      <c r="M100" s="59">
         <f>IF(I100="","",ROUND(I100-E100,2))</f>
         <v/>
       </c>
-      <c r="L100" s="60">
+      <c r="N100" s="60">
         <f>IF(J100="","",J100-F100)</f>
         <v/>
       </c>
-      <c r="M100" s="56" t="n"/>
-      <c r="N100" s="56" t="n"/>
+      <c r="O100" s="56" t="n"/>
+      <c r="P100" s="56" t="n"/>
     </row>
     <row r="101" ht="15" customHeight="1" s="47">
       <c r="A101" s="54" t="n"/>
@@ -3425,18 +3664,20 @@
       <c r="E101" s="59" t="n"/>
       <c r="F101" s="60" t="n"/>
       <c r="G101" s="54" t="n"/>
-      <c r="I101" s="61" t="n"/>
-      <c r="J101" s="62" t="n"/>
-      <c r="K101" s="59">
+      <c r="I101" s="92" t="n"/>
+      <c r="J101" s="93" t="n"/>
+      <c r="K101" s="61" t="n"/>
+      <c r="L101" s="62" t="n"/>
+      <c r="M101" s="59">
         <f>IF(I101="","",ROUND(I101-E101,2))</f>
         <v/>
       </c>
-      <c r="L101" s="60">
+      <c r="N101" s="60">
         <f>IF(J101="","",J101-F101)</f>
         <v/>
       </c>
-      <c r="M101" s="56" t="n"/>
-      <c r="N101" s="56" t="n"/>
+      <c r="O101" s="56" t="n"/>
+      <c r="P101" s="56" t="n"/>
     </row>
     <row r="102" ht="15" customHeight="1" s="47">
       <c r="A102" s="54" t="n"/>
@@ -3446,18 +3687,20 @@
       <c r="E102" s="59" t="n"/>
       <c r="F102" s="60" t="n"/>
       <c r="G102" s="54" t="n"/>
-      <c r="I102" s="61" t="n"/>
-      <c r="J102" s="62" t="n"/>
-      <c r="K102" s="59">
+      <c r="I102" s="92" t="n"/>
+      <c r="J102" s="93" t="n"/>
+      <c r="K102" s="61" t="n"/>
+      <c r="L102" s="62" t="n"/>
+      <c r="M102" s="59">
         <f>IF(I102="","",ROUND(I102-E102,2))</f>
         <v/>
       </c>
-      <c r="L102" s="60">
+      <c r="N102" s="60">
         <f>IF(J102="","",J102-F102)</f>
         <v/>
       </c>
-      <c r="M102" s="56" t="n"/>
-      <c r="N102" s="56" t="n"/>
+      <c r="O102" s="56" t="n"/>
+      <c r="P102" s="56" t="n"/>
     </row>
     <row r="103" ht="15" customHeight="1" s="47">
       <c r="A103" s="54" t="n"/>
@@ -3467,18 +3710,20 @@
       <c r="E103" s="59" t="n"/>
       <c r="F103" s="60" t="n"/>
       <c r="G103" s="54" t="n"/>
-      <c r="I103" s="61" t="n"/>
-      <c r="J103" s="62" t="n"/>
-      <c r="K103" s="59">
+      <c r="I103" s="92" t="n"/>
+      <c r="J103" s="93" t="n"/>
+      <c r="K103" s="61" t="n"/>
+      <c r="L103" s="62" t="n"/>
+      <c r="M103" s="59">
         <f>IF(I103="","",ROUND(I103-E103,2))</f>
         <v/>
       </c>
-      <c r="L103" s="60">
+      <c r="N103" s="60">
         <f>IF(J103="","",J103-F103)</f>
         <v/>
       </c>
-      <c r="M103" s="56" t="n"/>
-      <c r="N103" s="56" t="n"/>
+      <c r="O103" s="56" t="n"/>
+      <c r="P103" s="56" t="n"/>
     </row>
     <row r="104" ht="15" customHeight="1" s="47">
       <c r="A104" s="54" t="n"/>
@@ -3488,18 +3733,20 @@
       <c r="E104" s="59" t="n"/>
       <c r="F104" s="60" t="n"/>
       <c r="G104" s="54" t="n"/>
-      <c r="I104" s="61" t="n"/>
-      <c r="J104" s="62" t="n"/>
-      <c r="K104" s="59">
+      <c r="I104" s="92" t="n"/>
+      <c r="J104" s="93" t="n"/>
+      <c r="K104" s="61" t="n"/>
+      <c r="L104" s="62" t="n"/>
+      <c r="M104" s="59">
         <f>IF(I104="","",ROUND(I104-E104,2))</f>
         <v/>
       </c>
-      <c r="L104" s="60">
+      <c r="N104" s="60">
         <f>IF(J104="","",J104-F104)</f>
         <v/>
       </c>
-      <c r="M104" s="56" t="n"/>
-      <c r="N104" s="56" t="n"/>
+      <c r="O104" s="56" t="n"/>
+      <c r="P104" s="56" t="n"/>
     </row>
     <row r="105" ht="15" customHeight="1" s="47">
       <c r="A105" s="54" t="n"/>
@@ -3509,18 +3756,20 @@
       <c r="E105" s="59" t="n"/>
       <c r="F105" s="60" t="n"/>
       <c r="G105" s="54" t="n"/>
-      <c r="I105" s="61" t="n"/>
-      <c r="J105" s="62" t="n"/>
-      <c r="K105" s="59">
+      <c r="I105" s="92" t="n"/>
+      <c r="J105" s="93" t="n"/>
+      <c r="K105" s="61" t="n"/>
+      <c r="L105" s="62" t="n"/>
+      <c r="M105" s="59">
         <f>IF(I105="","",ROUND(I105-E105,2))</f>
         <v/>
       </c>
-      <c r="L105" s="60">
+      <c r="N105" s="60">
         <f>IF(J105="","",J105-F105)</f>
         <v/>
       </c>
-      <c r="M105" s="56" t="n"/>
-      <c r="N105" s="56" t="n"/>
+      <c r="O105" s="56" t="n"/>
+      <c r="P105" s="56" t="n"/>
     </row>
     <row r="106" ht="15" customHeight="1" s="47">
       <c r="A106" s="54" t="n"/>
@@ -3530,18 +3779,20 @@
       <c r="E106" s="59" t="n"/>
       <c r="F106" s="60" t="n"/>
       <c r="G106" s="54" t="n"/>
-      <c r="I106" s="61" t="n"/>
-      <c r="J106" s="62" t="n"/>
-      <c r="K106" s="59">
+      <c r="I106" s="92" t="n"/>
+      <c r="J106" s="93" t="n"/>
+      <c r="K106" s="61" t="n"/>
+      <c r="L106" s="62" t="n"/>
+      <c r="M106" s="59">
         <f>IF(I106="","",ROUND(I106-E106,2))</f>
         <v/>
       </c>
-      <c r="L106" s="60">
+      <c r="N106" s="60">
         <f>IF(J106="","",J106-F106)</f>
         <v/>
       </c>
-      <c r="M106" s="56" t="n"/>
-      <c r="N106" s="56" t="n"/>
+      <c r="O106" s="56" t="n"/>
+      <c r="P106" s="56" t="n"/>
     </row>
     <row r="107" ht="15" customHeight="1" s="47">
       <c r="A107" s="54" t="n"/>
@@ -3551,18 +3802,20 @@
       <c r="E107" s="59" t="n"/>
       <c r="F107" s="60" t="n"/>
       <c r="G107" s="54" t="n"/>
-      <c r="I107" s="61" t="n"/>
-      <c r="J107" s="62" t="n"/>
-      <c r="K107" s="59">
+      <c r="I107" s="92" t="n"/>
+      <c r="J107" s="93" t="n"/>
+      <c r="K107" s="61" t="n"/>
+      <c r="L107" s="62" t="n"/>
+      <c r="M107" s="59">
         <f>IF(I107="","",ROUND(I107-E107,2))</f>
         <v/>
       </c>
-      <c r="L107" s="60">
+      <c r="N107" s="60">
         <f>IF(J107="","",J107-F107)</f>
         <v/>
       </c>
-      <c r="M107" s="56" t="n"/>
-      <c r="N107" s="56" t="n"/>
+      <c r="O107" s="56" t="n"/>
+      <c r="P107" s="56" t="n"/>
     </row>
     <row r="108" ht="15" customHeight="1" s="47">
       <c r="A108" s="54" t="n"/>
@@ -3572,18 +3825,20 @@
       <c r="E108" s="59" t="n"/>
       <c r="F108" s="60" t="n"/>
       <c r="G108" s="54" t="n"/>
-      <c r="I108" s="61" t="n"/>
-      <c r="J108" s="62" t="n"/>
-      <c r="K108" s="59">
+      <c r="I108" s="92" t="n"/>
+      <c r="J108" s="93" t="n"/>
+      <c r="K108" s="61" t="n"/>
+      <c r="L108" s="62" t="n"/>
+      <c r="M108" s="59">
         <f>IF(I108="","",ROUND(I108-E108,2))</f>
         <v/>
       </c>
-      <c r="L108" s="60">
+      <c r="N108" s="60">
         <f>IF(J108="","",J108-F108)</f>
         <v/>
       </c>
-      <c r="M108" s="56" t="n"/>
-      <c r="N108" s="56" t="n"/>
+      <c r="O108" s="56" t="n"/>
+      <c r="P108" s="56" t="n"/>
     </row>
     <row r="109" ht="15" customHeight="1" s="47">
       <c r="A109" s="54" t="n"/>
@@ -3593,18 +3848,20 @@
       <c r="E109" s="59" t="n"/>
       <c r="F109" s="60" t="n"/>
       <c r="G109" s="54" t="n"/>
-      <c r="I109" s="61" t="n"/>
-      <c r="J109" s="62" t="n"/>
-      <c r="K109" s="59">
+      <c r="I109" s="92" t="n"/>
+      <c r="J109" s="93" t="n"/>
+      <c r="K109" s="61" t="n"/>
+      <c r="L109" s="62" t="n"/>
+      <c r="M109" s="59">
         <f>IF(I109="","",ROUND(I109-E109,2))</f>
         <v/>
       </c>
-      <c r="L109" s="60">
+      <c r="N109" s="60">
         <f>IF(J109="","",J109-F109)</f>
         <v/>
       </c>
-      <c r="M109" s="56" t="n"/>
-      <c r="N109" s="56" t="n"/>
+      <c r="O109" s="56" t="n"/>
+      <c r="P109" s="56" t="n"/>
     </row>
     <row r="110" ht="15" customHeight="1" s="47">
       <c r="A110" s="54" t="n"/>
@@ -3614,18 +3871,20 @@
       <c r="E110" s="59" t="n"/>
       <c r="F110" s="60" t="n"/>
       <c r="G110" s="54" t="n"/>
-      <c r="I110" s="61" t="n"/>
-      <c r="J110" s="62" t="n"/>
-      <c r="K110" s="59">
+      <c r="I110" s="92" t="n"/>
+      <c r="J110" s="93" t="n"/>
+      <c r="K110" s="61" t="n"/>
+      <c r="L110" s="62" t="n"/>
+      <c r="M110" s="59">
         <f>IF(I110="","",ROUND(I110-E110,2))</f>
         <v/>
       </c>
-      <c r="L110" s="60">
+      <c r="N110" s="60">
         <f>IF(J110="","",J110-F110)</f>
         <v/>
       </c>
-      <c r="M110" s="56" t="n"/>
-      <c r="N110" s="56" t="n"/>
+      <c r="O110" s="56" t="n"/>
+      <c r="P110" s="56" t="n"/>
     </row>
     <row r="111" ht="15" customHeight="1" s="47">
       <c r="A111" s="54" t="n"/>
@@ -3635,18 +3894,20 @@
       <c r="E111" s="59" t="n"/>
       <c r="F111" s="60" t="n"/>
       <c r="G111" s="54" t="n"/>
-      <c r="I111" s="61" t="n"/>
-      <c r="J111" s="62" t="n"/>
-      <c r="K111" s="59">
+      <c r="I111" s="92" t="n"/>
+      <c r="J111" s="93" t="n"/>
+      <c r="K111" s="61" t="n"/>
+      <c r="L111" s="62" t="n"/>
+      <c r="M111" s="59">
         <f>IF(I111="","",ROUND(I111-E111,2))</f>
         <v/>
       </c>
-      <c r="L111" s="60">
+      <c r="N111" s="60">
         <f>IF(J111="","",J111-F111)</f>
         <v/>
       </c>
-      <c r="M111" s="56" t="n"/>
-      <c r="N111" s="56" t="n"/>
+      <c r="O111" s="56" t="n"/>
+      <c r="P111" s="56" t="n"/>
     </row>
     <row r="112" ht="15" customHeight="1" s="47">
       <c r="A112" s="54" t="n"/>
@@ -3656,18 +3917,20 @@
       <c r="E112" s="59" t="n"/>
       <c r="F112" s="60" t="n"/>
       <c r="G112" s="54" t="n"/>
-      <c r="I112" s="61" t="n"/>
-      <c r="J112" s="62" t="n"/>
-      <c r="K112" s="59">
+      <c r="I112" s="92" t="n"/>
+      <c r="J112" s="93" t="n"/>
+      <c r="K112" s="61" t="n"/>
+      <c r="L112" s="62" t="n"/>
+      <c r="M112" s="59">
         <f>IF(I112="","",ROUND(I112-E112,2))</f>
         <v/>
       </c>
-      <c r="L112" s="60">
+      <c r="N112" s="60">
         <f>IF(J112="","",J112-F112)</f>
         <v/>
       </c>
-      <c r="M112" s="56" t="n"/>
-      <c r="N112" s="56" t="n"/>
+      <c r="O112" s="56" t="n"/>
+      <c r="P112" s="56" t="n"/>
     </row>
     <row r="113" ht="15" customHeight="1" s="47">
       <c r="A113" s="54" t="n"/>
@@ -3677,18 +3940,20 @@
       <c r="E113" s="59" t="n"/>
       <c r="F113" s="60" t="n"/>
       <c r="G113" s="54" t="n"/>
-      <c r="I113" s="61" t="n"/>
-      <c r="J113" s="62" t="n"/>
-      <c r="K113" s="59">
+      <c r="I113" s="92" t="n"/>
+      <c r="J113" s="93" t="n"/>
+      <c r="K113" s="61" t="n"/>
+      <c r="L113" s="62" t="n"/>
+      <c r="M113" s="59">
         <f>IF(I113="","",ROUND(I113-E113,2))</f>
         <v/>
       </c>
-      <c r="L113" s="60">
+      <c r="N113" s="60">
         <f>IF(J113="","",J113-F113)</f>
         <v/>
       </c>
-      <c r="M113" s="56" t="n"/>
-      <c r="N113" s="56" t="n"/>
+      <c r="O113" s="56" t="n"/>
+      <c r="P113" s="56" t="n"/>
     </row>
     <row r="114" ht="15" customHeight="1" s="47">
       <c r="A114" s="54" t="n"/>
@@ -3698,18 +3963,20 @@
       <c r="E114" s="59" t="n"/>
       <c r="F114" s="60" t="n"/>
       <c r="G114" s="54" t="n"/>
-      <c r="I114" s="61" t="n"/>
-      <c r="J114" s="62" t="n"/>
-      <c r="K114" s="59">
+      <c r="I114" s="92" t="n"/>
+      <c r="J114" s="93" t="n"/>
+      <c r="K114" s="61" t="n"/>
+      <c r="L114" s="62" t="n"/>
+      <c r="M114" s="59">
         <f>IF(I114="","",ROUND(I114-E114,2))</f>
         <v/>
       </c>
-      <c r="L114" s="60">
+      <c r="N114" s="60">
         <f>IF(J114="","",J114-F114)</f>
         <v/>
       </c>
-      <c r="M114" s="56" t="n"/>
-      <c r="N114" s="56" t="n"/>
+      <c r="O114" s="56" t="n"/>
+      <c r="P114" s="56" t="n"/>
     </row>
     <row r="115" ht="15" customHeight="1" s="47">
       <c r="A115" s="54" t="n"/>
@@ -3719,18 +3986,20 @@
       <c r="E115" s="59" t="n"/>
       <c r="F115" s="60" t="n"/>
       <c r="G115" s="54" t="n"/>
-      <c r="I115" s="61" t="n"/>
-      <c r="J115" s="62" t="n"/>
-      <c r="K115" s="59">
+      <c r="I115" s="92" t="n"/>
+      <c r="J115" s="93" t="n"/>
+      <c r="K115" s="61" t="n"/>
+      <c r="L115" s="62" t="n"/>
+      <c r="M115" s="59">
         <f>IF(I115="","",ROUND(I115-E115,2))</f>
         <v/>
       </c>
-      <c r="L115" s="60">
+      <c r="N115" s="60">
         <f>IF(J115="","",J115-F115)</f>
         <v/>
       </c>
-      <c r="M115" s="56" t="n"/>
-      <c r="N115" s="56" t="n"/>
+      <c r="O115" s="56" t="n"/>
+      <c r="P115" s="56" t="n"/>
     </row>
     <row r="116" ht="15" customHeight="1" s="47">
       <c r="A116" s="54" t="n"/>
@@ -3740,18 +4009,20 @@
       <c r="E116" s="59" t="n"/>
       <c r="F116" s="60" t="n"/>
       <c r="G116" s="54" t="n"/>
-      <c r="I116" s="61" t="n"/>
-      <c r="J116" s="62" t="n"/>
-      <c r="K116" s="59">
+      <c r="I116" s="92" t="n"/>
+      <c r="J116" s="93" t="n"/>
+      <c r="K116" s="61" t="n"/>
+      <c r="L116" s="62" t="n"/>
+      <c r="M116" s="59">
         <f>IF(I116="","",ROUND(I116-E116,2))</f>
         <v/>
       </c>
-      <c r="L116" s="60">
+      <c r="N116" s="60">
         <f>IF(J116="","",J116-F116)</f>
         <v/>
       </c>
-      <c r="M116" s="56" t="n"/>
-      <c r="N116" s="56" t="n"/>
+      <c r="O116" s="56" t="n"/>
+      <c r="P116" s="56" t="n"/>
     </row>
     <row r="117" ht="15" customHeight="1" s="47">
       <c r="A117" s="54" t="n"/>
@@ -3761,18 +4032,20 @@
       <c r="E117" s="59" t="n"/>
       <c r="F117" s="60" t="n"/>
       <c r="G117" s="54" t="n"/>
-      <c r="I117" s="61" t="n"/>
-      <c r="J117" s="62" t="n"/>
-      <c r="K117" s="59">
+      <c r="I117" s="92" t="n"/>
+      <c r="J117" s="93" t="n"/>
+      <c r="K117" s="61" t="n"/>
+      <c r="L117" s="62" t="n"/>
+      <c r="M117" s="59">
         <f>IF(I117="","",ROUND(I117-E117,2))</f>
         <v/>
       </c>
-      <c r="L117" s="60">
+      <c r="N117" s="60">
         <f>IF(J117="","",J117-F117)</f>
         <v/>
       </c>
-      <c r="M117" s="56" t="n"/>
-      <c r="N117" s="56" t="n"/>
+      <c r="O117" s="56" t="n"/>
+      <c r="P117" s="56" t="n"/>
     </row>
     <row r="118" ht="15" customHeight="1" s="47">
       <c r="A118" s="54" t="n"/>
@@ -3782,18 +4055,20 @@
       <c r="E118" s="59" t="n"/>
       <c r="F118" s="60" t="n"/>
       <c r="G118" s="54" t="n"/>
-      <c r="I118" s="61" t="n"/>
-      <c r="J118" s="62" t="n"/>
-      <c r="K118" s="59">
+      <c r="I118" s="92" t="n"/>
+      <c r="J118" s="93" t="n"/>
+      <c r="K118" s="61" t="n"/>
+      <c r="L118" s="62" t="n"/>
+      <c r="M118" s="59">
         <f>IF(I118="","",ROUND(I118-E118,2))</f>
         <v/>
       </c>
-      <c r="L118" s="60">
+      <c r="N118" s="60">
         <f>IF(J118="","",J118-F118)</f>
         <v/>
       </c>
-      <c r="M118" s="56" t="n"/>
-      <c r="N118" s="56" t="n"/>
+      <c r="O118" s="56" t="n"/>
+      <c r="P118" s="56" t="n"/>
     </row>
     <row r="119" ht="15" customHeight="1" s="47">
       <c r="A119" s="54" t="n"/>
@@ -3803,18 +4078,20 @@
       <c r="E119" s="59" t="n"/>
       <c r="F119" s="60" t="n"/>
       <c r="G119" s="54" t="n"/>
-      <c r="I119" s="61" t="n"/>
-      <c r="J119" s="62" t="n"/>
-      <c r="K119" s="59">
+      <c r="I119" s="92" t="n"/>
+      <c r="J119" s="93" t="n"/>
+      <c r="K119" s="61" t="n"/>
+      <c r="L119" s="62" t="n"/>
+      <c r="M119" s="59">
         <f>IF(I119="","",ROUND(I119-E119,2))</f>
         <v/>
       </c>
-      <c r="L119" s="60">
+      <c r="N119" s="60">
         <f>IF(J119="","",J119-F119)</f>
         <v/>
       </c>
-      <c r="M119" s="56" t="n"/>
-      <c r="N119" s="56" t="n"/>
+      <c r="O119" s="56" t="n"/>
+      <c r="P119" s="56" t="n"/>
     </row>
     <row r="120" ht="15" customHeight="1" s="47">
       <c r="A120" s="54" t="n"/>
@@ -3824,18 +4101,20 @@
       <c r="E120" s="59" t="n"/>
       <c r="F120" s="60" t="n"/>
       <c r="G120" s="54" t="n"/>
-      <c r="I120" s="61" t="n"/>
-      <c r="J120" s="62" t="n"/>
-      <c r="K120" s="59">
+      <c r="I120" s="92" t="n"/>
+      <c r="J120" s="93" t="n"/>
+      <c r="K120" s="61" t="n"/>
+      <c r="L120" s="62" t="n"/>
+      <c r="M120" s="59">
         <f>IF(I120="","",ROUND(I120-E120,2))</f>
         <v/>
       </c>
-      <c r="L120" s="60">
+      <c r="N120" s="60">
         <f>IF(J120="","",J120-F120)</f>
         <v/>
       </c>
-      <c r="M120" s="56" t="n"/>
-      <c r="N120" s="56" t="n"/>
+      <c r="O120" s="56" t="n"/>
+      <c r="P120" s="56" t="n"/>
     </row>
     <row r="121" ht="15" customHeight="1" s="47">
       <c r="A121" s="54" t="n"/>
@@ -3845,18 +4124,20 @@
       <c r="E121" s="59" t="n"/>
       <c r="F121" s="60" t="n"/>
       <c r="G121" s="54" t="n"/>
-      <c r="I121" s="61" t="n"/>
-      <c r="J121" s="62" t="n"/>
-      <c r="K121" s="59">
+      <c r="I121" s="92" t="n"/>
+      <c r="J121" s="93" t="n"/>
+      <c r="K121" s="61" t="n"/>
+      <c r="L121" s="62" t="n"/>
+      <c r="M121" s="59">
         <f>IF(I121="","",ROUND(I121-E121,2))</f>
         <v/>
       </c>
-      <c r="L121" s="60">
+      <c r="N121" s="60">
         <f>IF(J121="","",J121-F121)</f>
         <v/>
       </c>
-      <c r="M121" s="56" t="n"/>
-      <c r="N121" s="56" t="n"/>
+      <c r="O121" s="56" t="n"/>
+      <c r="P121" s="56" t="n"/>
     </row>
     <row r="122" ht="15" customHeight="1" s="47">
       <c r="A122" s="54" t="n"/>
@@ -3866,18 +4147,20 @@
       <c r="E122" s="59" t="n"/>
       <c r="F122" s="60" t="n"/>
       <c r="G122" s="54" t="n"/>
-      <c r="I122" s="61" t="n"/>
-      <c r="J122" s="62" t="n"/>
-      <c r="K122" s="59">
+      <c r="I122" s="92" t="n"/>
+      <c r="J122" s="93" t="n"/>
+      <c r="K122" s="61" t="n"/>
+      <c r="L122" s="62" t="n"/>
+      <c r="M122" s="59">
         <f>IF(I122="","",ROUND(I122-E122,2))</f>
         <v/>
       </c>
-      <c r="L122" s="60">
+      <c r="N122" s="60">
         <f>IF(J122="","",J122-F122)</f>
         <v/>
       </c>
-      <c r="M122" s="56" t="n"/>
-      <c r="N122" s="56" t="n"/>
+      <c r="O122" s="56" t="n"/>
+      <c r="P122" s="56" t="n"/>
     </row>
     <row r="123" ht="15" customHeight="1" s="47">
       <c r="A123" s="54" t="n"/>
@@ -3887,18 +4170,20 @@
       <c r="E123" s="59" t="n"/>
       <c r="F123" s="60" t="n"/>
       <c r="G123" s="54" t="n"/>
-      <c r="I123" s="61" t="n"/>
-      <c r="J123" s="62" t="n"/>
-      <c r="K123" s="59">
+      <c r="I123" s="92" t="n"/>
+      <c r="J123" s="93" t="n"/>
+      <c r="K123" s="61" t="n"/>
+      <c r="L123" s="62" t="n"/>
+      <c r="M123" s="59">
         <f>IF(I123="","",ROUND(I123-E123,2))</f>
         <v/>
       </c>
-      <c r="L123" s="60">
+      <c r="N123" s="60">
         <f>IF(J123="","",J123-F123)</f>
         <v/>
       </c>
-      <c r="M123" s="56" t="n"/>
-      <c r="N123" s="56" t="n"/>
+      <c r="O123" s="56" t="n"/>
+      <c r="P123" s="56" t="n"/>
     </row>
     <row r="124" ht="15" customHeight="1" s="47">
       <c r="A124" s="54" t="n"/>
@@ -3908,18 +4193,20 @@
       <c r="E124" s="59" t="n"/>
       <c r="F124" s="60" t="n"/>
       <c r="G124" s="54" t="n"/>
-      <c r="I124" s="61" t="n"/>
-      <c r="J124" s="62" t="n"/>
-      <c r="K124" s="59">
+      <c r="I124" s="92" t="n"/>
+      <c r="J124" s="93" t="n"/>
+      <c r="K124" s="61" t="n"/>
+      <c r="L124" s="62" t="n"/>
+      <c r="M124" s="59">
         <f>IF(I124="","",ROUND(I124-E124,2))</f>
         <v/>
       </c>
-      <c r="L124" s="60">
+      <c r="N124" s="60">
         <f>IF(J124="","",J124-F124)</f>
         <v/>
       </c>
-      <c r="M124" s="56" t="n"/>
-      <c r="N124" s="56" t="n"/>
+      <c r="O124" s="56" t="n"/>
+      <c r="P124" s="56" t="n"/>
     </row>
     <row r="125" ht="15" customHeight="1" s="47">
       <c r="A125" s="54" t="n"/>
@@ -3929,18 +4216,20 @@
       <c r="E125" s="59" t="n"/>
       <c r="F125" s="60" t="n"/>
       <c r="G125" s="54" t="n"/>
-      <c r="I125" s="61" t="n"/>
-      <c r="J125" s="62" t="n"/>
-      <c r="K125" s="59">
+      <c r="I125" s="92" t="n"/>
+      <c r="J125" s="93" t="n"/>
+      <c r="K125" s="61" t="n"/>
+      <c r="L125" s="62" t="n"/>
+      <c r="M125" s="59">
         <f>IF(I125="","",ROUND(I125-E125,2))</f>
         <v/>
       </c>
-      <c r="L125" s="60">
+      <c r="N125" s="60">
         <f>IF(J125="","",J125-F125)</f>
         <v/>
       </c>
-      <c r="M125" s="56" t="n"/>
-      <c r="N125" s="56" t="n"/>
+      <c r="O125" s="56" t="n"/>
+      <c r="P125" s="56" t="n"/>
     </row>
     <row r="126" ht="15" customHeight="1" s="47">
       <c r="A126" s="54" t="n"/>
@@ -3950,18 +4239,20 @@
       <c r="E126" s="59" t="n"/>
       <c r="F126" s="60" t="n"/>
       <c r="G126" s="54" t="n"/>
-      <c r="I126" s="61" t="n"/>
-      <c r="J126" s="62" t="n"/>
-      <c r="K126" s="59">
+      <c r="I126" s="92" t="n"/>
+      <c r="J126" s="93" t="n"/>
+      <c r="K126" s="61" t="n"/>
+      <c r="L126" s="62" t="n"/>
+      <c r="M126" s="59">
         <f>IF(I126="","",ROUND(I126-E126,2))</f>
         <v/>
       </c>
-      <c r="L126" s="60">
+      <c r="N126" s="60">
         <f>IF(J126="","",J126-F126)</f>
         <v/>
       </c>
-      <c r="M126" s="56" t="n"/>
-      <c r="N126" s="56" t="n"/>
+      <c r="O126" s="56" t="n"/>
+      <c r="P126" s="56" t="n"/>
     </row>
     <row r="127" ht="15" customHeight="1" s="47">
       <c r="A127" s="54" t="n"/>
@@ -3971,18 +4262,20 @@
       <c r="E127" s="59" t="n"/>
       <c r="F127" s="60" t="n"/>
       <c r="G127" s="54" t="n"/>
-      <c r="I127" s="61" t="n"/>
-      <c r="J127" s="62" t="n"/>
-      <c r="K127" s="59">
+      <c r="I127" s="92" t="n"/>
+      <c r="J127" s="93" t="n"/>
+      <c r="K127" s="61" t="n"/>
+      <c r="L127" s="62" t="n"/>
+      <c r="M127" s="59">
         <f>IF(I127="","",ROUND(I127-E127,2))</f>
         <v/>
       </c>
-      <c r="L127" s="60">
+      <c r="N127" s="60">
         <f>IF(J127="","",J127-F127)</f>
         <v/>
       </c>
-      <c r="M127" s="56" t="n"/>
-      <c r="N127" s="56" t="n"/>
+      <c r="O127" s="56" t="n"/>
+      <c r="P127" s="56" t="n"/>
     </row>
     <row r="128" ht="15" customHeight="1" s="47">
       <c r="A128" s="54" t="n"/>
@@ -3992,18 +4285,20 @@
       <c r="E128" s="59" t="n"/>
       <c r="F128" s="60" t="n"/>
       <c r="G128" s="54" t="n"/>
-      <c r="I128" s="61" t="n"/>
-      <c r="J128" s="62" t="n"/>
-      <c r="K128" s="59">
+      <c r="I128" s="92" t="n"/>
+      <c r="J128" s="93" t="n"/>
+      <c r="K128" s="61" t="n"/>
+      <c r="L128" s="62" t="n"/>
+      <c r="M128" s="59">
         <f>IF(I128="","",ROUND(I128-E128,2))</f>
         <v/>
       </c>
-      <c r="L128" s="60">
+      <c r="N128" s="60">
         <f>IF(J128="","",J128-F128)</f>
         <v/>
       </c>
-      <c r="M128" s="56" t="n"/>
-      <c r="N128" s="56" t="n"/>
+      <c r="O128" s="56" t="n"/>
+      <c r="P128" s="56" t="n"/>
     </row>
     <row r="129" ht="15" customHeight="1" s="47">
       <c r="A129" s="54" t="n"/>
@@ -4013,18 +4308,20 @@
       <c r="E129" s="59" t="n"/>
       <c r="F129" s="60" t="n"/>
       <c r="G129" s="54" t="n"/>
-      <c r="I129" s="61" t="n"/>
-      <c r="J129" s="62" t="n"/>
-      <c r="K129" s="59">
+      <c r="I129" s="92" t="n"/>
+      <c r="J129" s="93" t="n"/>
+      <c r="K129" s="61" t="n"/>
+      <c r="L129" s="62" t="n"/>
+      <c r="M129" s="59">
         <f>IF(I129="","",ROUND(I129-E129,2))</f>
         <v/>
       </c>
-      <c r="L129" s="60">
+      <c r="N129" s="60">
         <f>IF(J129="","",J129-F129)</f>
         <v/>
       </c>
-      <c r="M129" s="56" t="n"/>
-      <c r="N129" s="56" t="n"/>
+      <c r="O129" s="56" t="n"/>
+      <c r="P129" s="56" t="n"/>
     </row>
     <row r="130" ht="15" customHeight="1" s="47">
       <c r="A130" s="54" t="n"/>
@@ -4034,18 +4331,20 @@
       <c r="E130" s="59" t="n"/>
       <c r="F130" s="60" t="n"/>
       <c r="G130" s="54" t="n"/>
-      <c r="I130" s="61" t="n"/>
-      <c r="J130" s="62" t="n"/>
-      <c r="K130" s="59">
+      <c r="I130" s="92" t="n"/>
+      <c r="J130" s="93" t="n"/>
+      <c r="K130" s="61" t="n"/>
+      <c r="L130" s="62" t="n"/>
+      <c r="M130" s="59">
         <f>IF(I130="","",ROUND(I130-E130,2))</f>
         <v/>
       </c>
-      <c r="L130" s="60">
+      <c r="N130" s="60">
         <f>IF(J130="","",J130-F130)</f>
         <v/>
       </c>
-      <c r="M130" s="56" t="n"/>
-      <c r="N130" s="56" t="n"/>
+      <c r="O130" s="56" t="n"/>
+      <c r="P130" s="56" t="n"/>
     </row>
     <row r="131" ht="15" customHeight="1" s="47">
       <c r="A131" s="54" t="n"/>
@@ -4055,18 +4354,20 @@
       <c r="E131" s="59" t="n"/>
       <c r="F131" s="60" t="n"/>
       <c r="G131" s="54" t="n"/>
-      <c r="I131" s="61" t="n"/>
-      <c r="J131" s="62" t="n"/>
-      <c r="K131" s="59">
+      <c r="I131" s="92" t="n"/>
+      <c r="J131" s="93" t="n"/>
+      <c r="K131" s="61" t="n"/>
+      <c r="L131" s="62" t="n"/>
+      <c r="M131" s="59">
         <f>IF(I131="","",ROUND(I131-E131,2))</f>
         <v/>
       </c>
-      <c r="L131" s="60">
+      <c r="N131" s="60">
         <f>IF(J131="","",J131-F131)</f>
         <v/>
       </c>
-      <c r="M131" s="56" t="n"/>
-      <c r="N131" s="56" t="n"/>
+      <c r="O131" s="56" t="n"/>
+      <c r="P131" s="56" t="n"/>
     </row>
     <row r="132" ht="15" customHeight="1" s="47">
       <c r="A132" s="54" t="n"/>
@@ -4076,18 +4377,20 @@
       <c r="E132" s="59" t="n"/>
       <c r="F132" s="60" t="n"/>
       <c r="G132" s="54" t="n"/>
-      <c r="I132" s="61" t="n"/>
-      <c r="J132" s="62" t="n"/>
-      <c r="K132" s="59">
+      <c r="I132" s="92" t="n"/>
+      <c r="J132" s="93" t="n"/>
+      <c r="K132" s="61" t="n"/>
+      <c r="L132" s="62" t="n"/>
+      <c r="M132" s="59">
         <f>IF(I132="","",ROUND(I132-E132,2))</f>
         <v/>
       </c>
-      <c r="L132" s="60">
+      <c r="N132" s="60">
         <f>IF(J132="","",J132-F132)</f>
         <v/>
       </c>
-      <c r="M132" s="56" t="n"/>
-      <c r="N132" s="56" t="n"/>
+      <c r="O132" s="56" t="n"/>
+      <c r="P132" s="56" t="n"/>
     </row>
     <row r="133" ht="15" customHeight="1" s="47">
       <c r="A133" s="54" t="n"/>
@@ -4097,18 +4400,20 @@
       <c r="E133" s="59" t="n"/>
       <c r="F133" s="60" t="n"/>
       <c r="G133" s="54" t="n"/>
-      <c r="I133" s="61" t="n"/>
-      <c r="J133" s="62" t="n"/>
-      <c r="K133" s="59">
+      <c r="I133" s="92" t="n"/>
+      <c r="J133" s="93" t="n"/>
+      <c r="K133" s="61" t="n"/>
+      <c r="L133" s="62" t="n"/>
+      <c r="M133" s="59">
         <f>IF(I133="","",ROUND(I133-E133,2))</f>
         <v/>
       </c>
-      <c r="L133" s="60">
+      <c r="N133" s="60">
         <f>IF(J133="","",J133-F133)</f>
         <v/>
       </c>
-      <c r="M133" s="56" t="n"/>
-      <c r="N133" s="56" t="n"/>
+      <c r="O133" s="56" t="n"/>
+      <c r="P133" s="56" t="n"/>
     </row>
     <row r="134" ht="15" customHeight="1" s="47">
       <c r="A134" s="54" t="n"/>
@@ -4118,18 +4423,20 @@
       <c r="E134" s="59" t="n"/>
       <c r="F134" s="60" t="n"/>
       <c r="G134" s="54" t="n"/>
-      <c r="I134" s="61" t="n"/>
-      <c r="J134" s="62" t="n"/>
-      <c r="K134" s="59">
+      <c r="I134" s="92" t="n"/>
+      <c r="J134" s="93" t="n"/>
+      <c r="K134" s="61" t="n"/>
+      <c r="L134" s="62" t="n"/>
+      <c r="M134" s="59">
         <f>IF(I134="","",ROUND(I134-E134,2))</f>
         <v/>
       </c>
-      <c r="L134" s="60">
+      <c r="N134" s="60">
         <f>IF(J134="","",J134-F134)</f>
         <v/>
       </c>
-      <c r="M134" s="56" t="n"/>
-      <c r="N134" s="56" t="n"/>
+      <c r="O134" s="56" t="n"/>
+      <c r="P134" s="56" t="n"/>
     </row>
     <row r="135" ht="15" customHeight="1" s="47">
       <c r="A135" s="54" t="n"/>
@@ -4139,18 +4446,20 @@
       <c r="E135" s="59" t="n"/>
       <c r="F135" s="60" t="n"/>
       <c r="G135" s="54" t="n"/>
-      <c r="I135" s="61" t="n"/>
-      <c r="J135" s="62" t="n"/>
-      <c r="K135" s="59">
+      <c r="I135" s="92" t="n"/>
+      <c r="J135" s="93" t="n"/>
+      <c r="K135" s="61" t="n"/>
+      <c r="L135" s="62" t="n"/>
+      <c r="M135" s="59">
         <f>IF(I135="","",ROUND(I135-E135,2))</f>
         <v/>
       </c>
-      <c r="L135" s="60">
+      <c r="N135" s="60">
         <f>IF(J135="","",J135-F135)</f>
         <v/>
       </c>
-      <c r="M135" s="56" t="n"/>
-      <c r="N135" s="56" t="n"/>
+      <c r="O135" s="56" t="n"/>
+      <c r="P135" s="56" t="n"/>
     </row>
     <row r="136" ht="15" customHeight="1" s="47">
       <c r="A136" s="54" t="n"/>
@@ -4160,18 +4469,20 @@
       <c r="E136" s="59" t="n"/>
       <c r="F136" s="60" t="n"/>
       <c r="G136" s="54" t="n"/>
-      <c r="I136" s="61" t="n"/>
-      <c r="J136" s="62" t="n"/>
-      <c r="K136" s="59">
+      <c r="I136" s="92" t="n"/>
+      <c r="J136" s="93" t="n"/>
+      <c r="K136" s="61" t="n"/>
+      <c r="L136" s="62" t="n"/>
+      <c r="M136" s="59">
         <f>IF(I136="","",ROUND(I136-E136,2))</f>
         <v/>
       </c>
-      <c r="L136" s="60">
+      <c r="N136" s="60">
         <f>IF(J136="","",J136-F136)</f>
         <v/>
       </c>
-      <c r="M136" s="56" t="n"/>
-      <c r="N136" s="56" t="n"/>
+      <c r="O136" s="56" t="n"/>
+      <c r="P136" s="56" t="n"/>
     </row>
     <row r="137" ht="15" customHeight="1" s="47">
       <c r="A137" s="54" t="n"/>
@@ -4181,18 +4492,20 @@
       <c r="E137" s="59" t="n"/>
       <c r="F137" s="60" t="n"/>
       <c r="G137" s="54" t="n"/>
-      <c r="I137" s="61" t="n"/>
-      <c r="J137" s="62" t="n"/>
-      <c r="K137" s="59">
+      <c r="I137" s="92" t="n"/>
+      <c r="J137" s="93" t="n"/>
+      <c r="K137" s="61" t="n"/>
+      <c r="L137" s="62" t="n"/>
+      <c r="M137" s="59">
         <f>IF(I137="","",ROUND(I137-E137,2))</f>
         <v/>
       </c>
-      <c r="L137" s="60">
+      <c r="N137" s="60">
         <f>IF(J137="","",J137-F137)</f>
         <v/>
       </c>
-      <c r="M137" s="56" t="n"/>
-      <c r="N137" s="56" t="n"/>
+      <c r="O137" s="56" t="n"/>
+      <c r="P137" s="56" t="n"/>
     </row>
     <row r="138" ht="15" customHeight="1" s="47">
       <c r="A138" s="54" t="n"/>
@@ -4202,18 +4515,20 @@
       <c r="E138" s="59" t="n"/>
       <c r="F138" s="60" t="n"/>
       <c r="G138" s="54" t="n"/>
-      <c r="I138" s="61" t="n"/>
-      <c r="J138" s="62" t="n"/>
-      <c r="K138" s="59">
+      <c r="I138" s="92" t="n"/>
+      <c r="J138" s="93" t="n"/>
+      <c r="K138" s="61" t="n"/>
+      <c r="L138" s="62" t="n"/>
+      <c r="M138" s="59">
         <f>IF(I138="","",ROUND(I138-E138,2))</f>
         <v/>
       </c>
-      <c r="L138" s="60">
+      <c r="N138" s="60">
         <f>IF(J138="","",J138-F138)</f>
         <v/>
       </c>
-      <c r="M138" s="56" t="n"/>
-      <c r="N138" s="56" t="n"/>
+      <c r="O138" s="56" t="n"/>
+      <c r="P138" s="56" t="n"/>
     </row>
     <row r="139" ht="15" customHeight="1" s="47">
       <c r="A139" s="54" t="n"/>
@@ -4223,18 +4538,20 @@
       <c r="E139" s="59" t="n"/>
       <c r="F139" s="60" t="n"/>
       <c r="G139" s="54" t="n"/>
-      <c r="I139" s="61" t="n"/>
-      <c r="J139" s="62" t="n"/>
-      <c r="K139" s="59">
+      <c r="I139" s="92" t="n"/>
+      <c r="J139" s="93" t="n"/>
+      <c r="K139" s="61" t="n"/>
+      <c r="L139" s="62" t="n"/>
+      <c r="M139" s="59">
         <f>IF(I139="","",ROUND(I139-E139,2))</f>
         <v/>
       </c>
-      <c r="L139" s="60">
+      <c r="N139" s="60">
         <f>IF(J139="","",J139-F139)</f>
         <v/>
       </c>
-      <c r="M139" s="56" t="n"/>
-      <c r="N139" s="56" t="n"/>
+      <c r="O139" s="56" t="n"/>
+      <c r="P139" s="56" t="n"/>
     </row>
     <row r="140" ht="15" customHeight="1" s="47">
       <c r="A140" s="54" t="n"/>
@@ -4244,18 +4561,20 @@
       <c r="E140" s="59" t="n"/>
       <c r="F140" s="60" t="n"/>
       <c r="G140" s="54" t="n"/>
-      <c r="I140" s="61" t="n"/>
-      <c r="J140" s="62" t="n"/>
-      <c r="K140" s="59">
+      <c r="I140" s="92" t="n"/>
+      <c r="J140" s="93" t="n"/>
+      <c r="K140" s="61" t="n"/>
+      <c r="L140" s="62" t="n"/>
+      <c r="M140" s="59">
         <f>IF(I140="","",ROUND(I140-E140,2))</f>
         <v/>
       </c>
-      <c r="L140" s="60">
+      <c r="N140" s="60">
         <f>IF(J140="","",J140-F140)</f>
         <v/>
       </c>
-      <c r="M140" s="56" t="n"/>
-      <c r="N140" s="56" t="n"/>
+      <c r="O140" s="56" t="n"/>
+      <c r="P140" s="56" t="n"/>
     </row>
     <row r="141" ht="15" customHeight="1" s="47">
       <c r="A141" s="54" t="n"/>
@@ -4265,18 +4584,20 @@
       <c r="E141" s="59" t="n"/>
       <c r="F141" s="60" t="n"/>
       <c r="G141" s="54" t="n"/>
-      <c r="I141" s="61" t="n"/>
-      <c r="J141" s="62" t="n"/>
-      <c r="K141" s="59">
+      <c r="I141" s="92" t="n"/>
+      <c r="J141" s="93" t="n"/>
+      <c r="K141" s="61" t="n"/>
+      <c r="L141" s="62" t="n"/>
+      <c r="M141" s="59">
         <f>IF(I141="","",ROUND(I141-E141,2))</f>
         <v/>
       </c>
-      <c r="L141" s="60">
+      <c r="N141" s="60">
         <f>IF(J141="","",J141-F141)</f>
         <v/>
       </c>
-      <c r="M141" s="56" t="n"/>
-      <c r="N141" s="56" t="n"/>
+      <c r="O141" s="56" t="n"/>
+      <c r="P141" s="56" t="n"/>
     </row>
     <row r="142" ht="15" customHeight="1" s="47">
       <c r="A142" s="54" t="n"/>
@@ -4286,18 +4607,20 @@
       <c r="E142" s="59" t="n"/>
       <c r="F142" s="60" t="n"/>
       <c r="G142" s="54" t="n"/>
-      <c r="I142" s="61" t="n"/>
-      <c r="J142" s="62" t="n"/>
-      <c r="K142" s="59">
+      <c r="I142" s="92" t="n"/>
+      <c r="J142" s="93" t="n"/>
+      <c r="K142" s="61" t="n"/>
+      <c r="L142" s="62" t="n"/>
+      <c r="M142" s="59">
         <f>IF(I142="","",ROUND(I142-E142,2))</f>
         <v/>
       </c>
-      <c r="L142" s="60">
+      <c r="N142" s="60">
         <f>IF(J142="","",J142-F142)</f>
         <v/>
       </c>
-      <c r="M142" s="56" t="n"/>
-      <c r="N142" s="56" t="n"/>
+      <c r="O142" s="56" t="n"/>
+      <c r="P142" s="56" t="n"/>
     </row>
     <row r="143" ht="15" customHeight="1" s="47">
       <c r="A143" s="54" t="n"/>
@@ -4307,18 +4630,20 @@
       <c r="E143" s="59" t="n"/>
       <c r="F143" s="60" t="n"/>
       <c r="G143" s="54" t="n"/>
-      <c r="I143" s="61" t="n"/>
-      <c r="J143" s="62" t="n"/>
-      <c r="K143" s="59">
+      <c r="I143" s="92" t="n"/>
+      <c r="J143" s="93" t="n"/>
+      <c r="K143" s="61" t="n"/>
+      <c r="L143" s="62" t="n"/>
+      <c r="M143" s="59">
         <f>IF(I143="","",ROUND(I143-E143,2))</f>
         <v/>
       </c>
-      <c r="L143" s="60">
+      <c r="N143" s="60">
         <f>IF(J143="","",J143-F143)</f>
         <v/>
       </c>
-      <c r="M143" s="56" t="n"/>
-      <c r="N143" s="56" t="n"/>
+      <c r="O143" s="56" t="n"/>
+      <c r="P143" s="56" t="n"/>
     </row>
     <row r="144" ht="15" customHeight="1" s="47">
       <c r="A144" s="54" t="n"/>
@@ -4328,18 +4653,20 @@
       <c r="E144" s="59" t="n"/>
       <c r="F144" s="60" t="n"/>
       <c r="G144" s="54" t="n"/>
-      <c r="I144" s="61" t="n"/>
-      <c r="J144" s="62" t="n"/>
-      <c r="K144" s="59">
+      <c r="I144" s="92" t="n"/>
+      <c r="J144" s="93" t="n"/>
+      <c r="K144" s="61" t="n"/>
+      <c r="L144" s="62" t="n"/>
+      <c r="M144" s="59">
         <f>IF(I144="","",ROUND(I144-E144,2))</f>
         <v/>
       </c>
-      <c r="L144" s="60">
+      <c r="N144" s="60">
         <f>IF(J144="","",J144-F144)</f>
         <v/>
       </c>
-      <c r="M144" s="56" t="n"/>
-      <c r="N144" s="56" t="n"/>
+      <c r="O144" s="56" t="n"/>
+      <c r="P144" s="56" t="n"/>
     </row>
     <row r="145" ht="15" customHeight="1" s="47">
       <c r="A145" s="54" t="n"/>
@@ -4349,18 +4676,20 @@
       <c r="E145" s="59" t="n"/>
       <c r="F145" s="60" t="n"/>
       <c r="G145" s="54" t="n"/>
-      <c r="I145" s="61" t="n"/>
-      <c r="J145" s="62" t="n"/>
-      <c r="K145" s="59">
+      <c r="I145" s="92" t="n"/>
+      <c r="J145" s="93" t="n"/>
+      <c r="K145" s="61" t="n"/>
+      <c r="L145" s="62" t="n"/>
+      <c r="M145" s="59">
         <f>IF(I145="","",ROUND(I145-E145,2))</f>
         <v/>
       </c>
-      <c r="L145" s="60">
+      <c r="N145" s="60">
         <f>IF(J145="","",J145-F145)</f>
         <v/>
       </c>
-      <c r="M145" s="56" t="n"/>
-      <c r="N145" s="56" t="n"/>
+      <c r="O145" s="56" t="n"/>
+      <c r="P145" s="56" t="n"/>
     </row>
     <row r="146" ht="15" customHeight="1" s="47">
       <c r="A146" s="54" t="n"/>
@@ -4370,18 +4699,20 @@
       <c r="E146" s="59" t="n"/>
       <c r="F146" s="60" t="n"/>
       <c r="G146" s="54" t="n"/>
-      <c r="I146" s="61" t="n"/>
-      <c r="J146" s="62" t="n"/>
-      <c r="K146" s="59">
+      <c r="I146" s="92" t="n"/>
+      <c r="J146" s="93" t="n"/>
+      <c r="K146" s="61" t="n"/>
+      <c r="L146" s="62" t="n"/>
+      <c r="M146" s="59">
         <f>IF(I146="","",ROUND(I146-E146,2))</f>
         <v/>
       </c>
-      <c r="L146" s="60">
+      <c r="N146" s="60">
         <f>IF(J146="","",J146-F146)</f>
         <v/>
       </c>
-      <c r="M146" s="56" t="n"/>
-      <c r="N146" s="56" t="n"/>
+      <c r="O146" s="56" t="n"/>
+      <c r="P146" s="56" t="n"/>
     </row>
     <row r="147" ht="15" customHeight="1" s="47">
       <c r="A147" s="54" t="n"/>
@@ -4391,18 +4722,20 @@
       <c r="E147" s="59" t="n"/>
       <c r="F147" s="60" t="n"/>
       <c r="G147" s="54" t="n"/>
-      <c r="I147" s="61" t="n"/>
-      <c r="J147" s="62" t="n"/>
-      <c r="K147" s="59">
+      <c r="I147" s="92" t="n"/>
+      <c r="J147" s="93" t="n"/>
+      <c r="K147" s="61" t="n"/>
+      <c r="L147" s="62" t="n"/>
+      <c r="M147" s="59">
         <f>IF(I147="","",ROUND(I147-E147,2))</f>
         <v/>
       </c>
-      <c r="L147" s="60">
+      <c r="N147" s="60">
         <f>IF(J147="","",J147-F147)</f>
         <v/>
       </c>
-      <c r="M147" s="56" t="n"/>
-      <c r="N147" s="56" t="n"/>
+      <c r="O147" s="56" t="n"/>
+      <c r="P147" s="56" t="n"/>
     </row>
     <row r="148" ht="15" customHeight="1" s="47">
       <c r="A148" s="54" t="n"/>
@@ -4412,18 +4745,20 @@
       <c r="E148" s="59" t="n"/>
       <c r="F148" s="60" t="n"/>
       <c r="G148" s="54" t="n"/>
-      <c r="I148" s="61" t="n"/>
-      <c r="J148" s="62" t="n"/>
-      <c r="K148" s="59">
+      <c r="I148" s="92" t="n"/>
+      <c r="J148" s="93" t="n"/>
+      <c r="K148" s="61" t="n"/>
+      <c r="L148" s="62" t="n"/>
+      <c r="M148" s="59">
         <f>IF(I148="","",ROUND(I148-E148,2))</f>
         <v/>
       </c>
-      <c r="L148" s="60">
+      <c r="N148" s="60">
         <f>IF(J148="","",J148-F148)</f>
         <v/>
       </c>
-      <c r="M148" s="56" t="n"/>
-      <c r="N148" s="56" t="n"/>
+      <c r="O148" s="56" t="n"/>
+      <c r="P148" s="56" t="n"/>
     </row>
     <row r="149" ht="15" customHeight="1" s="47">
       <c r="A149" s="54" t="n"/>
@@ -4433,18 +4768,20 @@
       <c r="E149" s="59" t="n"/>
       <c r="F149" s="60" t="n"/>
       <c r="G149" s="54" t="n"/>
-      <c r="I149" s="61" t="n"/>
-      <c r="J149" s="62" t="n"/>
-      <c r="K149" s="59">
+      <c r="I149" s="92" t="n"/>
+      <c r="J149" s="93" t="n"/>
+      <c r="K149" s="61" t="n"/>
+      <c r="L149" s="62" t="n"/>
+      <c r="M149" s="59">
         <f>IF(I149="","",ROUND(I149-E149,2))</f>
         <v/>
       </c>
-      <c r="L149" s="60">
+      <c r="N149" s="60">
         <f>IF(J149="","",J149-F149)</f>
         <v/>
       </c>
-      <c r="M149" s="56" t="n"/>
-      <c r="N149" s="56" t="n"/>
+      <c r="O149" s="56" t="n"/>
+      <c r="P149" s="56" t="n"/>
     </row>
     <row r="150" ht="15" customHeight="1" s="47">
       <c r="A150" s="54" t="n"/>
@@ -4454,18 +4791,20 @@
       <c r="E150" s="59" t="n"/>
       <c r="F150" s="60" t="n"/>
       <c r="G150" s="54" t="n"/>
-      <c r="I150" s="61" t="n"/>
-      <c r="J150" s="62" t="n"/>
-      <c r="K150" s="59">
+      <c r="I150" s="92" t="n"/>
+      <c r="J150" s="93" t="n"/>
+      <c r="K150" s="61" t="n"/>
+      <c r="L150" s="62" t="n"/>
+      <c r="M150" s="59">
         <f>IF(I150="","",ROUND(I150-E150,2))</f>
         <v/>
       </c>
-      <c r="L150" s="60">
+      <c r="N150" s="60">
         <f>IF(J150="","",J150-F150)</f>
         <v/>
       </c>
-      <c r="M150" s="56" t="n"/>
-      <c r="N150" s="56" t="n"/>
+      <c r="O150" s="56" t="n"/>
+      <c r="P150" s="56" t="n"/>
     </row>
     <row r="151" ht="15" customHeight="1" s="47">
       <c r="A151" s="54" t="n"/>
@@ -4475,18 +4814,20 @@
       <c r="E151" s="59" t="n"/>
       <c r="F151" s="60" t="n"/>
       <c r="G151" s="54" t="n"/>
-      <c r="I151" s="61" t="n"/>
-      <c r="J151" s="62" t="n"/>
-      <c r="K151" s="59">
+      <c r="I151" s="92" t="n"/>
+      <c r="J151" s="93" t="n"/>
+      <c r="K151" s="61" t="n"/>
+      <c r="L151" s="62" t="n"/>
+      <c r="M151" s="59">
         <f>IF(I151="","",ROUND(I151-E151,2))</f>
         <v/>
       </c>
-      <c r="L151" s="60">
+      <c r="N151" s="60">
         <f>IF(J151="","",J151-F151)</f>
         <v/>
       </c>
-      <c r="M151" s="56" t="n"/>
-      <c r="N151" s="56" t="n"/>
+      <c r="O151" s="56" t="n"/>
+      <c r="P151" s="56" t="n"/>
     </row>
     <row r="152" ht="15" customHeight="1" s="47">
       <c r="A152" s="54" t="n"/>
@@ -4496,18 +4837,20 @@
       <c r="E152" s="59" t="n"/>
       <c r="F152" s="60" t="n"/>
       <c r="G152" s="54" t="n"/>
-      <c r="I152" s="61" t="n"/>
-      <c r="J152" s="62" t="n"/>
-      <c r="K152" s="59">
+      <c r="I152" s="92" t="n"/>
+      <c r="J152" s="93" t="n"/>
+      <c r="K152" s="61" t="n"/>
+      <c r="L152" s="62" t="n"/>
+      <c r="M152" s="59">
         <f>IF(I152="","",ROUND(I152-E152,2))</f>
         <v/>
       </c>
-      <c r="L152" s="60">
+      <c r="N152" s="60">
         <f>IF(J152="","",J152-F152)</f>
         <v/>
       </c>
-      <c r="M152" s="56" t="n"/>
-      <c r="N152" s="56" t="n"/>
+      <c r="O152" s="56" t="n"/>
+      <c r="P152" s="56" t="n"/>
     </row>
     <row r="153" ht="15" customHeight="1" s="47">
       <c r="A153" s="54" t="n"/>
@@ -4517,18 +4860,20 @@
       <c r="E153" s="59" t="n"/>
       <c r="F153" s="60" t="n"/>
       <c r="G153" s="54" t="n"/>
-      <c r="I153" s="61" t="n"/>
-      <c r="J153" s="62" t="n"/>
-      <c r="K153" s="59">
+      <c r="I153" s="92" t="n"/>
+      <c r="J153" s="93" t="n"/>
+      <c r="K153" s="61" t="n"/>
+      <c r="L153" s="62" t="n"/>
+      <c r="M153" s="59">
         <f>IF(I153="","",ROUND(I153-E153,2))</f>
         <v/>
       </c>
-      <c r="L153" s="60">
+      <c r="N153" s="60">
         <f>IF(J153="","",J153-F153)</f>
         <v/>
       </c>
-      <c r="M153" s="56" t="n"/>
-      <c r="N153" s="56" t="n"/>
+      <c r="O153" s="56" t="n"/>
+      <c r="P153" s="56" t="n"/>
     </row>
     <row r="154" ht="15" customHeight="1" s="47">
       <c r="A154" s="54" t="n"/>
@@ -4538,18 +4883,20 @@
       <c r="E154" s="59" t="n"/>
       <c r="F154" s="60" t="n"/>
       <c r="G154" s="54" t="n"/>
-      <c r="I154" s="61" t="n"/>
-      <c r="J154" s="62" t="n"/>
-      <c r="K154" s="59">
+      <c r="I154" s="92" t="n"/>
+      <c r="J154" s="93" t="n"/>
+      <c r="K154" s="61" t="n"/>
+      <c r="L154" s="62" t="n"/>
+      <c r="M154" s="59">
         <f>IF(I154="","",ROUND(I154-E154,2))</f>
         <v/>
       </c>
-      <c r="L154" s="60">
+      <c r="N154" s="60">
         <f>IF(J154="","",J154-F154)</f>
         <v/>
       </c>
-      <c r="M154" s="56" t="n"/>
-      <c r="N154" s="56" t="n"/>
+      <c r="O154" s="56" t="n"/>
+      <c r="P154" s="56" t="n"/>
     </row>
     <row r="155" ht="15" customHeight="1" s="47">
       <c r="A155" s="54" t="n"/>
@@ -4559,18 +4906,20 @@
       <c r="E155" s="59" t="n"/>
       <c r="F155" s="60" t="n"/>
       <c r="G155" s="54" t="n"/>
-      <c r="I155" s="61" t="n"/>
-      <c r="J155" s="62" t="n"/>
-      <c r="K155" s="59">
+      <c r="I155" s="92" t="n"/>
+      <c r="J155" s="93" t="n"/>
+      <c r="K155" s="61" t="n"/>
+      <c r="L155" s="62" t="n"/>
+      <c r="M155" s="59">
         <f>IF(I155="","",ROUND(I155-E155,2))</f>
         <v/>
       </c>
-      <c r="L155" s="60">
+      <c r="N155" s="60">
         <f>IF(J155="","",J155-F155)</f>
         <v/>
       </c>
-      <c r="M155" s="56" t="n"/>
-      <c r="N155" s="56" t="n"/>
+      <c r="O155" s="56" t="n"/>
+      <c r="P155" s="56" t="n"/>
     </row>
     <row r="156" ht="15" customHeight="1" s="47">
       <c r="A156" s="54" t="n"/>
@@ -4580,18 +4929,20 @@
       <c r="E156" s="59" t="n"/>
       <c r="F156" s="60" t="n"/>
       <c r="G156" s="54" t="n"/>
-      <c r="I156" s="61" t="n"/>
-      <c r="J156" s="62" t="n"/>
-      <c r="K156" s="59">
+      <c r="I156" s="92" t="n"/>
+      <c r="J156" s="93" t="n"/>
+      <c r="K156" s="61" t="n"/>
+      <c r="L156" s="62" t="n"/>
+      <c r="M156" s="59">
         <f>IF(I156="","",ROUND(I156-E156,2))</f>
         <v/>
       </c>
-      <c r="L156" s="60">
+      <c r="N156" s="60">
         <f>IF(J156="","",J156-F156)</f>
         <v/>
       </c>
-      <c r="M156" s="56" t="n"/>
-      <c r="N156" s="56" t="n"/>
+      <c r="O156" s="56" t="n"/>
+      <c r="P156" s="56" t="n"/>
     </row>
     <row r="157" ht="15" customHeight="1" s="47">
       <c r="A157" s="54" t="n"/>
@@ -4601,18 +4952,20 @@
       <c r="E157" s="59" t="n"/>
       <c r="F157" s="60" t="n"/>
       <c r="G157" s="54" t="n"/>
-      <c r="I157" s="61" t="n"/>
-      <c r="J157" s="62" t="n"/>
-      <c r="K157" s="59">
+      <c r="I157" s="92" t="n"/>
+      <c r="J157" s="93" t="n"/>
+      <c r="K157" s="61" t="n"/>
+      <c r="L157" s="62" t="n"/>
+      <c r="M157" s="59">
         <f>IF(I157="","",ROUND(I157-E157,2))</f>
         <v/>
       </c>
-      <c r="L157" s="60">
+      <c r="N157" s="60">
         <f>IF(J157="","",J157-F157)</f>
         <v/>
       </c>
-      <c r="M157" s="56" t="n"/>
-      <c r="N157" s="56" t="n"/>
+      <c r="O157" s="56" t="n"/>
+      <c r="P157" s="56" t="n"/>
     </row>
     <row r="158" ht="15" customHeight="1" s="47">
       <c r="A158" s="54" t="n"/>
@@ -4622,18 +4975,20 @@
       <c r="E158" s="59" t="n"/>
       <c r="F158" s="60" t="n"/>
       <c r="G158" s="54" t="n"/>
-      <c r="I158" s="61" t="n"/>
-      <c r="J158" s="62" t="n"/>
-      <c r="K158" s="59">
+      <c r="I158" s="92" t="n"/>
+      <c r="J158" s="93" t="n"/>
+      <c r="K158" s="61" t="n"/>
+      <c r="L158" s="62" t="n"/>
+      <c r="M158" s="59">
         <f>IF(I158="","",ROUND(I158-E158,2))</f>
         <v/>
       </c>
-      <c r="L158" s="60">
+      <c r="N158" s="60">
         <f>IF(J158="","",J158-F158)</f>
         <v/>
       </c>
-      <c r="M158" s="56" t="n"/>
-      <c r="N158" s="56" t="n"/>
+      <c r="O158" s="56" t="n"/>
+      <c r="P158" s="56" t="n"/>
     </row>
     <row r="159" ht="15" customHeight="1" s="47">
       <c r="A159" s="54" t="n"/>
@@ -4643,18 +4998,20 @@
       <c r="E159" s="59" t="n"/>
       <c r="F159" s="60" t="n"/>
       <c r="G159" s="54" t="n"/>
-      <c r="I159" s="61" t="n"/>
-      <c r="J159" s="62" t="n"/>
-      <c r="K159" s="59">
+      <c r="I159" s="92" t="n"/>
+      <c r="J159" s="93" t="n"/>
+      <c r="K159" s="61" t="n"/>
+      <c r="L159" s="62" t="n"/>
+      <c r="M159" s="59">
         <f>IF(I159="","",ROUND(I159-E159,2))</f>
         <v/>
       </c>
-      <c r="L159" s="60">
+      <c r="N159" s="60">
         <f>IF(J159="","",J159-F159)</f>
         <v/>
       </c>
-      <c r="M159" s="56" t="n"/>
-      <c r="N159" s="56" t="n"/>
+      <c r="O159" s="56" t="n"/>
+      <c r="P159" s="56" t="n"/>
     </row>
     <row r="160" ht="15" customHeight="1" s="47">
       <c r="A160" s="54" t="n"/>
@@ -4664,18 +5021,20 @@
       <c r="E160" s="59" t="n"/>
       <c r="F160" s="60" t="n"/>
       <c r="G160" s="54" t="n"/>
-      <c r="I160" s="61" t="n"/>
-      <c r="J160" s="62" t="n"/>
-      <c r="K160" s="59">
+      <c r="I160" s="92" t="n"/>
+      <c r="J160" s="93" t="n"/>
+      <c r="K160" s="61" t="n"/>
+      <c r="L160" s="62" t="n"/>
+      <c r="M160" s="59">
         <f>IF(I160="","",ROUND(I160-E160,2))</f>
         <v/>
       </c>
-      <c r="L160" s="60">
+      <c r="N160" s="60">
         <f>IF(J160="","",J160-F160)</f>
         <v/>
       </c>
-      <c r="M160" s="56" t="n"/>
-      <c r="N160" s="56" t="n"/>
+      <c r="O160" s="56" t="n"/>
+      <c r="P160" s="56" t="n"/>
     </row>
     <row r="161" ht="15" customHeight="1" s="47">
       <c r="A161" s="63" t="n"/>
@@ -4695,24 +5054,26 @@
         <v/>
       </c>
       <c r="G161" s="63" t="n"/>
-      <c r="I161" s="65">
+      <c r="I161" s="92" t="n"/>
+      <c r="J161" s="93" t="n"/>
+      <c r="K161" s="65">
         <f>SUM(I5:I160)</f>
         <v/>
       </c>
-      <c r="J161" s="66">
+      <c r="L161" s="66">
         <f>SUM(J5:J160)</f>
         <v/>
       </c>
-      <c r="K161" s="65">
+      <c r="M161" s="65">
         <f>SUM(K5:K160)</f>
         <v/>
       </c>
-      <c r="L161" s="66">
+      <c r="N161" s="66">
         <f>SUM(L5:L160)</f>
         <v/>
       </c>
-      <c r="M161" s="63" t="n"/>
-      <c r="N161" s="63" t="n"/>
+      <c r="O161" s="63" t="n"/>
+      <c r="P161" s="63" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A4:M160"/>
@@ -20276,11 +20637,11 @@
         <v/>
       </c>
       <c r="F5" s="59">
-        <f>SUMIF('Count Sheet'!$A$5:$A$160,$A5,'Count Sheet'!$I$5:$I$160)</f>
+        <f>SUMIF('Count Sheet'!$A$5:$A$160,$A5,'Count Sheet'!$K$5:$K$160)</f>
         <v/>
       </c>
       <c r="G5" s="60">
-        <f>SUMIF('Count Sheet'!$A$5:$A$160,$A5,'Count Sheet'!$J$5:$J$160)</f>
+        <f>SUMIF('Count Sheet'!$A$5:$A$160,$A5,'Count Sheet'!$L$5:$L$160)</f>
         <v/>
       </c>
       <c r="H5" s="59">
@@ -20324,11 +20685,11 @@
         <v/>
       </c>
       <c r="F6" s="59">
-        <f>SUMIF('Count Sheet'!$A$5:$A$160,$A6,'Count Sheet'!$I$5:$I$160)</f>
+        <f>SUMIF('Count Sheet'!$A$5:$A$160,$A6,'Count Sheet'!$K$5:$K$160)</f>
         <v/>
       </c>
       <c r="G6" s="60">
-        <f>SUMIF('Count Sheet'!$A$5:$A$160,$A6,'Count Sheet'!$J$5:$J$160)</f>
+        <f>SUMIF('Count Sheet'!$A$5:$A$160,$A6,'Count Sheet'!$L$5:$L$160)</f>
         <v/>
       </c>
       <c r="H6" s="59">
@@ -20372,11 +20733,11 @@
         <v/>
       </c>
       <c r="F7" s="59">
-        <f>SUMIF('Count Sheet'!$A$5:$A$160,$A7,'Count Sheet'!$I$5:$I$160)</f>
+        <f>SUMIF('Count Sheet'!$A$5:$A$160,$A7,'Count Sheet'!$K$5:$K$160)</f>
         <v/>
       </c>
       <c r="G7" s="60">
-        <f>SUMIF('Count Sheet'!$A$5:$A$160,$A7,'Count Sheet'!$J$5:$J$160)</f>
+        <f>SUMIF('Count Sheet'!$A$5:$A$160,$A7,'Count Sheet'!$L$5:$L$160)</f>
         <v/>
       </c>
       <c r="H7" s="59">
@@ -20420,11 +20781,11 @@
         <v/>
       </c>
       <c r="F8" s="59">
-        <f>SUMIF('Count Sheet'!$A$5:$A$160,$A8,'Count Sheet'!$I$5:$I$160)</f>
+        <f>SUMIF('Count Sheet'!$A$5:$A$160,$A8,'Count Sheet'!$K$5:$K$160)</f>
         <v/>
       </c>
       <c r="G8" s="60">
-        <f>SUMIF('Count Sheet'!$A$5:$A$160,$A8,'Count Sheet'!$J$5:$J$160)</f>
+        <f>SUMIF('Count Sheet'!$A$5:$A$160,$A8,'Count Sheet'!$L$5:$L$160)</f>
         <v/>
       </c>
       <c r="H8" s="59">
@@ -20468,11 +20829,11 @@
         <v/>
       </c>
       <c r="F9" s="59">
-        <f>SUMIF('Count Sheet'!$A$5:$A$160,$A9,'Count Sheet'!$I$5:$I$160)</f>
+        <f>SUMIF('Count Sheet'!$A$5:$A$160,$A9,'Count Sheet'!$K$5:$K$160)</f>
         <v/>
       </c>
       <c r="G9" s="60">
-        <f>SUMIF('Count Sheet'!$A$5:$A$160,$A9,'Count Sheet'!$J$5:$J$160)</f>
+        <f>SUMIF('Count Sheet'!$A$5:$A$160,$A9,'Count Sheet'!$L$5:$L$160)</f>
         <v/>
       </c>
       <c r="H9" s="59">
@@ -20516,11 +20877,11 @@
         <v/>
       </c>
       <c r="F10" s="59">
-        <f>SUMIF('Count Sheet'!$A$5:$A$160,$A10,'Count Sheet'!$I$5:$I$160)</f>
+        <f>SUMIF('Count Sheet'!$A$5:$A$160,$A10,'Count Sheet'!$K$5:$K$160)</f>
         <v/>
       </c>
       <c r="G10" s="60">
-        <f>SUMIF('Count Sheet'!$A$5:$A$160,$A10,'Count Sheet'!$J$5:$J$160)</f>
+        <f>SUMIF('Count Sheet'!$A$5:$A$160,$A10,'Count Sheet'!$L$5:$L$160)</f>
         <v/>
       </c>
       <c r="H10" s="59">
@@ -20564,11 +20925,11 @@
         <v/>
       </c>
       <c r="F11" s="59">
-        <f>SUMIF('Count Sheet'!$A$5:$A$160,$A11,'Count Sheet'!$I$5:$I$160)</f>
+        <f>SUMIF('Count Sheet'!$A$5:$A$160,$A11,'Count Sheet'!$K$5:$K$160)</f>
         <v/>
       </c>
       <c r="G11" s="60">
-        <f>SUMIF('Count Sheet'!$A$5:$A$160,$A11,'Count Sheet'!$J$5:$J$160)</f>
+        <f>SUMIF('Count Sheet'!$A$5:$A$160,$A11,'Count Sheet'!$L$5:$L$160)</f>
         <v/>
       </c>
       <c r="H11" s="59">
@@ -20612,11 +20973,11 @@
         <v/>
       </c>
       <c r="F12" s="59">
-        <f>SUMIF('Count Sheet'!$A$5:$A$160,$A12,'Count Sheet'!$I$5:$I$160)</f>
+        <f>SUMIF('Count Sheet'!$A$5:$A$160,$A12,'Count Sheet'!$K$5:$K$160)</f>
         <v/>
       </c>
       <c r="G12" s="60">
-        <f>SUMIF('Count Sheet'!$A$5:$A$160,$A12,'Count Sheet'!$J$5:$J$160)</f>
+        <f>SUMIF('Count Sheet'!$A$5:$A$160,$A12,'Count Sheet'!$L$5:$L$160)</f>
         <v/>
       </c>
       <c r="H12" s="59">
@@ -20660,11 +21021,11 @@
         <v/>
       </c>
       <c r="F13" s="59">
-        <f>SUMIF('Count Sheet'!$A$5:$A$160,$A13,'Count Sheet'!$I$5:$I$160)</f>
+        <f>SUMIF('Count Sheet'!$A$5:$A$160,$A13,'Count Sheet'!$K$5:$K$160)</f>
         <v/>
       </c>
       <c r="G13" s="60">
-        <f>SUMIF('Count Sheet'!$A$5:$A$160,$A13,'Count Sheet'!$J$5:$J$160)</f>
+        <f>SUMIF('Count Sheet'!$A$5:$A$160,$A13,'Count Sheet'!$L$5:$L$160)</f>
         <v/>
       </c>
       <c r="H13" s="59">
@@ -20708,11 +21069,11 @@
         <v/>
       </c>
       <c r="F14" s="59">
-        <f>SUMIF('Count Sheet'!$A$5:$A$160,$A14,'Count Sheet'!$I$5:$I$160)</f>
+        <f>SUMIF('Count Sheet'!$A$5:$A$160,$A14,'Count Sheet'!$K$5:$K$160)</f>
         <v/>
       </c>
       <c r="G14" s="60">
-        <f>SUMIF('Count Sheet'!$A$5:$A$160,$A14,'Count Sheet'!$J$5:$J$160)</f>
+        <f>SUMIF('Count Sheet'!$A$5:$A$160,$A14,'Count Sheet'!$L$5:$L$160)</f>
         <v/>
       </c>
       <c r="H14" s="59">
@@ -20756,11 +21117,11 @@
         <v/>
       </c>
       <c r="F15" s="59">
-        <f>SUMIF('Count Sheet'!$A$5:$A$160,$A15,'Count Sheet'!$I$5:$I$160)</f>
+        <f>SUMIF('Count Sheet'!$A$5:$A$160,$A15,'Count Sheet'!$K$5:$K$160)</f>
         <v/>
       </c>
       <c r="G15" s="60">
-        <f>SUMIF('Count Sheet'!$A$5:$A$160,$A15,'Count Sheet'!$J$5:$J$160)</f>
+        <f>SUMIF('Count Sheet'!$A$5:$A$160,$A15,'Count Sheet'!$L$5:$L$160)</f>
         <v/>
       </c>
       <c r="H15" s="59">
@@ -20804,11 +21165,11 @@
         <v/>
       </c>
       <c r="F16" s="59">
-        <f>SUMIF('Count Sheet'!$A$5:$A$160,$A16,'Count Sheet'!$I$5:$I$160)</f>
+        <f>SUMIF('Count Sheet'!$A$5:$A$160,$A16,'Count Sheet'!$K$5:$K$160)</f>
         <v/>
       </c>
       <c r="G16" s="60">
-        <f>SUMIF('Count Sheet'!$A$5:$A$160,$A16,'Count Sheet'!$J$5:$J$160)</f>
+        <f>SUMIF('Count Sheet'!$A$5:$A$160,$A16,'Count Sheet'!$L$5:$L$160)</f>
         <v/>
       </c>
       <c r="H16" s="59">
@@ -20852,11 +21213,11 @@
         <v/>
       </c>
       <c r="F17" s="59">
-        <f>SUMIF('Count Sheet'!$A$5:$A$160,$A17,'Count Sheet'!$I$5:$I$160)</f>
+        <f>SUMIF('Count Sheet'!$A$5:$A$160,$A17,'Count Sheet'!$K$5:$K$160)</f>
         <v/>
       </c>
       <c r="G17" s="60">
-        <f>SUMIF('Count Sheet'!$A$5:$A$160,$A17,'Count Sheet'!$J$5:$J$160)</f>
+        <f>SUMIF('Count Sheet'!$A$5:$A$160,$A17,'Count Sheet'!$L$5:$L$160)</f>
         <v/>
       </c>
       <c r="H17" s="59">
@@ -20900,11 +21261,11 @@
         <v/>
       </c>
       <c r="F18" s="59">
-        <f>SUMIF('Count Sheet'!$A$5:$A$160,$A18,'Count Sheet'!$I$5:$I$160)</f>
+        <f>SUMIF('Count Sheet'!$A$5:$A$160,$A18,'Count Sheet'!$K$5:$K$160)</f>
         <v/>
       </c>
       <c r="G18" s="60">
-        <f>SUMIF('Count Sheet'!$A$5:$A$160,$A18,'Count Sheet'!$J$5:$J$160)</f>
+        <f>SUMIF('Count Sheet'!$A$5:$A$160,$A18,'Count Sheet'!$L$5:$L$160)</f>
         <v/>
       </c>
       <c r="H18" s="59">
